--- a/Sistemi_sablon_radni.xlsx
+++ b/Sistemi_sablon_radni.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andra\PycharmProjects\HorsesProduction\MainEnv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andra\PycharmProjects\Horses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A755A0D-D835-466C-87B4-25D196946F94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A98778-F54B-4FF4-A182-047A5EA2182E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18600" yWindow="0" windowWidth="20880" windowHeight="8430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,1264 +424,1264 @@
     <t>&lt;6</t>
   </si>
   <si>
+    <t>&lt;10000</t>
+  </si>
+  <si>
+    <t>Archie Watson</t>
+  </si>
+  <si>
+    <t>Hollie Doyle</t>
+  </si>
+  <si>
+    <t>3yo+</t>
+  </si>
+  <si>
+    <t>Rossa Ryan</t>
+  </si>
+  <si>
+    <t>Eve Johnson Houghton</t>
+  </si>
+  <si>
+    <t>&gt;45</t>
+  </si>
+  <si>
+    <t>Gillian Boanas</t>
+  </si>
+  <si>
+    <t>Rod Millman</t>
+  </si>
+  <si>
+    <t>&gt;70</t>
+  </si>
+  <si>
+    <t>&gt;5</t>
+  </si>
+  <si>
+    <t>&lt;1400</t>
+  </si>
+  <si>
+    <t>&lt;1700</t>
+  </si>
+  <si>
+    <t>&gt;57</t>
+  </si>
+  <si>
+    <t>&gt;3</t>
+  </si>
+  <si>
+    <t>&gt;=25</t>
+  </si>
+  <si>
+    <t>Declan Carroll</t>
+  </si>
+  <si>
+    <t>Ayr, Redcar, Yarmouth, Doncaster, Ffos Las, Nottingham, Haydock, Newbury, Wetherby</t>
+  </si>
+  <si>
+    <t>Chris Wall</t>
+  </si>
+  <si>
+    <t>Christopher Mason</t>
+  </si>
+  <si>
+    <t>Chepstow</t>
+  </si>
+  <si>
+    <t>Chepstow, Brighton</t>
+  </si>
+  <si>
+    <t>Clive Cox</t>
+  </si>
+  <si>
+    <t>Chepstow, Epsom, Brighton</t>
+  </si>
+  <si>
+    <t>Chepstow, Epsom</t>
+  </si>
+  <si>
+    <t>Beverley, Carlisle</t>
+  </si>
+  <si>
+    <t>Edward Bethell</t>
+  </si>
+  <si>
+    <t>Ismail Mohammed</t>
+  </si>
+  <si>
+    <t>John Butler</t>
+  </si>
+  <si>
+    <t>Rae Guest</t>
+  </si>
+  <si>
+    <t>Bath</t>
+  </si>
+  <si>
+    <t>Yarmouth</t>
+  </si>
+  <si>
+    <t>&lt;=1</t>
+  </si>
+  <si>
+    <t>K R Burke</t>
+  </si>
+  <si>
+    <t>Richard Fahey</t>
+  </si>
+  <si>
+    <t>&gt;2000</t>
+  </si>
+  <si>
+    <t>Jim Goldie</t>
+  </si>
+  <si>
+    <t>Catterick</t>
+  </si>
+  <si>
+    <t>Keith Dalgleish</t>
+  </si>
+  <si>
+    <t>Newmarket (July)</t>
+  </si>
+  <si>
+    <t>Saeed bin Suroor</t>
+  </si>
+  <si>
+    <t>William Buick</t>
+  </si>
+  <si>
+    <t>John &amp; Thady Gosden, John Gosden</t>
+  </si>
+  <si>
+    <t>Robert Havlin</t>
+  </si>
+  <si>
+    <t>Goodwood, Newbury</t>
+  </si>
+  <si>
+    <t>William Haggas</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Newmarket</t>
+  </si>
+  <si>
+    <t>Gary Moore</t>
+  </si>
+  <si>
+    <t>&lt;20</t>
+  </si>
+  <si>
+    <t>Ivan Furtado</t>
+  </si>
+  <si>
+    <t>c, f</t>
+  </si>
+  <si>
+    <t>&lt;2</t>
+  </si>
+  <si>
+    <t>Oisin Murphy</t>
+  </si>
+  <si>
+    <t>Adam Farragher</t>
+  </si>
+  <si>
+    <t>Ian Williams</t>
+  </si>
+  <si>
+    <t>James Ferguson</t>
+  </si>
+  <si>
+    <t>&lt;60</t>
+  </si>
+  <si>
+    <t>Mrs John Harrington</t>
+  </si>
+  <si>
+    <t>&gt;10</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>between 1051 and 1449</t>
+  </si>
+  <si>
+    <t>Simon &amp; Ed Crisford</t>
+  </si>
+  <si>
+    <t>between 2151 and 2249</t>
+  </si>
+  <si>
+    <t>Grant Tuer</t>
+  </si>
+  <si>
+    <t>&gt;=3</t>
+  </si>
+  <si>
+    <t>Hugo Palmer</t>
+  </si>
+  <si>
+    <t>&lt;8</t>
+  </si>
+  <si>
+    <t>James Fanshawe</t>
+  </si>
+  <si>
+    <t>between 8 and 13</t>
+  </si>
+  <si>
+    <t>Beverley, Hamilton, Carlisle</t>
+  </si>
+  <si>
+    <t>Redcar, Ayr, Yarmouth, York, Doncaster, Ffos Las, Nottingham, Haydock, Newbury, Wetherby</t>
+  </si>
+  <si>
+    <t>Ollie Pears</t>
+  </si>
+  <si>
+    <t>Julie Camacho</t>
+  </si>
+  <si>
+    <t>&lt; -10</t>
+  </si>
+  <si>
+    <t>between 14 and 29</t>
+  </si>
+  <si>
+    <t>Newmarket, Newmarket (July)</t>
+  </si>
+  <si>
+    <t>Rank_overall</t>
+  </si>
+  <si>
+    <t>&lt;=2</t>
+  </si>
+  <si>
+    <t>AVGPRB2_overall_Proj</t>
+  </si>
+  <si>
+    <t>Steph Hollinshead</t>
+  </si>
+  <si>
+    <t>Julia Feilden</t>
+  </si>
+  <si>
+    <t>&lt;21</t>
+  </si>
+  <si>
+    <t>Michael Appleby</t>
+  </si>
+  <si>
+    <t>between 6 and 9</t>
+  </si>
+  <si>
+    <t>Beverley, Carlisle, Pontefract</t>
+  </si>
+  <si>
+    <t>Paul Midgley</t>
+  </si>
+  <si>
+    <t>&gt;20</t>
+  </si>
+  <si>
+    <t>&lt;1</t>
+  </si>
+  <si>
+    <t>between -3 and -1</t>
+  </si>
+  <si>
+    <t>Charlie Johnston</t>
+  </si>
+  <si>
+    <t>Tom Clover</t>
+  </si>
+  <si>
+    <t>Sys102</t>
+  </si>
+  <si>
+    <t>Sys103</t>
+  </si>
+  <si>
+    <t>Sys104</t>
+  </si>
+  <si>
+    <t>Sys105</t>
+  </si>
+  <si>
+    <t>Sys106</t>
+  </si>
+  <si>
+    <t>Sys107</t>
+  </si>
+  <si>
+    <t>4yo+</t>
+  </si>
+  <si>
+    <t>&lt;3</t>
+  </si>
+  <si>
+    <t>&gt;2</t>
+  </si>
+  <si>
+    <t>&lt;=3</t>
+  </si>
+  <si>
+    <t>David Evans</t>
+  </si>
+  <si>
+    <t>Bryan Smart</t>
+  </si>
+  <si>
+    <t>AVGPRB2_Track</t>
+  </si>
+  <si>
+    <t>Ed Dunlop</t>
+  </si>
+  <si>
+    <t>&lt;30</t>
+  </si>
+  <si>
+    <t>Sir Mark Prescott Bt</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Graham Lee</t>
+  </si>
+  <si>
+    <t>between 1 and 2</t>
+  </si>
+  <si>
+    <t>Jonathan Portman</t>
+  </si>
+  <si>
+    <t>Marco Botti</t>
+  </si>
+  <si>
+    <t>David Simcock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;10 </t>
+  </si>
+  <si>
+    <t>Dianne Sayer</t>
+  </si>
+  <si>
+    <t>Brian Ellison</t>
+  </si>
+  <si>
+    <t>between 2 and 3</t>
+  </si>
+  <si>
+    <t>between 1 and 3</t>
+  </si>
+  <si>
+    <t>ABS_DD</t>
+  </si>
+  <si>
+    <t>[OR_Limit-OR]</t>
+  </si>
+  <si>
+    <t>p, p1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>in (66.67, 100)</t>
+  </si>
+  <si>
+    <t>in (50, 100)</t>
+  </si>
+  <si>
+    <t>Beverley</t>
+  </si>
+  <si>
+    <t>&gt;=1760</t>
+  </si>
+  <si>
+    <t>Rank_overall_1</t>
+  </si>
+  <si>
+    <t>between 8 and 9</t>
+  </si>
+  <si>
+    <t>[OR]</t>
+  </si>
+  <si>
+    <t>between 5 and 6</t>
+  </si>
+  <si>
+    <t>&lt;-40</t>
+  </si>
+  <si>
+    <t>&lt;-1</t>
+  </si>
+  <si>
+    <t>Sys109</t>
+  </si>
+  <si>
+    <t>Sys111</t>
+  </si>
+  <si>
+    <t>Sys112</t>
+  </si>
+  <si>
+    <t>Goodwood</t>
+  </si>
+  <si>
+    <t>&lt;14</t>
+  </si>
+  <si>
+    <t>&lt;=4</t>
+  </si>
+  <si>
+    <t>Sys114</t>
+  </si>
+  <si>
+    <t>Jack Mitchell</t>
+  </si>
+  <si>
+    <t>Sys115</t>
+  </si>
+  <si>
+    <t>Ed Walker</t>
+  </si>
+  <si>
+    <t>Ascot</t>
+  </si>
+  <si>
+    <t>Sys116</t>
+  </si>
+  <si>
+    <t>Harry Eustace</t>
+  </si>
+  <si>
+    <t>Sys117</t>
+  </si>
+  <si>
+    <t>Sys118</t>
+  </si>
+  <si>
+    <t>Sys120</t>
+  </si>
+  <si>
+    <t>Milton Harris</t>
+  </si>
+  <si>
+    <t>Sys121</t>
+  </si>
+  <si>
+    <t>Miss Natalia Lupini</t>
+  </si>
+  <si>
+    <t>M C Grassick</t>
+  </si>
+  <si>
+    <t>Sys123</t>
+  </si>
+  <si>
+    <t>Sys124</t>
+  </si>
+  <si>
+    <t>Ruth Carr</t>
+  </si>
+  <si>
+    <t>James Sullivan</t>
+  </si>
+  <si>
+    <t>Thomas Gibney</t>
+  </si>
+  <si>
+    <t>Sys126</t>
+  </si>
+  <si>
+    <t>Timothy Doyle</t>
+  </si>
+  <si>
+    <t>Sys127</t>
+  </si>
+  <si>
+    <t>Sys129</t>
+  </si>
+  <si>
+    <t>Sys130</t>
+  </si>
+  <si>
+    <t>Sys131</t>
+  </si>
+  <si>
+    <t>&lt;15</t>
+  </si>
+  <si>
+    <t>Sys133</t>
+  </si>
+  <si>
+    <t>Sys134</t>
+  </si>
+  <si>
+    <t>blanks</t>
+  </si>
+  <si>
+    <t>Patrick Chamings</t>
+  </si>
+  <si>
+    <t>Sys135</t>
+  </si>
+  <si>
+    <t>Sys136</t>
+  </si>
+  <si>
+    <t>Sys137</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Sys138</t>
+  </si>
+  <si>
+    <t>Sys139</t>
+  </si>
+  <si>
+    <t>Denis Gerard Hogan</t>
+  </si>
+  <si>
+    <t>&lt;12</t>
+  </si>
+  <si>
+    <t>&gt;1</t>
+  </si>
+  <si>
+    <t>Class_rating_1</t>
+  </si>
+  <si>
+    <t>Rank_Class_1</t>
+  </si>
+  <si>
+    <t>Class_rating_2</t>
+  </si>
+  <si>
+    <t>Rank_Class_2</t>
+  </si>
+  <si>
+    <t>Class_rating_3</t>
+  </si>
+  <si>
+    <t>Rank_Class_3</t>
+  </si>
+  <si>
+    <t>Rank_SFOR_M</t>
+  </si>
+  <si>
+    <t>Rank_SF_M</t>
+  </si>
+  <si>
+    <t>Trainer_change</t>
+  </si>
+  <si>
+    <t>Sys142</t>
+  </si>
+  <si>
+    <t>&gt;6</t>
+  </si>
+  <si>
+    <t>Sys144</t>
+  </si>
+  <si>
+    <t>Blanks or 100</t>
+  </si>
+  <si>
+    <t>Sys145</t>
+  </si>
+  <si>
+    <t>George Boughey</t>
+  </si>
+  <si>
+    <t>&gt;200</t>
+  </si>
+  <si>
+    <t>Sys147</t>
+  </si>
+  <si>
+    <t>Sys149</t>
+  </si>
+  <si>
+    <t>Sys150</t>
+  </si>
+  <si>
+    <t>Sys151</t>
+  </si>
+  <si>
+    <t>Sys152</t>
+  </si>
+  <si>
+    <t>Sys153</t>
+  </si>
+  <si>
+    <t>Sys154</t>
+  </si>
+  <si>
+    <t>Sys155</t>
+  </si>
+  <si>
+    <t>Sys156</t>
+  </si>
+  <si>
+    <t>Sys157</t>
+  </si>
+  <si>
+    <t>Chris Dwyer</t>
+  </si>
+  <si>
+    <t>Sys158</t>
+  </si>
+  <si>
+    <t>Sys161</t>
+  </si>
+  <si>
+    <t>Pam Sly</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Tristan Davidson</t>
+  </si>
+  <si>
+    <t>Sys162</t>
+  </si>
+  <si>
+    <t>Sys163</t>
+  </si>
+  <si>
+    <t>Sys164</t>
+  </si>
+  <si>
+    <t>Chester</t>
+  </si>
+  <si>
+    <t>&lt;1500</t>
+  </si>
+  <si>
+    <t>Sys165</t>
+  </si>
+  <si>
+    <t>&lt;= 3</t>
+  </si>
+  <si>
+    <t>Sys166</t>
+  </si>
+  <si>
+    <t>&lt;70</t>
+  </si>
+  <si>
+    <t>between 0 and -10</t>
+  </si>
+  <si>
+    <t>&lt;100</t>
+  </si>
+  <si>
+    <t>&lt;90</t>
+  </si>
+  <si>
+    <t>Rank_Track_1</t>
+  </si>
+  <si>
+    <t>Sys167</t>
+  </si>
+  <si>
+    <t>Sys168</t>
+  </si>
+  <si>
+    <t>Sys169</t>
+  </si>
+  <si>
+    <t>Sys170</t>
+  </si>
+  <si>
+    <t>Sys171</t>
+  </si>
+  <si>
+    <t>Josephine Gordon</t>
+  </si>
+  <si>
+    <t>Sys172</t>
+  </si>
+  <si>
+    <t>Saffie Osborne</t>
+  </si>
+  <si>
+    <t>Sys173</t>
+  </si>
+  <si>
+    <t>Sys174</t>
+  </si>
+  <si>
+    <t>Sys175</t>
+  </si>
+  <si>
+    <t>Sys177</t>
+  </si>
+  <si>
+    <t>Ben Curtis</t>
+  </si>
+  <si>
+    <t>&gt;135</t>
+  </si>
+  <si>
+    <t>Sys178</t>
+  </si>
+  <si>
+    <t>Phil Dennis</t>
+  </si>
+  <si>
+    <t>Sys179</t>
+  </si>
+  <si>
+    <t>Oisin Orr</t>
+  </si>
+  <si>
+    <t>&gt;4</t>
+  </si>
+  <si>
+    <t>Sys180</t>
+  </si>
+  <si>
+    <t>Clifford Lee</t>
+  </si>
+  <si>
+    <t>Hamilton, Carlisle, Beverley</t>
+  </si>
+  <si>
+    <t>Sys182</t>
+  </si>
+  <si>
+    <t>Paul Hanagan</t>
+  </si>
+  <si>
+    <t>Sys183</t>
+  </si>
+  <si>
+    <t>Sys186</t>
+  </si>
+  <si>
+    <t>Sys187</t>
+  </si>
+  <si>
+    <t>Sys188</t>
+  </si>
+  <si>
+    <t>&gt;2400</t>
+  </si>
+  <si>
+    <t>Fergal OBrien</t>
+  </si>
+  <si>
+    <t>Peter Fahey</t>
+  </si>
+  <si>
+    <t>Sys189</t>
+  </si>
+  <si>
+    <t>Sys191</t>
+  </si>
+  <si>
+    <t>Michael Bell</t>
+  </si>
+  <si>
+    <t>Sys192</t>
+  </si>
+  <si>
+    <t>Charles Hills</t>
+  </si>
+  <si>
+    <t>&gt;130</t>
+  </si>
+  <si>
+    <t>Sys193</t>
+  </si>
+  <si>
+    <t>Tom Marquand</t>
+  </si>
+  <si>
+    <t>&lt;2.5</t>
+  </si>
+  <si>
+    <t>Tim Easterby</t>
+  </si>
+  <si>
+    <t>Roger Fell &amp; Sean Murray, Roger Fell</t>
+  </si>
+  <si>
+    <t>Sys198</t>
+  </si>
+  <si>
+    <t>Sys199</t>
+  </si>
+  <si>
+    <t>&lt;=75</t>
+  </si>
+  <si>
+    <t>Sys200</t>
+  </si>
+  <si>
+    <t>Sys201</t>
+  </si>
+  <si>
+    <t>David Menuisier</t>
+  </si>
+  <si>
+    <t>Sys202</t>
+  </si>
+  <si>
+    <t>Robert Cowell</t>
+  </si>
+  <si>
+    <t>Sys203</t>
+  </si>
+  <si>
+    <t>Sys204</t>
+  </si>
+  <si>
+    <t>Sys205</t>
+  </si>
+  <si>
+    <t>Sys206</t>
+  </si>
+  <si>
+    <t>Sys207</t>
+  </si>
+  <si>
+    <t>Sys208</t>
+  </si>
+  <si>
+    <t>Sys209</t>
+  </si>
+  <si>
+    <t>Sys210</t>
+  </si>
+  <si>
+    <t>Harrison Shaw</t>
+  </si>
+  <si>
+    <t>Sys211</t>
+  </si>
+  <si>
+    <t>Paul Mulrennan</t>
+  </si>
+  <si>
+    <t>Sys212</t>
+  </si>
+  <si>
+    <t>Musselburgh</t>
+  </si>
+  <si>
+    <t>Sys213</t>
+  </si>
+  <si>
+    <t>&lt;=0.25</t>
+  </si>
+  <si>
+    <t>Sys214</t>
+  </si>
+  <si>
+    <t>Sys215</t>
+  </si>
+  <si>
+    <t>Sys216</t>
+  </si>
+  <si>
+    <t>Richard Spencer</t>
+  </si>
+  <si>
+    <t>Last_Race_Name</t>
+  </si>
+  <si>
+    <t>Sys217</t>
+  </si>
+  <si>
+    <t>Sys219</t>
+  </si>
+  <si>
+    <t>Sys220</t>
+  </si>
+  <si>
+    <t>Sys221</t>
+  </si>
+  <si>
+    <t>Sys222</t>
+  </si>
+  <si>
+    <t>B F Brookhouse</t>
+  </si>
+  <si>
+    <t>Nottingham</t>
+  </si>
+  <si>
+    <t>Nigel Tinkler</t>
+  </si>
+  <si>
+    <t>Sys223</t>
+  </si>
+  <si>
+    <t>Sys224</t>
+  </si>
+  <si>
+    <t>Sys225</t>
+  </si>
+  <si>
+    <t>Sys226</t>
+  </si>
+  <si>
+    <t>Sys227</t>
+  </si>
+  <si>
+    <t>Sys228</t>
+  </si>
+  <si>
+    <t>Sys229</t>
+  </si>
+  <si>
+    <t>David Probert</t>
+  </si>
+  <si>
+    <t>Connor Beasley</t>
+  </si>
+  <si>
+    <t>Sys231</t>
+  </si>
+  <si>
+    <t>J P Murtagh</t>
+  </si>
+  <si>
+    <t>Sys232</t>
+  </si>
+  <si>
+    <t>Rank_Age</t>
+  </si>
+  <si>
+    <t>Sys233</t>
+  </si>
+  <si>
+    <t>Sys235</t>
+  </si>
+  <si>
+    <t>Sys238</t>
+  </si>
+  <si>
+    <t>Sys239</t>
+  </si>
+  <si>
+    <t>Sys241</t>
+  </si>
+  <si>
+    <t>Sys242</t>
+  </si>
+  <si>
+    <t>Sys243</t>
+  </si>
+  <si>
+    <t>Sys245</t>
+  </si>
+  <si>
+    <t>Rank_OR_desc</t>
+  </si>
+  <si>
+    <t>Chelsea Banham</t>
+  </si>
+  <si>
+    <t>Joey Haynes</t>
+  </si>
+  <si>
+    <t>Sys246</t>
+  </si>
+  <si>
+    <t>Sys247</t>
+  </si>
+  <si>
+    <t>George Baker</t>
+  </si>
+  <si>
+    <t>Sys248</t>
+  </si>
+  <si>
+    <t>Sys249</t>
+  </si>
+  <si>
+    <t>Sys250</t>
+  </si>
+  <si>
+    <t>Sys251</t>
+  </si>
+  <si>
+    <t>Sys253</t>
+  </si>
+  <si>
+    <t>Sys254</t>
+  </si>
+  <si>
+    <t>Sys255</t>
+  </si>
+  <si>
+    <t>Sys256</t>
+  </si>
+  <si>
+    <t>Simon Hodgson</t>
+  </si>
+  <si>
+    <t>Sys257</t>
+  </si>
+  <si>
+    <t>Sys259</t>
+  </si>
+  <si>
+    <t>Sys260</t>
+  </si>
+  <si>
+    <t>Sys261</t>
+  </si>
+  <si>
+    <t>Sys263</t>
+  </si>
+  <si>
+    <t>Sys264</t>
+  </si>
+  <si>
+    <t>A J Martin</t>
+  </si>
+  <si>
+    <t>Ben Coen</t>
+  </si>
+  <si>
+    <t>David &amp; Nicola Barron</t>
+  </si>
+  <si>
+    <t>Sys265</t>
+  </si>
+  <si>
+    <t>Sys266</t>
+  </si>
+  <si>
+    <t>David Loughnane</t>
+  </si>
+  <si>
+    <t>Laura Pearson</t>
+  </si>
+  <si>
+    <t>Sys267</t>
+  </si>
+  <si>
+    <t>Jarlath P Fahey</t>
+  </si>
+  <si>
+    <t>Leigh Roche</t>
+  </si>
+  <si>
+    <t>Sys268</t>
+  </si>
+  <si>
+    <t>Sys269</t>
+  </si>
+  <si>
+    <t>Sys270</t>
+  </si>
+  <si>
+    <t>Sys273</t>
+  </si>
+  <si>
+    <t>Sys274</t>
+  </si>
+  <si>
+    <t>W McCreery</t>
+  </si>
+  <si>
+    <t>Nathan Crosse</t>
+  </si>
+  <si>
+    <t>Sys275</t>
+  </si>
+  <si>
+    <t>Sys276</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Musselburgh</t>
+  </si>
+  <si>
+    <t>Rowan Scott</t>
+  </si>
+  <si>
+    <t>Sys277</t>
+  </si>
+  <si>
+    <t>Simon Whitaker</t>
+  </si>
+  <si>
+    <t>Sys278</t>
+  </si>
+  <si>
+    <t>Iain Jardine</t>
+  </si>
+  <si>
+    <t>Sys279</t>
+  </si>
+  <si>
+    <t>Sys280</t>
+  </si>
+  <si>
+    <t>Sys281</t>
+  </si>
+  <si>
+    <t>Sys282</t>
+  </si>
+  <si>
+    <t>Sys284</t>
+  </si>
+  <si>
+    <t>Sys285</t>
+  </si>
+  <si>
+    <t>Sys286</t>
+  </si>
+  <si>
+    <t>trainer</t>
+  </si>
+  <si>
+    <t>ORLimitNumeric</t>
+  </si>
+  <si>
+    <t>noOfRunners</t>
+  </si>
+  <si>
+    <t>track</t>
+  </si>
+  <si>
+    <t>raceClassNumeric</t>
+  </si>
+  <si>
+    <t>favourite</t>
+  </si>
+  <si>
+    <t>prize</t>
+  </si>
+  <si>
+    <t>jockey</t>
+  </si>
+  <si>
+    <t>raceName</t>
+  </si>
+  <si>
+    <t>hType</t>
+  </si>
+  <si>
+    <t>Rank_Track_2</t>
+  </si>
+  <si>
+    <t>jockeyClaim</t>
+  </si>
+  <si>
+    <t>ZERO</t>
+  </si>
+  <si>
+    <t>between 11 and 17</t>
+  </si>
+  <si>
+    <t>between 60 and 70</t>
+  </si>
+  <si>
+    <t>ageLimit</t>
+  </si>
+  <si>
+    <t>m, f</t>
+  </si>
+  <si>
+    <t>g, c</t>
+  </si>
+  <si>
+    <t>between -3 and 1</t>
+  </si>
+  <si>
+    <t>CD_Overall</t>
+  </si>
+  <si>
+    <t>CurrentSeason</t>
+  </si>
+  <si>
+    <t>not like '%amateur%'</t>
+  </si>
+  <si>
+    <t>like '%Apprentice%'</t>
+  </si>
+  <si>
+    <t>not like '%Apprentice%'</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>&gt;=1</t>
+  </si>
+  <si>
+    <t>is null</t>
+  </si>
+  <si>
+    <t>between 3 and 4</t>
+  </si>
+  <si>
+    <t>Sys294</t>
+  </si>
+  <si>
+    <t>David Allan</t>
+  </si>
+  <si>
+    <t>Thirsk</t>
+  </si>
+  <si>
+    <t>Sys230</t>
+  </si>
+  <si>
+    <t>Sys272</t>
+  </si>
+  <si>
+    <t>Sys287_Sep</t>
+  </si>
+  <si>
+    <t>Sys288_Sep</t>
+  </si>
+  <si>
+    <t>Sys289_Sep</t>
+  </si>
+  <si>
+    <t>Sys290_Sep</t>
+  </si>
+  <si>
+    <t>Sys291_Sep</t>
+  </si>
+  <si>
+    <t>Sys292_Sep</t>
+  </si>
+  <si>
+    <t>Sys293_Sep</t>
+  </si>
+  <si>
+    <t>overall_ftc</t>
+  </si>
+  <si>
+    <t>track_cnt</t>
+  </si>
+  <si>
+    <t>overall_minor</t>
+  </si>
+  <si>
+    <t>Proj_PRB2_Track_Overall</t>
+  </si>
+  <si>
     <t>AVGPRB2_overall</t>
-  </si>
-  <si>
-    <t>&lt;10000</t>
-  </si>
-  <si>
-    <t>Archie Watson</t>
-  </si>
-  <si>
-    <t>Hollie Doyle</t>
-  </si>
-  <si>
-    <t>3yo+</t>
-  </si>
-  <si>
-    <t>Rossa Ryan</t>
-  </si>
-  <si>
-    <t>Eve Johnson Houghton</t>
-  </si>
-  <si>
-    <t>&gt;45</t>
-  </si>
-  <si>
-    <t>Gillian Boanas</t>
-  </si>
-  <si>
-    <t>Rod Millman</t>
-  </si>
-  <si>
-    <t>&gt;70</t>
-  </si>
-  <si>
-    <t>&gt;5</t>
-  </si>
-  <si>
-    <t>&lt;1400</t>
-  </si>
-  <si>
-    <t>&lt;1700</t>
-  </si>
-  <si>
-    <t>&gt;57</t>
-  </si>
-  <si>
-    <t>&gt;3</t>
-  </si>
-  <si>
-    <t>&gt;=25</t>
-  </si>
-  <si>
-    <t>Declan Carroll</t>
-  </si>
-  <si>
-    <t>AVGPRB2_Track_Proj</t>
-  </si>
-  <si>
-    <t>Ayr, Redcar, Yarmouth, Doncaster, Ffos Las, Nottingham, Haydock, Newbury, Wetherby</t>
-  </si>
-  <si>
-    <t>Chris Wall</t>
-  </si>
-  <si>
-    <t>Christopher Mason</t>
-  </si>
-  <si>
-    <t>Chepstow</t>
-  </si>
-  <si>
-    <t>Chepstow, Brighton</t>
-  </si>
-  <si>
-    <t>Clive Cox</t>
-  </si>
-  <si>
-    <t>Chepstow, Epsom, Brighton</t>
-  </si>
-  <si>
-    <t>Chepstow, Epsom</t>
-  </si>
-  <si>
-    <t>Beverley, Carlisle</t>
-  </si>
-  <si>
-    <t>Edward Bethell</t>
-  </si>
-  <si>
-    <t>Ismail Mohammed</t>
-  </si>
-  <si>
-    <t>John Butler</t>
-  </si>
-  <si>
-    <t>Rae Guest</t>
-  </si>
-  <si>
-    <t>Bath</t>
-  </si>
-  <si>
-    <t>Yarmouth</t>
-  </si>
-  <si>
-    <t>&lt;=1</t>
-  </si>
-  <si>
-    <t>K R Burke</t>
-  </si>
-  <si>
-    <t>Richard Fahey</t>
-  </si>
-  <si>
-    <t>&gt;2000</t>
-  </si>
-  <si>
-    <t>Jim Goldie</t>
-  </si>
-  <si>
-    <t>Catterick</t>
-  </si>
-  <si>
-    <t>Keith Dalgleish</t>
-  </si>
-  <si>
-    <t>Newmarket (July)</t>
-  </si>
-  <si>
-    <t>Saeed bin Suroor</t>
-  </si>
-  <si>
-    <t>William Buick</t>
-  </si>
-  <si>
-    <t>John &amp; Thady Gosden, John Gosden</t>
-  </si>
-  <si>
-    <t>Robert Havlin</t>
-  </si>
-  <si>
-    <t>Goodwood, Newbury</t>
-  </si>
-  <si>
-    <t>William Haggas</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>Newmarket</t>
-  </si>
-  <si>
-    <t>Gary Moore</t>
-  </si>
-  <si>
-    <t>&lt;20</t>
-  </si>
-  <si>
-    <t>Ivan Furtado</t>
-  </si>
-  <si>
-    <t>c, f</t>
-  </si>
-  <si>
-    <t>&lt;2</t>
-  </si>
-  <si>
-    <t>Oisin Murphy</t>
-  </si>
-  <si>
-    <t>Adam Farragher</t>
-  </si>
-  <si>
-    <t>Ian Williams</t>
-  </si>
-  <si>
-    <t>James Ferguson</t>
-  </si>
-  <si>
-    <t>&lt;60</t>
-  </si>
-  <si>
-    <t>Mrs John Harrington</t>
-  </si>
-  <si>
-    <t>&gt;10</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>between 1051 and 1449</t>
-  </si>
-  <si>
-    <t>Simon &amp; Ed Crisford</t>
-  </si>
-  <si>
-    <t>between 2151 and 2249</t>
-  </si>
-  <si>
-    <t>Grant Tuer</t>
-  </si>
-  <si>
-    <t>&gt;=3</t>
-  </si>
-  <si>
-    <t>Hugo Palmer</t>
-  </si>
-  <si>
-    <t>&lt;8</t>
-  </si>
-  <si>
-    <t>James Fanshawe</t>
-  </si>
-  <si>
-    <t>between 8 and 13</t>
-  </si>
-  <si>
-    <t>Beverley, Hamilton, Carlisle</t>
-  </si>
-  <si>
-    <t>Redcar, Ayr, Yarmouth, York, Doncaster, Ffos Las, Nottingham, Haydock, Newbury, Wetherby</t>
-  </si>
-  <si>
-    <t>Ollie Pears</t>
-  </si>
-  <si>
-    <t>Julie Camacho</t>
-  </si>
-  <si>
-    <t>&lt; -10</t>
-  </si>
-  <si>
-    <t>between 14 and 29</t>
-  </si>
-  <si>
-    <t>Newmarket, Newmarket (July)</t>
-  </si>
-  <si>
-    <t>Rank_overall</t>
-  </si>
-  <si>
-    <t>&lt;=2</t>
-  </si>
-  <si>
-    <t>AVGPRB2_overall_Proj</t>
-  </si>
-  <si>
-    <t>Steph Hollinshead</t>
-  </si>
-  <si>
-    <t>Julia Feilden</t>
-  </si>
-  <si>
-    <t>&lt;21</t>
-  </si>
-  <si>
-    <t>Michael Appleby</t>
-  </si>
-  <si>
-    <t>between 6 and 9</t>
-  </si>
-  <si>
-    <t>Beverley, Carlisle, Pontefract</t>
-  </si>
-  <si>
-    <t>Paul Midgley</t>
-  </si>
-  <si>
-    <t>&gt;20</t>
-  </si>
-  <si>
-    <t>&lt;1</t>
-  </si>
-  <si>
-    <t>between -3 and -1</t>
-  </si>
-  <si>
-    <t>Charlie Johnston</t>
-  </si>
-  <si>
-    <t>Tom Clover</t>
-  </si>
-  <si>
-    <t>Sys102</t>
-  </si>
-  <si>
-    <t>Sys103</t>
-  </si>
-  <si>
-    <t>Sys104</t>
-  </si>
-  <si>
-    <t>Sys105</t>
-  </si>
-  <si>
-    <t>Sys106</t>
-  </si>
-  <si>
-    <t>Sys107</t>
-  </si>
-  <si>
-    <t>4yo+</t>
-  </si>
-  <si>
-    <t>&lt;3</t>
-  </si>
-  <si>
-    <t>&gt;2</t>
-  </si>
-  <si>
-    <t>&lt;=3</t>
-  </si>
-  <si>
-    <t>David Evans</t>
-  </si>
-  <si>
-    <t>Bryan Smart</t>
-  </si>
-  <si>
-    <t>AVGPRB2_Track</t>
-  </si>
-  <si>
-    <t>Ed Dunlop</t>
-  </si>
-  <si>
-    <t>&lt;30</t>
-  </si>
-  <si>
-    <t>Sir Mark Prescott Bt</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>Graham Lee</t>
-  </si>
-  <si>
-    <t>between 1 and 2</t>
-  </si>
-  <si>
-    <t>Jonathan Portman</t>
-  </si>
-  <si>
-    <t>Marco Botti</t>
-  </si>
-  <si>
-    <t>David Simcock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;10 </t>
-  </si>
-  <si>
-    <t>Dianne Sayer</t>
-  </si>
-  <si>
-    <t>Brian Ellison</t>
-  </si>
-  <si>
-    <t>between 2 and 3</t>
-  </si>
-  <si>
-    <t>between 1 and 3</t>
-  </si>
-  <si>
-    <t>ABS_DD</t>
-  </si>
-  <si>
-    <t>[OR_Limit-OR]</t>
-  </si>
-  <si>
-    <t>p, p1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>in (66.67, 100)</t>
-  </si>
-  <si>
-    <t>in (50, 100)</t>
-  </si>
-  <si>
-    <t>Beverley</t>
-  </si>
-  <si>
-    <t>&gt;=1760</t>
-  </si>
-  <si>
-    <t>Rank_overall_1</t>
-  </si>
-  <si>
-    <t>between 8 and 9</t>
-  </si>
-  <si>
-    <t>[OR]</t>
-  </si>
-  <si>
-    <t>between 5 and 6</t>
-  </si>
-  <si>
-    <t>&lt;-40</t>
-  </si>
-  <si>
-    <t>&lt;-1</t>
-  </si>
-  <si>
-    <t>Sys109</t>
-  </si>
-  <si>
-    <t>Sys111</t>
-  </si>
-  <si>
-    <t>Sys112</t>
-  </si>
-  <si>
-    <t>Goodwood</t>
-  </si>
-  <si>
-    <t>&lt;14</t>
-  </si>
-  <si>
-    <t>&lt;=4</t>
-  </si>
-  <si>
-    <t>Sys114</t>
-  </si>
-  <si>
-    <t>Jack Mitchell</t>
-  </si>
-  <si>
-    <t>Sys115</t>
-  </si>
-  <si>
-    <t>Ed Walker</t>
-  </si>
-  <si>
-    <t>Ascot</t>
-  </si>
-  <si>
-    <t>Sys116</t>
-  </si>
-  <si>
-    <t>Harry Eustace</t>
-  </si>
-  <si>
-    <t>Sys117</t>
-  </si>
-  <si>
-    <t>Sys118</t>
-  </si>
-  <si>
-    <t>Sys120</t>
-  </si>
-  <si>
-    <t>Milton Harris</t>
-  </si>
-  <si>
-    <t>Sys121</t>
-  </si>
-  <si>
-    <t>Miss Natalia Lupini</t>
-  </si>
-  <si>
-    <t>M C Grassick</t>
-  </si>
-  <si>
-    <t>Sys123</t>
-  </si>
-  <si>
-    <t>Sys124</t>
-  </si>
-  <si>
-    <t>Ruth Carr</t>
-  </si>
-  <si>
-    <t>James Sullivan</t>
-  </si>
-  <si>
-    <t>Thomas Gibney</t>
-  </si>
-  <si>
-    <t>Sys126</t>
-  </si>
-  <si>
-    <t>Timothy Doyle</t>
-  </si>
-  <si>
-    <t>Sys127</t>
-  </si>
-  <si>
-    <t>Sys129</t>
-  </si>
-  <si>
-    <t>Sys130</t>
-  </si>
-  <si>
-    <t>Sys131</t>
-  </si>
-  <si>
-    <t>&lt;15</t>
-  </si>
-  <si>
-    <t>Sys133</t>
-  </si>
-  <si>
-    <t>Sys134</t>
-  </si>
-  <si>
-    <t>blanks</t>
-  </si>
-  <si>
-    <t>Patrick Chamings</t>
-  </si>
-  <si>
-    <t>Sys135</t>
-  </si>
-  <si>
-    <t>Sys136</t>
-  </si>
-  <si>
-    <t>Sys137</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Sys138</t>
-  </si>
-  <si>
-    <t>Sys139</t>
-  </si>
-  <si>
-    <t>Denis Gerard Hogan</t>
-  </si>
-  <si>
-    <t>&lt;12</t>
-  </si>
-  <si>
-    <t>&gt;1</t>
-  </si>
-  <si>
-    <t>Class_rating_1</t>
-  </si>
-  <si>
-    <t>Rank_Class_1</t>
-  </si>
-  <si>
-    <t>Class_rating_2</t>
-  </si>
-  <si>
-    <t>Rank_Class_2</t>
-  </si>
-  <si>
-    <t>Class_rating_3</t>
-  </si>
-  <si>
-    <t>Rank_Class_3</t>
-  </si>
-  <si>
-    <t>Rank_SFOR_M</t>
-  </si>
-  <si>
-    <t>Rank_SF_M</t>
-  </si>
-  <si>
-    <t>Trainer_change</t>
-  </si>
-  <si>
-    <t>Sys142</t>
-  </si>
-  <si>
-    <t>&gt;6</t>
-  </si>
-  <si>
-    <t>Sys144</t>
-  </si>
-  <si>
-    <t>Blanks or 100</t>
-  </si>
-  <si>
-    <t>Sys145</t>
-  </si>
-  <si>
-    <t>George Boughey</t>
-  </si>
-  <si>
-    <t>&gt;200</t>
-  </si>
-  <si>
-    <t>Sys147</t>
-  </si>
-  <si>
-    <t>Sys149</t>
-  </si>
-  <si>
-    <t>Sys150</t>
-  </si>
-  <si>
-    <t>Sys151</t>
-  </si>
-  <si>
-    <t>Sys152</t>
-  </si>
-  <si>
-    <t>Sys153</t>
-  </si>
-  <si>
-    <t>Sys154</t>
-  </si>
-  <si>
-    <t>Sys155</t>
-  </si>
-  <si>
-    <t>Sys156</t>
-  </si>
-  <si>
-    <t>Sys157</t>
-  </si>
-  <si>
-    <t>Chris Dwyer</t>
-  </si>
-  <si>
-    <t>Sys158</t>
-  </si>
-  <si>
-    <t>Sys161</t>
-  </si>
-  <si>
-    <t>Pam Sly</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Tristan Davidson</t>
-  </si>
-  <si>
-    <t>Sys162</t>
-  </si>
-  <si>
-    <t>Sys163</t>
-  </si>
-  <si>
-    <t>Sys164</t>
-  </si>
-  <si>
-    <t>Chester</t>
-  </si>
-  <si>
-    <t>&lt;1500</t>
-  </si>
-  <si>
-    <t>Sys165</t>
-  </si>
-  <si>
-    <t>&lt;= 3</t>
-  </si>
-  <si>
-    <t>Sys166</t>
-  </si>
-  <si>
-    <t>&lt;70</t>
-  </si>
-  <si>
-    <t>between 0 and -10</t>
-  </si>
-  <si>
-    <t>&lt;100</t>
-  </si>
-  <si>
-    <t>&lt;90</t>
-  </si>
-  <si>
-    <t>Rank_Track_1</t>
-  </si>
-  <si>
-    <t>Sys167</t>
-  </si>
-  <si>
-    <t>Sys168</t>
-  </si>
-  <si>
-    <t>Sys169</t>
-  </si>
-  <si>
-    <t>Sys170</t>
-  </si>
-  <si>
-    <t>Sys171</t>
-  </si>
-  <si>
-    <t>Josephine Gordon</t>
-  </si>
-  <si>
-    <t>Sys172</t>
-  </si>
-  <si>
-    <t>Saffie Osborne</t>
-  </si>
-  <si>
-    <t>Sys173</t>
-  </si>
-  <si>
-    <t>Sys174</t>
-  </si>
-  <si>
-    <t>Sys175</t>
-  </si>
-  <si>
-    <t>Sys177</t>
-  </si>
-  <si>
-    <t>Ben Curtis</t>
-  </si>
-  <si>
-    <t>&gt;135</t>
-  </si>
-  <si>
-    <t>Sys178</t>
-  </si>
-  <si>
-    <t>Phil Dennis</t>
-  </si>
-  <si>
-    <t>Sys179</t>
-  </si>
-  <si>
-    <t>Oisin Orr</t>
-  </si>
-  <si>
-    <t>&gt;4</t>
-  </si>
-  <si>
-    <t>Sys180</t>
-  </si>
-  <si>
-    <t>Clifford Lee</t>
-  </si>
-  <si>
-    <t>Hamilton, Carlisle, Beverley</t>
-  </si>
-  <si>
-    <t>Sys182</t>
-  </si>
-  <si>
-    <t>Paul Hanagan</t>
-  </si>
-  <si>
-    <t>Sys183</t>
-  </si>
-  <si>
-    <t>Sys186</t>
-  </si>
-  <si>
-    <t>Sys187</t>
-  </si>
-  <si>
-    <t>Sys188</t>
-  </si>
-  <si>
-    <t>&gt;2400</t>
-  </si>
-  <si>
-    <t>Fergal OBrien</t>
-  </si>
-  <si>
-    <t>Peter Fahey</t>
-  </si>
-  <si>
-    <t>Sys189</t>
-  </si>
-  <si>
-    <t>Sys191</t>
-  </si>
-  <si>
-    <t>Michael Bell</t>
-  </si>
-  <si>
-    <t>Sys192</t>
-  </si>
-  <si>
-    <t>Charles Hills</t>
-  </si>
-  <si>
-    <t>&gt;130</t>
-  </si>
-  <si>
-    <t>Sys193</t>
-  </si>
-  <si>
-    <t>Tom Marquand</t>
-  </si>
-  <si>
-    <t>&lt;2.5</t>
-  </si>
-  <si>
-    <t>Tim Easterby</t>
-  </si>
-  <si>
-    <t>Roger Fell &amp; Sean Murray, Roger Fell</t>
-  </si>
-  <si>
-    <t>Sys198</t>
-  </si>
-  <si>
-    <t>Sys199</t>
-  </si>
-  <si>
-    <t>&lt;=75</t>
-  </si>
-  <si>
-    <t>Sys200</t>
-  </si>
-  <si>
-    <t>Sys201</t>
-  </si>
-  <si>
-    <t>David Menuisier</t>
-  </si>
-  <si>
-    <t>Sys202</t>
-  </si>
-  <si>
-    <t>Robert Cowell</t>
-  </si>
-  <si>
-    <t>Sys203</t>
-  </si>
-  <si>
-    <t>Sys204</t>
-  </si>
-  <si>
-    <t>Sys205</t>
-  </si>
-  <si>
-    <t>Sys206</t>
-  </si>
-  <si>
-    <t>Sys207</t>
-  </si>
-  <si>
-    <t>Sys208</t>
-  </si>
-  <si>
-    <t>Sys209</t>
-  </si>
-  <si>
-    <t>Sys210</t>
-  </si>
-  <si>
-    <t>Harrison Shaw</t>
-  </si>
-  <si>
-    <t>Sys211</t>
-  </si>
-  <si>
-    <t>Paul Mulrennan</t>
-  </si>
-  <si>
-    <t>Sys212</t>
-  </si>
-  <si>
-    <t>Musselburgh</t>
-  </si>
-  <si>
-    <t>Sys213</t>
-  </si>
-  <si>
-    <t>&lt;=0.25</t>
-  </si>
-  <si>
-    <t>Sys214</t>
-  </si>
-  <si>
-    <t>Sys215</t>
-  </si>
-  <si>
-    <t>Sys216</t>
-  </si>
-  <si>
-    <t>Richard Spencer</t>
-  </si>
-  <si>
-    <t>Last_Race_Name</t>
-  </si>
-  <si>
-    <t>Sys217</t>
-  </si>
-  <si>
-    <t>Sys219</t>
-  </si>
-  <si>
-    <t>Sys220</t>
-  </si>
-  <si>
-    <t>Sys221</t>
-  </si>
-  <si>
-    <t>Sys222</t>
-  </si>
-  <si>
-    <t>B F Brookhouse</t>
-  </si>
-  <si>
-    <t>Nottingham</t>
-  </si>
-  <si>
-    <t>Nigel Tinkler</t>
-  </si>
-  <si>
-    <t>Sys223</t>
-  </si>
-  <si>
-    <t>Sys224</t>
-  </si>
-  <si>
-    <t>Sys225</t>
-  </si>
-  <si>
-    <t>Sys226</t>
-  </si>
-  <si>
-    <t>Sys227</t>
-  </si>
-  <si>
-    <t>Sys228</t>
-  </si>
-  <si>
-    <t>Sys229</t>
-  </si>
-  <si>
-    <t>David Probert</t>
-  </si>
-  <si>
-    <t>Connor Beasley</t>
-  </si>
-  <si>
-    <t>Sys231</t>
-  </si>
-  <si>
-    <t>J P Murtagh</t>
-  </si>
-  <si>
-    <t>Sys232</t>
-  </si>
-  <si>
-    <t>Rank_Age</t>
-  </si>
-  <si>
-    <t>Sys233</t>
-  </si>
-  <si>
-    <t>Sys235</t>
-  </si>
-  <si>
-    <t>Sys238</t>
-  </si>
-  <si>
-    <t>MinimalOR</t>
-  </si>
-  <si>
-    <t>Sys239</t>
-  </si>
-  <si>
-    <t>Sys241</t>
-  </si>
-  <si>
-    <t>Sys242</t>
-  </si>
-  <si>
-    <t>Sys243</t>
-  </si>
-  <si>
-    <t>Sys245</t>
-  </si>
-  <si>
-    <t>Rank_OR_desc</t>
-  </si>
-  <si>
-    <t>Chelsea Banham</t>
-  </si>
-  <si>
-    <t>Joey Haynes</t>
-  </si>
-  <si>
-    <t>Sys246</t>
-  </si>
-  <si>
-    <t>Sys247</t>
-  </si>
-  <si>
-    <t>George Baker</t>
-  </si>
-  <si>
-    <t>Sys248</t>
-  </si>
-  <si>
-    <t>Sys249</t>
-  </si>
-  <si>
-    <t>Sys250</t>
-  </si>
-  <si>
-    <t>Sys251</t>
-  </si>
-  <si>
-    <t>Sys253</t>
-  </si>
-  <si>
-    <t>Sys254</t>
-  </si>
-  <si>
-    <t>Sys255</t>
-  </si>
-  <si>
-    <t>Sys256</t>
-  </si>
-  <si>
-    <t>Simon Hodgson</t>
-  </si>
-  <si>
-    <t>Sys257</t>
-  </si>
-  <si>
-    <t>Sys259</t>
-  </si>
-  <si>
-    <t>Sys260</t>
-  </si>
-  <si>
-    <t>Sys261</t>
-  </si>
-  <si>
-    <t>Sys263</t>
-  </si>
-  <si>
-    <t>Sys264</t>
-  </si>
-  <si>
-    <t>A J Martin</t>
-  </si>
-  <si>
-    <t>Ben Coen</t>
-  </si>
-  <si>
-    <t>David &amp; Nicola Barron</t>
-  </si>
-  <si>
-    <t>Sys265</t>
-  </si>
-  <si>
-    <t>Sys266</t>
-  </si>
-  <si>
-    <t>David Loughnane</t>
-  </si>
-  <si>
-    <t>Laura Pearson</t>
-  </si>
-  <si>
-    <t>Sys267</t>
-  </si>
-  <si>
-    <t>Jarlath P Fahey</t>
-  </si>
-  <si>
-    <t>Leigh Roche</t>
-  </si>
-  <si>
-    <t>Sys268</t>
-  </si>
-  <si>
-    <t>Sys269</t>
-  </si>
-  <si>
-    <t>Sys270</t>
-  </si>
-  <si>
-    <t>Sys273</t>
-  </si>
-  <si>
-    <t>Sys274</t>
-  </si>
-  <si>
-    <t>W McCreery</t>
-  </si>
-  <si>
-    <t>Nathan Crosse</t>
-  </si>
-  <si>
-    <t>Sys275</t>
-  </si>
-  <si>
-    <t>Sys276</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Musselburgh</t>
-  </si>
-  <si>
-    <t>Rowan Scott</t>
-  </si>
-  <si>
-    <t>Sys277</t>
-  </si>
-  <si>
-    <t>Simon Whitaker</t>
-  </si>
-  <si>
-    <t>Sys278</t>
-  </si>
-  <si>
-    <t>Iain Jardine</t>
-  </si>
-  <si>
-    <t>Sys279</t>
-  </si>
-  <si>
-    <t>Sys280</t>
-  </si>
-  <si>
-    <t>Sys281</t>
-  </si>
-  <si>
-    <t>Sys282</t>
-  </si>
-  <si>
-    <t>Sys284</t>
-  </si>
-  <si>
-    <t>Sys285</t>
-  </si>
-  <si>
-    <t>Sys286</t>
-  </si>
-  <si>
-    <t>trainer</t>
-  </si>
-  <si>
-    <t>ORLimitNumeric</t>
-  </si>
-  <si>
-    <t>noOfRunners</t>
-  </si>
-  <si>
-    <t>track</t>
-  </si>
-  <si>
-    <t>raceClassNumeric</t>
-  </si>
-  <si>
-    <t>favourite</t>
-  </si>
-  <si>
-    <t>prize</t>
-  </si>
-  <si>
-    <t>jockey</t>
-  </si>
-  <si>
-    <t>raceName</t>
-  </si>
-  <si>
-    <t>hType</t>
-  </si>
-  <si>
-    <t>Rank_Track_2</t>
-  </si>
-  <si>
-    <t>FTC</t>
-  </si>
-  <si>
-    <t>jockeyClaim</t>
-  </si>
-  <si>
-    <t>ZERO</t>
-  </si>
-  <si>
-    <t>between 11 and 17</t>
-  </si>
-  <si>
-    <t>between 60 and 70</t>
-  </si>
-  <si>
-    <t>ageLimit</t>
-  </si>
-  <si>
-    <t>m, f</t>
-  </si>
-  <si>
-    <t>g, c</t>
-  </si>
-  <si>
-    <t>between -3 and 1</t>
-  </si>
-  <si>
-    <t>CD_Overall</t>
-  </si>
-  <si>
-    <t>TrackCNT</t>
-  </si>
-  <si>
-    <t>CurrentSeason</t>
-  </si>
-  <si>
-    <t>not like '%amateur%'</t>
-  </si>
-  <si>
-    <t>like '%Apprentice%'</t>
-  </si>
-  <si>
-    <t>not like '%Apprentice%'</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>&gt;=1</t>
-  </si>
-  <si>
-    <t>is null</t>
-  </si>
-  <si>
-    <t>between 3 and 4</t>
-  </si>
-  <si>
-    <t>Sys294</t>
-  </si>
-  <si>
-    <t>David Allan</t>
-  </si>
-  <si>
-    <t>Thirsk</t>
-  </si>
-  <si>
-    <t>Sys230</t>
-  </si>
-  <si>
-    <t>Sys272</t>
-  </si>
-  <si>
-    <t>Sys287_Sep</t>
-  </si>
-  <si>
-    <t>Sys288_Sep</t>
-  </si>
-  <si>
-    <t>Sys289_Sep</t>
-  </si>
-  <si>
-    <t>Sys290_Sep</t>
-  </si>
-  <si>
-    <t>Sys291_Sep</t>
-  </si>
-  <si>
-    <t>Sys292_Sep</t>
-  </si>
-  <si>
-    <t>Sys293_Sep</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
@@ -2176,28 +2176,28 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>512</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>515</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>7</v>
@@ -2206,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="W1" s="5" t="s">
         <v>10</v>
@@ -2221,103 +2221,103 @@
         <v>11</v>
       </c>
       <c r="Y1" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>521</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>149</v>
+        <v>549</v>
       </c>
       <c r="AH1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AJ1" s="5" t="s">
         <v>14</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AL1" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AO1" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AT1" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="AS1" s="5" t="s">
+      <c r="AU1" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="AV1" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="AU1" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AX1" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="AY1" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="AZ1" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="BA1" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="BB1" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="BC1" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="BD1" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="BE1" s="5" t="s">
         <v>317</v>
-      </c>
-      <c r="AW1" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="AX1" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="AY1" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="AZ1" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="BA1" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="BB1" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="BC1" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="BD1" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="BE1" s="5" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
@@ -2351,28 +2351,28 @@
         <v>107</v>
       </c>
       <c r="G3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="X3" t="s">
         <v>115</v>
       </c>
       <c r="Z3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AX3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AY3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
         <v>108</v>
       </c>
       <c r="H4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -2395,10 +2395,10 @@
         <v>107</v>
       </c>
       <c r="AU4" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AY4" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
         <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -2441,22 +2441,22 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="X6" t="s">
         <v>130</v>
       </c>
       <c r="AA6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AV6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AY6" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
@@ -2496,13 +2496,13 @@
         <v>113</v>
       </c>
       <c r="R8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AU8" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AY8" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
@@ -2513,7 +2513,7 @@
         <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E9" t="s">
         <v>120</v>
@@ -2542,10 +2542,10 @@
         <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O10" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -2559,22 +2559,22 @@
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O11" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="V11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
@@ -2588,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G12" t="s">
         <v>124</v>
@@ -2600,7 +2600,7 @@
         <v>124</v>
       </c>
       <c r="AU12" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
@@ -2614,13 +2614,13 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G13" t="s">
         <v>124</v>
       </c>
       <c r="R13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="X13" t="s">
         <v>124</v>
@@ -2640,7 +2640,7 @@
         <v>124</v>
       </c>
       <c r="R14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="W14">
         <v>3</v>
@@ -2652,7 +2652,7 @@
         <v>126</v>
       </c>
       <c r="AA14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
@@ -2663,7 +2663,7 @@
         <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G15" t="s">
         <v>124</v>
@@ -2672,10 +2672,10 @@
         <v>130</v>
       </c>
       <c r="Z15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AA15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
@@ -2683,7 +2683,7 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
         <v>117</v>
@@ -2695,16 +2695,16 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X16" t="s">
         <v>130</v>
       </c>
       <c r="AA16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
@@ -2718,16 +2718,16 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O17" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="T17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W17">
         <v>3</v>
@@ -2738,19 +2738,19 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" t="s">
         <v>137</v>
-      </c>
-      <c r="D18" t="s">
-        <v>251</v>
-      </c>
-      <c r="E18" t="s">
-        <v>138</v>
       </c>
       <c r="X18" t="s">
         <v>130</v>
       </c>
       <c r="AE18" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
@@ -2758,13 +2758,13 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X19" t="s">
         <v>130</v>
@@ -2775,13 +2775,13 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="O20" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
@@ -2795,13 +2795,13 @@
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF21" t="s">
         <v>141</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
@@ -2815,19 +2815,19 @@
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S22">
         <v>1</v>
       </c>
       <c r="U22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AF22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2835,7 +2835,7 @@
         <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>105</v>
@@ -2844,28 +2844,28 @@
         <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N23" s="3">
         <v>6</v>
       </c>
       <c r="O23" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AF23" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="U23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z23" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="AF23" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="AY23" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="24" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2873,17 +2873,17 @@
         <v>37</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="V24" s="2" t="s">
         <v>116</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.25">
@@ -2891,10 +2891,10 @@
         <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="V25">
         <v>1</v>
@@ -2906,7 +2906,7 @@
         <v>100</v>
       </c>
       <c r="AM25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:51" ht="60" x14ac:dyDescent="0.25">
@@ -2914,22 +2914,22 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O26" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="V26">
         <v>1</v>
       </c>
       <c r="AH26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AJ26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:51" ht="60" x14ac:dyDescent="0.25">
@@ -2940,16 +2940,16 @@
         <v>110</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O27" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="V27">
         <v>1</v>
       </c>
       <c r="AH27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AM27">
         <v>1</v>
@@ -2960,13 +2960,13 @@
         <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O28" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2974,13 +2974,13 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O29" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
@@ -2988,16 +2988,16 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O30" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AY30" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
@@ -3011,10 +3011,10 @@
         <v>115</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O31" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.25">
@@ -3022,13 +3022,13 @@
         <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O32" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="33" spans="1:35" ht="60" x14ac:dyDescent="0.25">
@@ -3036,13 +3036,13 @@
         <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O33" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="34" spans="1:35" ht="60" x14ac:dyDescent="0.25">
@@ -3050,13 +3050,13 @@
         <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O34" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="35" spans="1:35" ht="60" x14ac:dyDescent="0.25">
@@ -3064,13 +3064,13 @@
         <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O35" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
@@ -3081,10 +3081,10 @@
         <v>111</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O36" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.25">
@@ -3095,13 +3095,13 @@
         <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O37" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
@@ -3109,17 +3109,17 @@
         <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C38" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="M38" s="1"/>
       <c r="O38" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.25">
@@ -3134,13 +3134,13 @@
       </c>
       <c r="M39" s="1"/>
       <c r="O39" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V39" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.25">
@@ -3148,17 +3148,17 @@
         <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="M40" s="1"/>
       <c r="O40" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.25">
@@ -3173,13 +3173,13 @@
       </c>
       <c r="M41" s="1"/>
       <c r="O41" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.25">
@@ -3187,16 +3187,16 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O42" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.25">
@@ -3204,16 +3204,16 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O43" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.25">
@@ -3224,10 +3224,10 @@
         <v>106</v>
       </c>
       <c r="M44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="T44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V44">
         <v>1</v>
@@ -3238,16 +3238,16 @@
         <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O45" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
@@ -3255,16 +3255,16 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M46" t="s">
+        <v>175</v>
+      </c>
+      <c r="O46" t="s">
+        <v>530</v>
+      </c>
+      <c r="AI46" t="s">
         <v>177</v>
-      </c>
-      <c r="O46" t="s">
-        <v>535</v>
-      </c>
-      <c r="AI46" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
@@ -3275,10 +3275,10 @@
         <v>106</v>
       </c>
       <c r="M47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="T47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V47">
         <v>1</v>
@@ -3289,13 +3289,13 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O48" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Z48" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
@@ -3303,13 +3303,13 @@
         <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O49" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Z49" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
@@ -3320,13 +3320,13 @@
         <v>110</v>
       </c>
       <c r="O50" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
@@ -3334,16 +3334,16 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="T51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X51" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AI51" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
@@ -3351,13 +3351,13 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O52" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T52" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
@@ -3365,13 +3365,13 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
         <v>120</v>
       </c>
       <c r="O53" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
@@ -3379,13 +3379,13 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O54" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
@@ -3393,16 +3393,16 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" t="s">
+        <v>190</v>
+      </c>
+      <c r="O55" t="s">
+        <v>530</v>
+      </c>
+      <c r="AI55" t="s">
         <v>191</v>
-      </c>
-      <c r="F55" t="s">
-        <v>192</v>
-      </c>
-      <c r="O55" t="s">
-        <v>535</v>
-      </c>
-      <c r="AI55" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
@@ -3410,16 +3410,16 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C56" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="O56" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U56" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
@@ -3427,16 +3427,16 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U57" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
@@ -3444,7 +3444,7 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -3456,7 +3456,7 @@
         <v>120</v>
       </c>
       <c r="AF58" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
@@ -3464,7 +3464,7 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3476,7 +3476,7 @@
         <v>130</v>
       </c>
       <c r="AF59" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
@@ -3484,7 +3484,7 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>120</v>
       </c>
       <c r="AF60" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
@@ -3507,7 +3507,7 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3516,13 +3516,13 @@
         <v>112</v>
       </c>
       <c r="M61" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="X61" t="s">
         <v>130</v>
       </c>
       <c r="AF61" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:35" ht="60" x14ac:dyDescent="0.25">
@@ -3536,13 +3536,13 @@
         <v>112</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AF62" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
@@ -3550,16 +3550,16 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D63" t="s">
         <v>105</v>
       </c>
       <c r="G63" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X63" t="s">
         <v>115</v>
@@ -3570,16 +3570,16 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G64" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="X64" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" spans="1:37" x14ac:dyDescent="0.25">
@@ -3590,13 +3590,13 @@
         <v>121</v>
       </c>
       <c r="E65" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F65" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O65" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="66" spans="1:37" x14ac:dyDescent="0.25">
@@ -3604,13 +3604,13 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M66" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O66" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Z66" t="s">
         <v>107</v>
@@ -3621,13 +3621,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O67" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Z67" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AB67" t="s">
         <v>107</v>
@@ -3638,7 +3638,7 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="X68" t="s">
         <v>120</v>
@@ -3652,7 +3652,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="X69" t="s">
         <v>115</v>
@@ -3661,7 +3661,7 @@
         <v>100</v>
       </c>
       <c r="AI69" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:37" x14ac:dyDescent="0.25">
@@ -3669,10 +3669,10 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E70" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="X70" t="s">
         <v>120</v>
@@ -3686,10 +3686,10 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E71" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="X71" t="s">
         <v>120</v>
@@ -3703,16 +3703,16 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C72" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N72" s="1">
         <v>6</v>
       </c>
       <c r="O72" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="73" spans="1:37" x14ac:dyDescent="0.25">
@@ -3720,22 +3720,22 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73" t="s">
+        <v>218</v>
+      </c>
+      <c r="D73" t="s">
         <v>219</v>
       </c>
-      <c r="C73" t="s">
-        <v>220</v>
-      </c>
-      <c r="D73" t="s">
-        <v>221</v>
-      </c>
       <c r="M73" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O73" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Z73" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:37" x14ac:dyDescent="0.25">
@@ -3746,13 +3746,13 @@
         <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="X74" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AK74" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:37" x14ac:dyDescent="0.25">
@@ -3760,16 +3760,16 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D75" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="X75" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AK75" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" spans="1:37" x14ac:dyDescent="0.25">
@@ -3777,16 +3777,16 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="X76" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AK76" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="77" spans="1:37" x14ac:dyDescent="0.25">
@@ -3794,16 +3794,16 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G77" t="s">
         <v>124</v>
       </c>
       <c r="X77" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AK77" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:37" x14ac:dyDescent="0.25">
@@ -3811,13 +3811,13 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D78" t="s">
         <v>116</v>
       </c>
       <c r="X78" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AK78" t="s">
         <v>105</v>
@@ -3840,7 +3840,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" spans="1:37" x14ac:dyDescent="0.25">
@@ -3848,10 +3848,10 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="X80" t="s">
         <v>115</v>
@@ -3860,7 +3860,7 @@
         <v>107</v>
       </c>
       <c r="AK80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:47" x14ac:dyDescent="0.25">
@@ -3868,10 +3868,10 @@
         <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V81" t="s">
         <v>116</v>
@@ -3880,13 +3880,13 @@
         <v>115</v>
       </c>
       <c r="AC81" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AJ81" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AK81" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:47" x14ac:dyDescent="0.25">
@@ -3894,10 +3894,10 @@
         <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O82" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AK82" t="s">
         <v>124</v>
@@ -3911,7 +3911,7 @@
         <v>96</v>
       </c>
       <c r="B83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="V83">
         <v>1</v>
@@ -3923,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:47" x14ac:dyDescent="0.25">
@@ -3931,7 +3931,7 @@
         <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="V84">
         <v>1</v>
@@ -3943,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:47" x14ac:dyDescent="0.25">
@@ -3951,7 +3951,7 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V85">
         <v>1</v>
@@ -3960,7 +3960,7 @@
         <v>115</v>
       </c>
       <c r="AD85" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AK85" t="s">
         <v>115</v>
@@ -3974,13 +3974,13 @@
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="X86" t="s">
         <v>115</v>
       </c>
       <c r="AK86" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:47" x14ac:dyDescent="0.25">
@@ -3988,10 +3988,10 @@
         <v>100</v>
       </c>
       <c r="B87" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C87" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="X87" t="s">
         <v>130</v>
@@ -4000,10 +4000,10 @@
         <v>126</v>
       </c>
       <c r="AA87" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AI87" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:47" x14ac:dyDescent="0.25">
@@ -4011,16 +4011,16 @@
         <v>101</v>
       </c>
       <c r="B88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="X88" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AI88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:47" x14ac:dyDescent="0.25">
@@ -4028,19 +4028,19 @@
         <v>102</v>
       </c>
       <c r="B89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E89" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="T89" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U89" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V89" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="X89" t="s">
         <v>115</v>
@@ -4057,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="W90">
         <v>3</v>
@@ -4066,21 +4066,21 @@
         <v>130</v>
       </c>
       <c r="AE90" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AI90" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B91" t="s">
         <v>123</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G91" t="s">
         <v>124</v>
@@ -4091,19 +4091,19 @@
     </row>
     <row r="92" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D92" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G92" t="s">
         <v>124</v>
       </c>
       <c r="M92" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="X92" t="s">
         <v>120</v>
@@ -4111,16 +4111,16 @@
     </row>
     <row r="93" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B93" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D93" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E93" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G93" t="s">
         <v>124</v>
@@ -4131,16 +4131,16 @@
     </row>
     <row r="94" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B94" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="X94" t="s">
         <v>115</v>
@@ -4148,19 +4148,19 @@
     </row>
     <row r="95" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B95" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E95" t="s">
         <v>115</v>
       </c>
       <c r="F95" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="W95" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="X95" t="s">
         <v>115</v>
@@ -4168,19 +4168,19 @@
     </row>
     <row r="96" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B96" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E96" t="s">
         <v>120</v>
       </c>
       <c r="F96" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W96" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="X96" t="s">
         <v>115</v>
@@ -4188,64 +4188,64 @@
     </row>
     <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B97" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="X97" t="s">
         <v>120</v>
       </c>
       <c r="AK97" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B98" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="X98" t="s">
         <v>120</v>
       </c>
       <c r="AK98" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C99" t="s">
         <v>116</v>
       </c>
       <c r="E99" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M99" t="s">
+        <v>267</v>
+      </c>
+      <c r="O99" t="s">
+        <v>530</v>
+      </c>
+      <c r="V99" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL99" t="s">
         <v>269</v>
-      </c>
-      <c r="O99" t="s">
-        <v>535</v>
-      </c>
-      <c r="V99" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL99" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B100" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T100" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="V100">
         <v>1</v>
@@ -4256,16 +4256,16 @@
     </row>
     <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>272</v>
+      </c>
+      <c r="B101" t="s">
+        <v>273</v>
+      </c>
+      <c r="M101" t="s">
         <v>274</v>
       </c>
-      <c r="B101" t="s">
-        <v>275</v>
-      </c>
-      <c r="M101" t="s">
-        <v>276</v>
-      </c>
       <c r="V101" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="W101">
         <v>3</v>
@@ -4273,86 +4273,86 @@
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O102" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W102">
         <v>5</v>
       </c>
       <c r="AC102" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B103" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="W103">
         <v>5</v>
       </c>
       <c r="AC103" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B104" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O104" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W104">
         <v>5</v>
       </c>
       <c r="AC104" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B105" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K105" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O105" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B106" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K106" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O106" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B107" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E107" t="s">
         <v>117</v>
@@ -4361,15 +4361,15 @@
         <v>2</v>
       </c>
       <c r="O107" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B108" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E108" t="s">
         <v>117</v>
@@ -4378,18 +4378,18 @@
         <v>2</v>
       </c>
       <c r="O108" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T108" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B109" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E109" t="s">
         <v>117</v>
@@ -4398,15 +4398,15 @@
         <v>2</v>
       </c>
       <c r="O109" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B110" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E110" t="s">
         <v>117</v>
@@ -4415,27 +4415,27 @@
         <v>2</v>
       </c>
       <c r="O110" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
       </c>
       <c r="O111" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W111">
         <v>3</v>
       </c>
       <c r="AC111" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI111" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AK111" t="s">
         <v>124</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O112" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W112">
         <v>3</v>
       </c>
       <c r="AC112" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI112" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AK112" t="s">
         <v>124</v>
@@ -4466,96 +4466,96 @@
     </row>
     <row r="113" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B113" t="s">
         <v>111</v>
       </c>
       <c r="E113" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O113" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="S113" t="s">
         <v>124</v>
       </c>
       <c r="W113" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="114" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B114" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="S114" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U114" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X114" t="s">
         <v>115</v>
       </c>
       <c r="AI114" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="115" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B115" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H115" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O115" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AE115" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AI115" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="116" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B116" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H116" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O116" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AE116" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AI116" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="117" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B117" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O117" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="V117" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AJ117">
         <v>1</v>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="118" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B118" t="s">
         <v>111</v>
@@ -4572,47 +4572,47 @@
         <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AK118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="119" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B119" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D119" t="s">
         <v>116</v>
       </c>
       <c r="E119" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X119" t="s">
         <v>120</v>
       </c>
       <c r="Y119" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="120" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B120" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="V120" t="s">
         <v>116</v>
       </c>
       <c r="X120" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Y120" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AH120" t="s">
         <v>107</v>
@@ -4620,19 +4620,19 @@
     </row>
     <row r="121" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I121" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O121" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R121" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AU121">
         <v>1</v>
@@ -4640,31 +4640,31 @@
     </row>
     <row r="122" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G122" t="s">
         <v>115</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O122" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="S122" t="s">
+        <v>141</v>
+      </c>
+      <c r="U122" t="s">
         <v>142</v>
       </c>
-      <c r="U122" t="s">
-        <v>143</v>
-      </c>
       <c r="AB122" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AG122" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AH122" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AU122">
         <v>1</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="123" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B123" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N123" s="1">
         <v>6</v>
@@ -4689,16 +4689,16 @@
     </row>
     <row r="124" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E124" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O124" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R124" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AP124">
         <v>1</v>
@@ -4710,12 +4710,12 @@
         <v>1</v>
       </c>
       <c r="AW124" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="125" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -4727,16 +4727,16 @@
         <v>115</v>
       </c>
       <c r="O125" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R125" t="s">
         <v>120</v>
       </c>
       <c r="AB125" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AC125" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AU125">
         <v>1</v>
@@ -4744,33 +4744,33 @@
     </row>
     <row r="126" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D126" t="s">
         <v>105</v>
       </c>
       <c r="I126" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O126" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Z126" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AO126" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AP126">
         <v>1</v>
       </c>
       <c r="AU126" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="127" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B127" t="s">
         <v>125</v>
@@ -4787,25 +4787,25 @@
     </row>
     <row r="128" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D128" t="s">
         <v>105</v>
       </c>
       <c r="O128" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AJ128" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL128" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AP128" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AR128" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AU128">
         <v>1</v>
@@ -4813,261 +4813,261 @@
     </row>
     <row r="129" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D129" t="s">
         <v>105</v>
       </c>
       <c r="O129" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AJ129" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL129" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AP129" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AR129" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AU129">
         <v>1</v>
       </c>
       <c r="BE129" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="130" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="O130" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AC130" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AE130" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AU130">
         <v>1</v>
       </c>
       <c r="AX130" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="131" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B131" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O131" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AX131" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="132" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B132" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O132" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AX132" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="133" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B133" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D133" t="s">
         <v>105</v>
       </c>
       <c r="O133" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AX133" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="134" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B134" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D134" t="s">
         <v>105</v>
       </c>
       <c r="O134" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AX134" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="135" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B135" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G135" t="s">
         <v>124</v>
       </c>
       <c r="O135" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AY135" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="136" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B136" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G136" t="s">
         <v>124</v>
       </c>
       <c r="O136" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AY136" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="137" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B137" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="O137" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AX137" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="AY137" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="138" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E138" t="s">
         <v>117</v>
       </c>
       <c r="M138" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O138" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="S138">
         <v>1</v>
       </c>
       <c r="U138" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AX138" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="139" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E139" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M139" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O139" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AP139" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AX139" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AY139" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="140" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D140" t="s">
         <v>105</v>
       </c>
       <c r="E140" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I140" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O140" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AC140" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AX140" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AY140" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="141" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D141" t="s">
         <v>105</v>
       </c>
       <c r="L141" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M141" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O141" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AY141" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="142" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B142" t="s">
         <v>106</v>
@@ -5076,39 +5076,39 @@
         <v>116</v>
       </c>
       <c r="M142" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="T142" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="143" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H143" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L143" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="O143" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AC143" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AK143" t="s">
         <v>124</v>
       </c>
       <c r="AP143" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AR143" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AT143" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AU143">
         <v>1</v>
@@ -5116,86 +5116,86 @@
     </row>
     <row r="144" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K144" t="s">
         <v>130</v>
       </c>
       <c r="O144" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T144" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K145" t="s">
         <v>130</v>
       </c>
       <c r="O145" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T145" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K146" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="O146" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T146" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="147" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K147" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="O147" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T147" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="148" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K148" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O148" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T148" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="W148" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="149" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O149" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T149" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y149" t="s">
         <v>126</v>
@@ -5203,265 +5203,265 @@
     </row>
     <row r="150" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>365</v>
+      </c>
+      <c r="N150" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="O150" t="s">
+        <v>530</v>
+      </c>
+      <c r="T150" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>527</v>
+      </c>
+      <c r="AN150" t="s">
         <v>367</v>
-      </c>
-      <c r="N150" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="O150" t="s">
-        <v>535</v>
-      </c>
-      <c r="T150" t="s">
-        <v>368</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>532</v>
-      </c>
-      <c r="AN150" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="151" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O151" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T151" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Y151" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AN151" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AY151" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="152" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O152" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T152" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="153" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>373</v>
+      </c>
+      <c r="M153" t="s">
         <v>375</v>
       </c>
-      <c r="M153" t="s">
-        <v>377</v>
-      </c>
       <c r="O153" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T153" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="154" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C154" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="O154" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T154" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="155" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O155" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W155">
         <v>4</v>
       </c>
       <c r="AC155" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="156" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B156" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O156" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U156" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="157" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B157" t="s">
         <v>125</v>
       </c>
       <c r="O157" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T157" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="U157" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="158" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B158" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O158" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U158" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="159" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B159" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E159" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="O159" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="U159" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="160" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B160" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C160" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="O160" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AI160" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="161" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>388</v>
+      </c>
+      <c r="B161" t="s">
+        <v>389</v>
+      </c>
+      <c r="C161" t="s">
+        <v>518</v>
+      </c>
+      <c r="O161" t="s">
+        <v>530</v>
+      </c>
+      <c r="AN161" t="s">
         <v>390</v>
-      </c>
-      <c r="B161" t="s">
-        <v>391</v>
-      </c>
-      <c r="C161" t="s">
-        <v>522</v>
-      </c>
-      <c r="O161" t="s">
-        <v>535</v>
-      </c>
-      <c r="AN161" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="162" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C162" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="O162" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="T162" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AN162" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="163" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B163" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="X163" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AN163" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="164" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J164" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O164" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="165" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B165" t="s">
         <v>110</v>
       </c>
       <c r="O165" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R165">
         <v>7</v>
@@ -5470,21 +5470,21 @@
         <v>4</v>
       </c>
       <c r="AC165" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="166" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B166" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C166" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="O166" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W166">
         <v>3</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="167" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B167" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C167" t="s">
         <v>116</v>
@@ -5504,54 +5504,54 @@
         <v>115</v>
       </c>
       <c r="BE167" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="168" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B168" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D168">
         <v>-1</v>
       </c>
       <c r="O168" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="169" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B169" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D169">
         <v>-1</v>
       </c>
       <c r="O169" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="170" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B170" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D170">
         <v>-2</v>
       </c>
       <c r="X170" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="171" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B171" t="s">
         <v>125</v>
@@ -5565,35 +5565,35 @@
     </row>
     <row r="172" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B172" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H172" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O172" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="173" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B173" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C173">
         <v>2</v>
       </c>
       <c r="O173" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="174" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B174" t="s">
         <v>111</v>
@@ -5602,100 +5602,100 @@
         <v>5</v>
       </c>
       <c r="O174" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="175" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="T175" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="X175" t="s">
         <v>120</v>
       </c>
       <c r="AI175" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="176" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T176" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="X176" t="s">
         <v>120</v>
       </c>
       <c r="AI176" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="177" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B177" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M177" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O177" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P177" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B178" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C178" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="O178" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AF178" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AY178" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="179" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B179" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C179" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="O179" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AF179" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AY179" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="180" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B180" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N180" s="1">
         <v>6</v>
@@ -5704,15 +5704,15 @@
         <v>115</v>
       </c>
       <c r="AK180" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="181" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B181" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N181" s="1">
         <v>6</v>
@@ -5723,10 +5723,10 @@
     </row>
     <row r="182" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D182" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E182" t="s">
         <v>120</v>
@@ -5735,18 +5735,18 @@
         <v>1</v>
       </c>
       <c r="W182" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="Y182" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="AZ182" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="183" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B183" t="s">
         <v>108</v>
@@ -5763,33 +5763,33 @@
     </row>
     <row r="184" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B184" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="O184" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Y184" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="AZ184" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="185" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B185" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E185" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O185" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AZ185" t="s">
         <v>126</v>
@@ -5797,24 +5797,24 @@
     </row>
     <row r="186" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>428</v>
+      </c>
+      <c r="B186" t="s">
+        <v>429</v>
+      </c>
+      <c r="M186" t="s">
         <v>430</v>
-      </c>
-      <c r="B186" t="s">
-        <v>431</v>
-      </c>
-      <c r="M186" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B187" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M187" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="V187" t="s">
         <v>116</v>
@@ -5825,13 +5825,13 @@
     </row>
     <row r="188" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B188" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T188" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="X188" t="s">
         <v>115</v>
@@ -5842,13 +5842,13 @@
     </row>
     <row r="189" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B189" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="T189" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="X189" t="s">
         <v>115</v>
@@ -5859,13 +5859,13 @@
     </row>
     <row r="190" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>452</v>
+      </c>
+      <c r="B190" t="s">
+        <v>454</v>
+      </c>
+      <c r="T190" t="s">
         <v>455</v>
-      </c>
-      <c r="B190" t="s">
-        <v>457</v>
-      </c>
-      <c r="T190" t="s">
-        <v>458</v>
       </c>
       <c r="X190" t="s">
         <v>115</v>
@@ -5876,13 +5876,13 @@
     </row>
     <row r="191" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B191" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="T191" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X191" t="s">
         <v>115</v>
@@ -5893,13 +5893,13 @@
     </row>
     <row r="192" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B192" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T192" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="BD192">
         <v>1</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="193" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B193" t="s">
         <v>114</v>
@@ -5919,15 +5919,15 @@
         <v>115</v>
       </c>
       <c r="BE193" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="194" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B194" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C194" t="s">
         <v>116</v>
@@ -5936,15 +5936,15 @@
         <v>115</v>
       </c>
       <c r="BE194" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="195" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B195" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C195" t="s">
         <v>116</v>
@@ -5953,15 +5953,15 @@
         <v>115</v>
       </c>
       <c r="BE195" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="196" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B196" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C196" t="s">
         <v>116</v>
@@ -5970,151 +5970,151 @@
         <v>115</v>
       </c>
       <c r="BE196" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="197" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B197" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T197" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="X197" t="s">
         <v>115</v>
       </c>
       <c r="AI197" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="198" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B198" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="X198" t="s">
         <v>115</v>
       </c>
       <c r="AI198" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="199" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B199" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="T199" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="X199" t="s">
         <v>115</v>
       </c>
       <c r="AK199" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="200" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B200" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="T200" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X200" t="s">
         <v>115</v>
       </c>
       <c r="AK200" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="201" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B201" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="T201" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="X201" t="s">
         <v>115</v>
       </c>
       <c r="AK201" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="202" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B202" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="T202" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="X202" t="s">
         <v>115</v>
       </c>
       <c r="AK202" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="203" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B203" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="X203" t="s">
         <v>115</v>
       </c>
       <c r="AI203" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AK203" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="204" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B204" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="T204" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="X204" t="s">
         <v>115</v>
       </c>
       <c r="AK204" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="205" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B205" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M205" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="V205">
         <v>1</v>
@@ -6125,16 +6125,16 @@
     </row>
     <row r="206" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B206" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M206" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T206" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="V206">
         <v>1</v>
@@ -6145,13 +6145,13 @@
     </row>
     <row r="207" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B207" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="M207" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V207">
         <v>1</v>
@@ -6162,19 +6162,19 @@
     </row>
     <row r="208" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B208" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E208" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G208" t="s">
         <v>124</v>
       </c>
       <c r="T208" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="X208" t="s">
         <v>115</v>
@@ -6182,19 +6182,19 @@
     </row>
     <row r="209" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B209" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E209" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G209" t="s">
         <v>124</v>
       </c>
       <c r="T209" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="X209" t="s">
         <v>115</v>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="210" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B210" t="s">
         <v>111</v>
@@ -6222,13 +6222,13 @@
     </row>
     <row r="211" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B211" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D211" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E211" t="s">
         <v>120</v>
@@ -6239,75 +6239,75 @@
     </row>
     <row r="212" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B212" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="R212">
         <v>9</v>
       </c>
       <c r="X212" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="BA212" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="213" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B213" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R213">
         <v>9</v>
       </c>
       <c r="X213" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
     </row>
     <row r="214" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B214" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R214">
         <v>9</v>
       </c>
       <c r="T214" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="X214" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="BD214" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="215" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B215" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R215">
         <v>9</v>
       </c>
       <c r="X215" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="AI215" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="216" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B216" t="s">
         <v>111</v>
@@ -6316,61 +6316,61 @@
         <v>9</v>
       </c>
       <c r="T216" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X216" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
     </row>
     <row r="217" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B217" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="R217">
         <v>9</v>
       </c>
       <c r="X217" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
     </row>
     <row r="218" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B218" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="R218">
         <v>9</v>
       </c>
       <c r="T218" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="X218" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="AI218" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="219" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B219" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M219" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="O219" t="s">
+        <v>530</v>
+      </c>
+      <c r="T219" t="s">
         <v>535</v>
-      </c>
-      <c r="T219" t="s">
-        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -6388,147 +6388,147 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/Sistemi_sablon_radni.xlsx
+++ b/Sistemi_sablon_radni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andra\PycharmProjects\Horses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A98778-F54B-4FF4-A182-047A5EA2182E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019F828A-D975-4279-B96B-5100B45157DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18600" yWindow="0" windowWidth="20880" windowHeight="8430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BE$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BE$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="548">
   <si>
     <t>System</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Sys4</t>
   </si>
   <si>
-    <t>Sys5</t>
-  </si>
-  <si>
     <t>Sys6</t>
   </si>
   <si>
@@ -1001,12 +998,6 @@
   </si>
   <si>
     <t>George Boughey</t>
-  </si>
-  <si>
-    <t>&gt;200</t>
-  </si>
-  <si>
-    <t>Sys147</t>
   </si>
   <si>
     <t>Sys149</t>
@@ -2089,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE219"/>
+  <dimension ref="A1:BE217"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -2152,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -2167,7 +2158,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
@@ -2176,28 +2167,28 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="M1" s="5" t="s">
+      <c r="P1" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>509</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>512</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>7</v>
@@ -2206,13 +2197,13 @@
         <v>8</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="W1" s="5" t="s">
         <v>10</v>
@@ -2221,103 +2212,103 @@
         <v>11</v>
       </c>
       <c r="Y1" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>517</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AH1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AJ1" s="5" t="s">
         <v>14</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL1" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AO1" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="AP1" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="AS1" s="5" t="s">
+      <c r="AT1" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AU1" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="AV1" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="AU1" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AX1" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="AY1" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ1" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="BA1" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="BB1" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="BC1" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="BD1" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="BE1" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="AX1" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="AY1" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="AZ1" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="BA1" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="BB1" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="BC1" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="BD1" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="BE1" s="5" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
@@ -2325,13 +2316,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:57" x14ac:dyDescent="0.25">
@@ -2339,40 +2330,40 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="X3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AX3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AY3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
@@ -2380,25 +2371,25 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="W4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AU4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AY4" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
@@ -2406,7 +2397,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2415,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N5" s="1">
         <v>2</v>
@@ -2426,37 +2417,19 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
       </c>
       <c r="D6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q6" t="s">
         <v>112</v>
-      </c>
-      <c r="E6" t="s">
-        <v>188</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>530</v>
-      </c>
-      <c r="R6" t="s">
-        <v>141</v>
-      </c>
-      <c r="X6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>209</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>209</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
@@ -2464,19 +2437,25 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
         <v>115</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>116</v>
       </c>
-      <c r="E7" t="s">
-        <v>117</v>
-      </c>
       <c r="Q7" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="R7" t="s">
+        <v>258</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>515</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
@@ -2484,25 +2463,25 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E8" t="s">
+        <v>119</v>
+      </c>
+      <c r="M8" t="s">
         <v>118</v>
       </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>113</v>
-      </c>
-      <c r="R8" t="s">
-        <v>259</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>518</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>531</v>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
@@ -2510,71 +2489,71 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>518</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
-      </c>
-      <c r="M9" t="s">
-        <v>119</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>124</v>
+        <v>187</v>
+      </c>
+      <c r="O9" t="s">
+        <v>527</v>
+      </c>
+      <c r="R9">
+        <v>8</v>
+      </c>
+      <c r="T9" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" t="s">
-        <v>188</v>
+      <c r="G10" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10" t="s">
+        <v>255</v>
       </c>
       <c r="O10" t="s">
-        <v>530</v>
-      </c>
-      <c r="R10">
-        <v>8</v>
-      </c>
-      <c r="T10" t="s">
-        <v>122</v>
+        <v>527</v>
+      </c>
+      <c r="U10" t="s">
+        <v>256</v>
+      </c>
+      <c r="V10" t="s">
+        <v>229</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>189</v>
+      </c>
       <c r="G11" t="s">
-        <v>219</v>
-      </c>
-      <c r="M11" t="s">
-        <v>256</v>
-      </c>
-      <c r="O11" t="s">
-        <v>530</v>
-      </c>
-      <c r="U11" t="s">
-        <v>257</v>
-      </c>
-      <c r="V11" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>347</v>
+        <v>123</v>
+      </c>
+      <c r="W11">
+        <v>3</v>
+      </c>
+      <c r="X11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
@@ -2582,25 +2561,22 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>346</v>
       </c>
       <c r="G12" t="s">
-        <v>124</v>
-      </c>
-      <c r="W12">
-        <v>3</v>
+        <v>123</v>
+      </c>
+      <c r="R12" t="s">
+        <v>140</v>
       </c>
       <c r="X12" t="s">
-        <v>124</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>518</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
@@ -2608,22 +2584,28 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
-        <v>349</v>
-      </c>
       <c r="G13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R13" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="W13">
+        <v>3</v>
       </c>
       <c r="X13" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
@@ -2631,28 +2613,22 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
+        <v>128</v>
+      </c>
+      <c r="C14" t="s">
+        <v>247</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
-      </c>
-      <c r="R14" t="s">
-        <v>141</v>
-      </c>
-      <c r="W14">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="X14" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>126</v>
+        <v>129</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>253</v>
       </c>
       <c r="AA14" t="s">
-        <v>347</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
@@ -2660,22 +2636,28 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>130</v>
+      </c>
+      <c r="T15" t="s">
+        <v>132</v>
+      </c>
+      <c r="X15" t="s">
         <v>129</v>
       </c>
-      <c r="C15" t="s">
-        <v>248</v>
-      </c>
-      <c r="G15" t="s">
-        <v>124</v>
-      </c>
-      <c r="X15" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>254</v>
-      </c>
       <c r="AA15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
@@ -2683,28 +2665,25 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>109</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" t="s">
-        <v>124</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>131</v>
+        <v>349</v>
+      </c>
+      <c r="O16" t="s">
+        <v>527</v>
+      </c>
+      <c r="R16" t="s">
+        <v>318</v>
       </c>
       <c r="T16" t="s">
-        <v>133</v>
-      </c>
-      <c r="X16" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>209</v>
+        <v>134</v>
+      </c>
+      <c r="W16">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
@@ -2712,25 +2691,19 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
+        <v>135</v>
+      </c>
+      <c r="D17" t="s">
+        <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>352</v>
-      </c>
-      <c r="O17" t="s">
-        <v>530</v>
-      </c>
-      <c r="R17" t="s">
-        <v>319</v>
-      </c>
-      <c r="T17" t="s">
-        <v>135</v>
-      </c>
-      <c r="W17">
-        <v>3</v>
+        <v>136</v>
+      </c>
+      <c r="X17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
@@ -2738,19 +2711,16 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" t="s">
         <v>136</v>
       </c>
-      <c r="D18" t="s">
-        <v>249</v>
-      </c>
-      <c r="E18" t="s">
-        <v>137</v>
-      </c>
       <c r="X18" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>532</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
@@ -2760,28 +2730,31 @@
       <c r="B19" t="s">
         <v>138</v>
       </c>
-      <c r="D19" t="s">
-        <v>249</v>
-      </c>
       <c r="E19" t="s">
-        <v>137</v>
-      </c>
-      <c r="X19" t="s">
-        <v>130</v>
+        <v>199</v>
+      </c>
+      <c r="O19" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="1">
+        <v>5</v>
+      </c>
+      <c r="O20" t="s">
+        <v>527</v>
+      </c>
+      <c r="P20" t="s">
         <v>139</v>
       </c>
-      <c r="E20" t="s">
-        <v>200</v>
-      </c>
-      <c r="O20" t="s">
-        <v>530</v>
+      <c r="AF20" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
@@ -2789,124 +2762,127 @@
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N21" s="1">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="P21" t="s">
+        <v>139</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="U21" t="s">
+        <v>141</v>
+      </c>
+      <c r="AF21" t="s">
         <v>140</v>
       </c>
-      <c r="AF21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="22" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="N22" s="1">
-        <v>5</v>
+      <c r="C22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="N22" s="3">
+        <v>6</v>
       </c>
       <c r="O22" t="s">
-        <v>530</v>
-      </c>
-      <c r="P22" t="s">
-        <v>140</v>
-      </c>
-      <c r="S22">
-        <v>1</v>
-      </c>
-      <c r="U22" t="s">
+        <v>527</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="U22" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AF22" t="s">
-        <v>141</v>
+      <c r="Z22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="23" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" t="s">
+        <v>527</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="N23" s="3">
-        <v>6</v>
-      </c>
-      <c r="O23" t="s">
-        <v>530</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z23" s="2" t="s">
+      <c r="AJ23" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
         <v>146</v>
       </c>
-      <c r="AF23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AY23" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="24" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="N24" s="3"/>
-      <c r="O24" t="s">
-        <v>530</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ24" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>231</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="X24" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG24">
+        <v>100</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:51" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
       <c r="B25" t="s">
+        <v>148</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G25" t="s">
-        <v>232</v>
+      <c r="O25" t="s">
+        <v>527</v>
       </c>
       <c r="V25">
         <v>1</v>
       </c>
-      <c r="X25" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG25">
-        <v>100</v>
-      </c>
-      <c r="AM25" t="s">
-        <v>209</v>
+      <c r="AH25" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:51" ht="60" x14ac:dyDescent="0.25">
@@ -2914,73 +2890,67 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O26" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="V26">
         <v>1</v>
       </c>
       <c r="AH26" t="s">
-        <v>255</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:51" ht="60" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="AM26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O27" t="s">
-        <v>530</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>255</v>
-      </c>
-      <c r="AM27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="28" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B28" t="s">
-        <v>150</v>
-      </c>
-      <c r="M28" s="1" t="s">
+      <c r="B28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M28" s="3" t="s">
         <v>151</v>
       </c>
       <c r="O28" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="29" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
+        <v>135</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O29" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="AY29" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
@@ -2988,16 +2958,16 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>154</v>
       </c>
       <c r="O30" t="s">
-        <v>530</v>
-      </c>
-      <c r="AY30" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
@@ -3005,19 +2975,16 @@
         <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>155</v>
       </c>
       <c r="O31" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="32" spans="1:51" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -3025,10 +2992,10 @@
         <v>157</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="O32" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="33" spans="1:35" ht="60" x14ac:dyDescent="0.25">
@@ -3039,10 +3006,10 @@
         <v>158</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O33" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="34" spans="1:35" ht="60" x14ac:dyDescent="0.25">
@@ -3053,24 +3020,24 @@
         <v>159</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O34" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>48</v>
       </c>
       <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="M35" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="O35" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
@@ -3078,13 +3045,16 @@
         <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="C36" t="s">
+        <v>162</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>161</v>
       </c>
       <c r="O36" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.25">
@@ -3092,16 +3062,17 @@
         <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>163</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>162</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="M37" s="1"/>
       <c r="O37" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="U37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
@@ -3109,17 +3080,20 @@
         <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
-      </c>
-      <c r="C38" t="s">
-        <v>518</v>
+        <v>113</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
       </c>
       <c r="M38" s="1"/>
       <c r="O38" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="U38" t="s">
-        <v>142</v>
+        <v>165</v>
+      </c>
+      <c r="V38" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.25">
@@ -3127,20 +3101,17 @@
         <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="M39" s="1"/>
       <c r="O39" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="U39" t="s">
-        <v>166</v>
-      </c>
-      <c r="V39" t="s">
-        <v>518</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.25">
@@ -3148,17 +3119,20 @@
         <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="M40" s="1"/>
       <c r="O40" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="T40" t="s">
+        <v>134</v>
       </c>
       <c r="U40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.25">
@@ -3166,20 +3140,16 @@
         <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1"/>
+        <v>168</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="O41" t="s">
-        <v>530</v>
-      </c>
-      <c r="T41" t="s">
-        <v>135</v>
+        <v>527</v>
       </c>
       <c r="U41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.25">
@@ -3187,16 +3157,16 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
+        <v>170</v>
+      </c>
+      <c r="M42" t="s">
         <v>169</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="O42" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="U42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.25">
@@ -3204,16 +3174,16 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
+        <v>105</v>
+      </c>
+      <c r="M43" t="s">
+        <v>206</v>
+      </c>
+      <c r="T43" t="s">
         <v>171</v>
       </c>
-      <c r="M43" t="s">
-        <v>170</v>
-      </c>
-      <c r="O43" t="s">
-        <v>530</v>
-      </c>
-      <c r="U43" t="s">
-        <v>166</v>
+      <c r="V43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.25">
@@ -3221,16 +3191,16 @@
         <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
-      </c>
-      <c r="M44" t="s">
-        <v>207</v>
+        <v>172</v>
+      </c>
+      <c r="C44" t="s">
+        <v>162</v>
+      </c>
+      <c r="O44" t="s">
+        <v>527</v>
       </c>
       <c r="T44" t="s">
-        <v>172</v>
-      </c>
-      <c r="V44">
-        <v>1</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:35" x14ac:dyDescent="0.25">
@@ -3238,16 +3208,16 @@
         <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" t="s">
-        <v>163</v>
+        <v>175</v>
+      </c>
+      <c r="M45" t="s">
+        <v>174</v>
       </c>
       <c r="O45" t="s">
-        <v>530</v>
-      </c>
-      <c r="T45" t="s">
-        <v>174</v>
+        <v>527</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
@@ -3255,16 +3225,16 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="M46" t="s">
-        <v>175</v>
-      </c>
-      <c r="O46" t="s">
-        <v>530</v>
-      </c>
-      <c r="AI46" t="s">
         <v>177</v>
+      </c>
+      <c r="T46" t="s">
+        <v>171</v>
+      </c>
+      <c r="V46">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
@@ -3272,16 +3242,13 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
-      </c>
-      <c r="M47" t="s">
         <v>178</v>
       </c>
-      <c r="T47" t="s">
-        <v>172</v>
-      </c>
-      <c r="V47">
-        <v>1</v>
+      <c r="O47" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.25">
@@ -3289,13 +3256,13 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
+        <v>180</v>
+      </c>
+      <c r="O48" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z48" t="s">
         <v>179</v>
-      </c>
-      <c r="O48" t="s">
-        <v>530</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
@@ -3303,13 +3270,16 @@
         <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="O49" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="T49" t="s">
+        <v>134</v>
       </c>
       <c r="Z49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
@@ -3317,16 +3287,16 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
-      </c>
-      <c r="O50" t="s">
-        <v>530</v>
+        <v>172</v>
       </c>
       <c r="T50" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>180</v>
+        <v>173</v>
+      </c>
+      <c r="X50" t="s">
+        <v>182</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
@@ -3334,16 +3304,13 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>173</v>
+        <v>170</v>
+      </c>
+      <c r="O51" t="s">
+        <v>527</v>
       </c>
       <c r="T51" t="s">
-        <v>174</v>
-      </c>
-      <c r="X51" t="s">
         <v>183</v>
-      </c>
-      <c r="AI51" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
@@ -3351,13 +3318,13 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>185</v>
+      </c>
+      <c r="E52" t="s">
+        <v>119</v>
       </c>
       <c r="O52" t="s">
-        <v>530</v>
-      </c>
-      <c r="T52" t="s">
-        <v>184</v>
+        <v>527</v>
       </c>
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
@@ -3368,10 +3335,10 @@
         <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="O53" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
@@ -3379,47 +3346,50 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>187</v>
-      </c>
-      <c r="E54" t="s">
         <v>188</v>
       </c>
+      <c r="F54" t="s">
+        <v>189</v>
+      </c>
       <c r="O54" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>189</v>
-      </c>
-      <c r="F55" t="s">
-        <v>190</v>
+        <v>163</v>
+      </c>
+      <c r="C55" t="s">
+        <v>515</v>
       </c>
       <c r="O55" t="s">
-        <v>530</v>
-      </c>
-      <c r="AI55" t="s">
+        <v>527</v>
+      </c>
+      <c r="U55" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="A56" t="s">
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" t="s">
-        <v>518</v>
+        <v>192</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="U56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
@@ -3427,16 +3397,19 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="O57" t="s">
-        <v>530</v>
-      </c>
-      <c r="U57" t="s">
-        <v>194</v>
+        <v>2</v>
+      </c>
+      <c r="I57" t="s">
+        <v>111</v>
+      </c>
+      <c r="X57" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
@@ -3444,19 +3417,19 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>111</v>
+      </c>
+      <c r="X58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF58" t="s">
         <v>195</v>
-      </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="I58" t="s">
-        <v>112</v>
-      </c>
-      <c r="X58" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF58" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
@@ -3464,19 +3437,22 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="W59">
+        <v>3</v>
       </c>
       <c r="X59" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AF59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
@@ -3484,65 +3460,62 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>112</v>
-      </c>
-      <c r="W60">
-        <v>3</v>
+        <v>111</v>
+      </c>
+      <c r="M60" t="s">
+        <v>200</v>
       </c>
       <c r="X60" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AF60" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="I61" t="s">
-        <v>112</v>
-      </c>
-      <c r="M61" t="s">
+        <v>111</v>
+      </c>
+      <c r="M61" s="1" t="s">
         <v>201</v>
       </c>
       <c r="X61" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="AF61" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="62" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>75</v>
       </c>
       <c r="B62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" t="s">
+        <v>189</v>
+      </c>
+      <c r="M62" t="s">
+        <v>155</v>
+      </c>
+      <c r="X62" t="s">
         <v>114</v>
-      </c>
-      <c r="I62" t="s">
-        <v>112</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="X62" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF62" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
@@ -3552,17 +3525,14 @@
       <c r="B63" t="s">
         <v>203</v>
       </c>
-      <c r="D63" t="s">
-        <v>105</v>
-      </c>
       <c r="G63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M63" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="X63" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
@@ -3570,16 +3540,16 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E64" t="s">
+        <v>205</v>
+      </c>
+      <c r="F64" t="s">
         <v>204</v>
       </c>
-      <c r="G64" t="s">
-        <v>190</v>
-      </c>
-      <c r="M64" t="s">
-        <v>201</v>
-      </c>
-      <c r="X64" t="s">
-        <v>198</v>
+      <c r="O64" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:37" x14ac:dyDescent="0.25">
@@ -3587,16 +3557,16 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
-      </c>
-      <c r="E65" t="s">
+        <v>170</v>
+      </c>
+      <c r="M65" t="s">
         <v>206</v>
       </c>
-      <c r="F65" t="s">
-        <v>205</v>
-      </c>
       <c r="O65" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:37" x14ac:dyDescent="0.25">
@@ -3604,16 +3574,16 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
-      </c>
-      <c r="M66" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="O66" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="Z66" t="s">
-        <v>107</v>
+        <v>179</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:37" x14ac:dyDescent="0.25">
@@ -3621,16 +3591,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>179</v>
-      </c>
-      <c r="O67" t="s">
-        <v>530</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>107</v>
+        <v>168</v>
+      </c>
+      <c r="X67" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z67">
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:37" x14ac:dyDescent="0.25">
@@ -3638,13 +3605,16 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="X68" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="Z68">
         <v>100</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:37" x14ac:dyDescent="0.25">
@@ -3654,14 +3624,14 @@
       <c r="B69" t="s">
         <v>211</v>
       </c>
+      <c r="E69" t="s">
+        <v>212</v>
+      </c>
       <c r="X69" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z69">
+        <v>119</v>
+      </c>
+      <c r="AB69">
         <v>100</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:37" x14ac:dyDescent="0.25">
@@ -3669,13 +3639,13 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
+        <v>213</v>
+      </c>
+      <c r="E70" t="s">
         <v>212</v>
       </c>
-      <c r="E70" t="s">
-        <v>213</v>
-      </c>
       <c r="X70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AB70">
         <v>100</v>
@@ -3686,16 +3656,16 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" t="s">
         <v>214</v>
       </c>
-      <c r="E71" t="s">
-        <v>213</v>
-      </c>
-      <c r="X71" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB71">
-        <v>100</v>
+      <c r="N71" s="1">
+        <v>6</v>
+      </c>
+      <c r="O71" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="72" spans="1:37" x14ac:dyDescent="0.25">
@@ -3703,16 +3673,22 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" t="s">
+        <v>217</v>
+      </c>
+      <c r="D72" t="s">
+        <v>218</v>
+      </c>
+      <c r="M72" t="s">
+        <v>215</v>
+      </c>
+      <c r="O72" t="s">
+        <v>527</v>
+      </c>
+      <c r="Z72" t="s">
         <v>179</v>
-      </c>
-      <c r="C72" t="s">
-        <v>215</v>
-      </c>
-      <c r="N72" s="1">
-        <v>6</v>
-      </c>
-      <c r="O72" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="73" spans="1:37" x14ac:dyDescent="0.25">
@@ -3720,22 +3696,16 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>217</v>
-      </c>
-      <c r="C73" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
         <v>219</v>
       </c>
-      <c r="M73" t="s">
-        <v>216</v>
-      </c>
-      <c r="O73" t="s">
-        <v>530</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>180</v>
+      <c r="X73" t="s">
+        <v>197</v>
+      </c>
+      <c r="AK73" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:37" x14ac:dyDescent="0.25">
@@ -3743,16 +3713,16 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="D74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X74" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AK74" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:37" x14ac:dyDescent="0.25">
@@ -3760,16 +3730,16 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X75" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AK75" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:37" x14ac:dyDescent="0.25">
@@ -3777,16 +3747,16 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>211</v>
-      </c>
-      <c r="D76" t="s">
-        <v>220</v>
+        <v>138</v>
+      </c>
+      <c r="G76" t="s">
+        <v>123</v>
       </c>
       <c r="X76" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AK76" t="s">
-        <v>190</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:37" x14ac:dyDescent="0.25">
@@ -3794,16 +3764,16 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>139</v>
-      </c>
-      <c r="G77" t="s">
-        <v>124</v>
+        <v>221</v>
+      </c>
+      <c r="D77" t="s">
+        <v>115</v>
       </c>
       <c r="X77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AK77" t="s">
-        <v>350</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:37" x14ac:dyDescent="0.25">
@@ -3811,16 +3781,19 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>222</v>
-      </c>
-      <c r="D78" t="s">
-        <v>116</v>
+        <v>120</v>
+      </c>
+      <c r="N78" s="1">
+        <v>5</v>
       </c>
       <c r="X78" t="s">
-        <v>198</v>
+        <v>114</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>106</v>
       </c>
       <c r="AK78" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:37" x14ac:dyDescent="0.25">
@@ -3828,19 +3801,19 @@
         <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
-      </c>
-      <c r="N79" s="1">
-        <v>5</v>
+        <v>210</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="X79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="1:37" x14ac:dyDescent="0.25">
@@ -3848,62 +3821,62 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>211</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>261</v>
+        <v>138</v>
+      </c>
+      <c r="C80" t="s">
+        <v>140</v>
+      </c>
+      <c r="V80" t="s">
+        <v>115</v>
       </c>
       <c r="X80" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>228</v>
+      </c>
+      <c r="AJ80" t="s">
+        <v>208</v>
       </c>
       <c r="AK80" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>139</v>
-      </c>
-      <c r="C81" t="s">
-        <v>141</v>
-      </c>
-      <c r="V81" t="s">
-        <v>116</v>
-      </c>
-      <c r="X81" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC81" t="s">
-        <v>229</v>
-      </c>
-      <c r="AJ81" t="s">
-        <v>209</v>
+        <v>131</v>
+      </c>
+      <c r="O81" t="s">
+        <v>527</v>
       </c>
       <c r="AK81" t="s">
-        <v>230</v>
+        <v>123</v>
+      </c>
+      <c r="AU81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="A82" t="s">
         <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
-      </c>
-      <c r="O82" t="s">
-        <v>530</v>
+        <v>233</v>
+      </c>
+      <c r="V82">
+        <v>1</v>
+      </c>
+      <c r="X82" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD82">
+        <v>100</v>
       </c>
       <c r="AK82" t="s">
-        <v>124</v>
-      </c>
-      <c r="AU82">
-        <v>1</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:47" x14ac:dyDescent="0.25">
@@ -3911,19 +3884,19 @@
         <v>96</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="V83">
         <v>1</v>
       </c>
       <c r="X83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AD83">
         <v>100</v>
       </c>
       <c r="AK83" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:47" x14ac:dyDescent="0.25">
@@ -3931,19 +3904,19 @@
         <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="V84">
         <v>1</v>
       </c>
       <c r="X84" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD84">
-        <v>100</v>
+        <v>114</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>515</v>
       </c>
       <c r="AK84" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="1:47" x14ac:dyDescent="0.25">
@@ -3951,19 +3924,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" t="s">
         <v>236</v>
       </c>
-      <c r="V85">
-        <v>1</v>
-      </c>
       <c r="X85" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD85" t="s">
-        <v>518</v>
+        <v>114</v>
       </c>
       <c r="AK85" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:47" x14ac:dyDescent="0.25">
@@ -3971,16 +3941,22 @@
         <v>99</v>
       </c>
       <c r="B86" t="s">
-        <v>114</v>
-      </c>
-      <c r="E86" t="s">
-        <v>237</v>
+        <v>175</v>
+      </c>
+      <c r="C86" t="s">
+        <v>515</v>
       </c>
       <c r="X86" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK86" t="s">
-        <v>190</v>
+        <v>129</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI86" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:47" x14ac:dyDescent="0.25">
@@ -3988,22 +3964,16 @@
         <v>100</v>
       </c>
       <c r="B87" t="s">
-        <v>176</v>
-      </c>
-      <c r="C87" t="s">
-        <v>518</v>
+        <v>237</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
       </c>
       <c r="X87" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y87" t="s">
-        <v>126</v>
-      </c>
-      <c r="AA87" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="AI87" t="s">
-        <v>177</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="1:47" x14ac:dyDescent="0.25">
@@ -4011,16 +3981,22 @@
         <v>101</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
+        <v>216</v>
+      </c>
+      <c r="E88" t="s">
+        <v>199</v>
+      </c>
+      <c r="T88" t="s">
+        <v>239</v>
+      </c>
+      <c r="U88" t="s">
+        <v>141</v>
+      </c>
+      <c r="V88" t="s">
+        <v>240</v>
       </c>
       <c r="X88" t="s">
-        <v>198</v>
-      </c>
-      <c r="AI88" t="s">
-        <v>239</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:47" x14ac:dyDescent="0.25">
@@ -4028,48 +4004,42 @@
         <v>102</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
-      </c>
-      <c r="E89" t="s">
-        <v>200</v>
-      </c>
-      <c r="T89" t="s">
-        <v>240</v>
-      </c>
-      <c r="U89" t="s">
-        <v>142</v>
-      </c>
-      <c r="V89" t="s">
-        <v>241</v>
+        <v>124</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>252</v>
+      </c>
+      <c r="W89">
+        <v>3</v>
       </c>
       <c r="X89" t="s">
-        <v>115</v>
+        <v>129</v>
+      </c>
+      <c r="AE89" t="s">
+        <v>529</v>
+      </c>
+      <c r="AI89" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="B90" t="s">
-        <v>125</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="H90" t="s">
-        <v>253</v>
-      </c>
-      <c r="W90">
-        <v>3</v>
+        <v>122</v>
+      </c>
+      <c r="D90" t="s">
+        <v>218</v>
+      </c>
+      <c r="G90" t="s">
+        <v>123</v>
       </c>
       <c r="X90" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE90" t="s">
-        <v>532</v>
-      </c>
-      <c r="AI90" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:47" x14ac:dyDescent="0.25">
@@ -4077,16 +4047,19 @@
         <v>223</v>
       </c>
       <c r="B91" t="s">
+        <v>241</v>
+      </c>
+      <c r="D91" t="s">
+        <v>218</v>
+      </c>
+      <c r="G91" t="s">
         <v>123</v>
       </c>
-      <c r="D91" t="s">
-        <v>219</v>
-      </c>
-      <c r="G91" t="s">
-        <v>124</v>
+      <c r="M91" t="s">
+        <v>160</v>
       </c>
       <c r="X91" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:47" x14ac:dyDescent="0.25">
@@ -4097,16 +4070,16 @@
         <v>242</v>
       </c>
       <c r="D92" t="s">
-        <v>219</v>
+        <v>218</v>
+      </c>
+      <c r="E92" t="s">
+        <v>348</v>
       </c>
       <c r="G92" t="s">
-        <v>124</v>
-      </c>
-      <c r="M92" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="X92" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:47" x14ac:dyDescent="0.25">
@@ -4116,17 +4089,14 @@
       <c r="B93" t="s">
         <v>243</v>
       </c>
-      <c r="D93" t="s">
-        <v>219</v>
-      </c>
-      <c r="E93" t="s">
-        <v>351</v>
-      </c>
-      <c r="G93" t="s">
-        <v>124</v>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>244</v>
       </c>
       <c r="X93" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:47" x14ac:dyDescent="0.25">
@@ -4134,16 +4104,19 @@
         <v>226</v>
       </c>
       <c r="B94" t="s">
+        <v>245</v>
+      </c>
+      <c r="E94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" t="s">
         <v>244</v>
       </c>
-      <c r="C94">
-        <v>2</v>
-      </c>
-      <c r="F94" t="s">
-        <v>245</v>
+      <c r="W94" t="s">
+        <v>230</v>
       </c>
       <c r="X94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:47" x14ac:dyDescent="0.25">
@@ -4154,36 +4127,30 @@
         <v>246</v>
       </c>
       <c r="E95" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F95" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="W95" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X95" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="B96" t="s">
-        <v>247</v>
-      </c>
-      <c r="E96" t="s">
-        <v>120</v>
-      </c>
-      <c r="F96" t="s">
-        <v>205</v>
-      </c>
-      <c r="W96" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="X96" t="s">
-        <v>115</v>
+        <v>119</v>
+      </c>
+      <c r="AK96" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="97" spans="1:38" x14ac:dyDescent="0.25">
@@ -4191,101 +4158,101 @@
         <v>264</v>
       </c>
       <c r="B97" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="X97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK97" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>265</v>
       </c>
-      <c r="B98" t="s">
-        <v>222</v>
-      </c>
-      <c r="X98" t="s">
-        <v>120</v>
-      </c>
-      <c r="AK98" t="s">
-        <v>263</v>
+      <c r="C98" t="s">
+        <v>115</v>
+      </c>
+      <c r="E98" t="s">
+        <v>267</v>
+      </c>
+      <c r="M98" t="s">
+        <v>266</v>
+      </c>
+      <c r="O98" t="s">
+        <v>527</v>
+      </c>
+      <c r="V98" t="s">
+        <v>162</v>
+      </c>
+      <c r="AL98" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>266</v>
-      </c>
-      <c r="C99" t="s">
-        <v>116</v>
-      </c>
-      <c r="E99" t="s">
-        <v>268</v>
-      </c>
-      <c r="M99" t="s">
-        <v>267</v>
-      </c>
-      <c r="O99" t="s">
-        <v>530</v>
-      </c>
-      <c r="V99" t="s">
-        <v>163</v>
-      </c>
-      <c r="AL99" t="s">
         <v>269</v>
+      </c>
+      <c r="B99" t="s">
+        <v>148</v>
+      </c>
+      <c r="T99" t="s">
+        <v>270</v>
+      </c>
+      <c r="V99">
+        <v>1</v>
+      </c>
+      <c r="AD99">
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
-      </c>
-      <c r="T100" t="s">
-        <v>271</v>
-      </c>
-      <c r="V100">
-        <v>1</v>
-      </c>
-      <c r="AD100">
-        <v>100</v>
+        <v>272</v>
+      </c>
+      <c r="M100" t="s">
+        <v>273</v>
+      </c>
+      <c r="V100" t="s">
+        <v>515</v>
+      </c>
+      <c r="W100">
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B101" t="s">
-        <v>273</v>
-      </c>
-      <c r="M101" t="s">
-        <v>274</v>
-      </c>
-      <c r="V101" t="s">
-        <v>518</v>
+        <v>245</v>
+      </c>
+      <c r="O101" t="s">
+        <v>527</v>
       </c>
       <c r="W101">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>276</v>
+      </c>
+      <c r="B102" t="s">
         <v>275</v>
-      </c>
-      <c r="B102" t="s">
-        <v>246</v>
-      </c>
-      <c r="O102" t="s">
-        <v>530</v>
       </c>
       <c r="W102">
         <v>5</v>
       </c>
       <c r="AC102" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.25">
@@ -4293,13 +4260,16 @@
         <v>277</v>
       </c>
       <c r="B103" t="s">
-        <v>276</v>
+        <v>203</v>
+      </c>
+      <c r="O103" t="s">
+        <v>527</v>
       </c>
       <c r="W103">
         <v>5</v>
       </c>
       <c r="AC103" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" spans="1:38" x14ac:dyDescent="0.25">
@@ -4307,44 +4277,44 @@
         <v>278</v>
       </c>
       <c r="B104" t="s">
-        <v>204</v>
+        <v>279</v>
+      </c>
+      <c r="K104" t="s">
+        <v>189</v>
       </c>
       <c r="O104" t="s">
-        <v>530</v>
-      </c>
-      <c r="W104">
-        <v>5</v>
-      </c>
-      <c r="AC104" t="s">
-        <v>229</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K105" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O105" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B106" t="s">
         <v>282</v>
       </c>
-      <c r="K106" t="s">
-        <v>190</v>
+      <c r="E106" t="s">
+        <v>116</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
       </c>
       <c r="O106" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.25">
@@ -4352,53 +4322,53 @@
         <v>284</v>
       </c>
       <c r="B107" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I107">
         <v>2</v>
       </c>
       <c r="O107" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="T107" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B108" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E108" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I108">
         <v>2</v>
       </c>
       <c r="O108" t="s">
-        <v>530</v>
-      </c>
-      <c r="T108" t="s">
-        <v>287</v>
+        <v>527</v>
       </c>
     </row>
     <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>290</v>
+      </c>
+      <c r="B109" t="s">
         <v>289</v>
       </c>
-      <c r="B109" t="s">
-        <v>288</v>
-      </c>
       <c r="E109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I109">
         <v>2</v>
       </c>
       <c r="O109" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="110" spans="1:38" x14ac:dyDescent="0.25">
@@ -4406,16 +4376,22 @@
         <v>291</v>
       </c>
       <c r="B110" t="s">
-        <v>290</v>
-      </c>
-      <c r="E110" t="s">
-        <v>117</v>
-      </c>
-      <c r="I110">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="O110" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="W110">
+        <v>3</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI110" t="s">
+        <v>190</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:38" x14ac:dyDescent="0.25">
@@ -4423,22 +4399,22 @@
         <v>292</v>
       </c>
       <c r="B111" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="O111" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="W111">
         <v>3</v>
       </c>
       <c r="AC111" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AI111" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AK111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.25">
@@ -4446,700 +4422,679 @@
         <v>293</v>
       </c>
       <c r="B112" t="s">
-        <v>157</v>
+        <v>110</v>
+      </c>
+      <c r="E112" t="s">
+        <v>294</v>
       </c>
       <c r="O112" t="s">
-        <v>530</v>
-      </c>
-      <c r="W112">
-        <v>3</v>
-      </c>
-      <c r="AC112" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI112" t="s">
-        <v>191</v>
-      </c>
-      <c r="AK112" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="S112" t="s">
+        <v>123</v>
+      </c>
+      <c r="W112" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
-      </c>
-      <c r="E113" t="s">
-        <v>295</v>
-      </c>
-      <c r="O113" t="s">
-        <v>530</v>
+        <v>210</v>
       </c>
       <c r="S113" t="s">
-        <v>124</v>
-      </c>
-      <c r="W113" t="s">
+        <v>231</v>
+      </c>
+      <c r="U113" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="X113" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI113" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="114" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>296</v>
       </c>
       <c r="B114" t="s">
-        <v>211</v>
-      </c>
-      <c r="S114" t="s">
-        <v>232</v>
-      </c>
-      <c r="U114" t="s">
-        <v>142</v>
-      </c>
-      <c r="X114" t="s">
-        <v>115</v>
+        <v>279</v>
+      </c>
+      <c r="H114" t="s">
+        <v>297</v>
+      </c>
+      <c r="O114" t="s">
+        <v>527</v>
+      </c>
+      <c r="AE114" t="s">
+        <v>529</v>
       </c>
       <c r="AI114" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="115" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>299</v>
+      </c>
+      <c r="B115" t="s">
+        <v>298</v>
+      </c>
+      <c r="H115" t="s">
         <v>297</v>
       </c>
-      <c r="B115" t="s">
-        <v>280</v>
-      </c>
-      <c r="H115" t="s">
-        <v>298</v>
-      </c>
       <c r="O115" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AE115" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AI115" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="116" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>300</v>
       </c>
       <c r="B116" t="s">
-        <v>299</v>
-      </c>
-      <c r="H116" t="s">
-        <v>298</v>
+        <v>178</v>
       </c>
       <c r="O116" t="s">
-        <v>530</v>
-      </c>
-      <c r="AE116" t="s">
-        <v>532</v>
-      </c>
-      <c r="AI116" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="V116" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>301</v>
       </c>
       <c r="B117" t="s">
-        <v>179</v>
+        <v>110</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
       </c>
       <c r="O117" t="s">
-        <v>530</v>
-      </c>
-      <c r="V117" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="AK117" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="118" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B118" t="s">
-        <v>111</v>
-      </c>
-      <c r="I118">
-        <v>1</v>
-      </c>
-      <c r="O118" t="s">
-        <v>530</v>
-      </c>
-      <c r="AK118" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="D118" t="s">
+        <v>115</v>
+      </c>
+      <c r="E118" t="s">
+        <v>187</v>
+      </c>
+      <c r="X118" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="119" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>304</v>
       </c>
       <c r="B119" t="s">
-        <v>286</v>
-      </c>
-      <c r="D119" t="s">
-        <v>116</v>
-      </c>
-      <c r="E119" t="s">
-        <v>188</v>
+        <v>305</v>
+      </c>
+      <c r="V119" t="s">
+        <v>115</v>
       </c>
       <c r="X119" t="s">
-        <v>120</v>
+        <v>306</v>
       </c>
       <c r="Y119" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+      <c r="AH119" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="120" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>305</v>
-      </c>
-      <c r="B120" t="s">
-        <v>306</v>
-      </c>
-      <c r="V120" t="s">
-        <v>116</v>
-      </c>
-      <c r="X120" t="s">
-        <v>307</v>
-      </c>
-      <c r="Y120" t="s">
-        <v>528</v>
-      </c>
-      <c r="AH120" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="C120" t="s">
+        <v>140</v>
+      </c>
+      <c r="I120" t="s">
+        <v>140</v>
+      </c>
+      <c r="O120" t="s">
+        <v>527</v>
+      </c>
+      <c r="R120" t="s">
+        <v>318</v>
+      </c>
+      <c r="AU120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>318</v>
-      </c>
-      <c r="C121" t="s">
+        <v>319</v>
+      </c>
+      <c r="G121" t="s">
+        <v>114</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O121" t="s">
+        <v>527</v>
+      </c>
+      <c r="S121" t="s">
+        <v>140</v>
+      </c>
+      <c r="U121" t="s">
         <v>141</v>
       </c>
-      <c r="I121" t="s">
-        <v>141</v>
-      </c>
-      <c r="O121" t="s">
-        <v>530</v>
-      </c>
-      <c r="R121" t="s">
-        <v>319</v>
+      <c r="AB121" t="s">
+        <v>515</v>
+      </c>
+      <c r="AG121" t="s">
+        <v>320</v>
+      </c>
+      <c r="AH121" t="s">
+        <v>320</v>
       </c>
       <c r="AU121">
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>320</v>
-      </c>
-      <c r="G122" t="s">
-        <v>115</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O122" t="s">
-        <v>530</v>
-      </c>
-      <c r="S122" t="s">
-        <v>141</v>
-      </c>
-      <c r="U122" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB122" t="s">
-        <v>518</v>
-      </c>
-      <c r="AG122" t="s">
         <v>321</v>
       </c>
-      <c r="AH122" t="s">
-        <v>321</v>
+      <c r="B122" t="s">
+        <v>322</v>
+      </c>
+      <c r="N122" s="1">
+        <v>6</v>
+      </c>
+      <c r="X122" t="s">
+        <v>114</v>
       </c>
       <c r="AU122">
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>322</v>
-      </c>
-      <c r="B123" t="s">
         <v>323</v>
       </c>
-      <c r="N123" s="1">
-        <v>6</v>
-      </c>
-      <c r="X123" t="s">
-        <v>115</v>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123" t="s">
+        <v>104</v>
+      </c>
+      <c r="G123" t="s">
+        <v>114</v>
+      </c>
+      <c r="O123" t="s">
+        <v>527</v>
+      </c>
+      <c r="R123" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB123" t="s">
+        <v>515</v>
+      </c>
+      <c r="AC123" t="s">
+        <v>228</v>
       </c>
       <c r="AU123">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>325</v>
-      </c>
-      <c r="E124" t="s">
         <v>324</v>
       </c>
+      <c r="D124" t="s">
+        <v>104</v>
+      </c>
+      <c r="I124" t="s">
+        <v>144</v>
+      </c>
       <c r="O124" t="s">
-        <v>530</v>
-      </c>
-      <c r="R124" t="s">
-        <v>141</v>
+        <v>527</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>179</v>
+      </c>
+      <c r="AO124" t="s">
+        <v>214</v>
       </c>
       <c r="AP124">
         <v>1</v>
       </c>
-      <c r="AR124">
-        <v>1</v>
-      </c>
-      <c r="AT124">
-        <v>1</v>
-      </c>
-      <c r="AW124" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AU124" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="125" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>326</v>
-      </c>
-      <c r="C125">
-        <v>1</v>
+        <v>325</v>
+      </c>
+      <c r="B125" t="s">
+        <v>124</v>
       </c>
       <c r="D125" t="s">
-        <v>105</v>
-      </c>
-      <c r="G125" t="s">
-        <v>115</v>
-      </c>
-      <c r="O125" t="s">
-        <v>530</v>
-      </c>
-      <c r="R125" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB125" t="s">
-        <v>518</v>
-      </c>
-      <c r="AC125" t="s">
-        <v>229</v>
+        <v>104</v>
+      </c>
+      <c r="X125" t="s">
+        <v>114</v>
       </c>
       <c r="AU125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>326</v>
+      </c>
+      <c r="D126" t="s">
+        <v>104</v>
+      </c>
+      <c r="O126" t="s">
+        <v>527</v>
+      </c>
+      <c r="AJ126" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL126" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP126" t="s">
+        <v>307</v>
+      </c>
+      <c r="AR126" t="s">
+        <v>307</v>
+      </c>
+      <c r="AU126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>327</v>
       </c>
-      <c r="D126" t="s">
-        <v>105</v>
-      </c>
-      <c r="I126" t="s">
-        <v>145</v>
-      </c>
-      <c r="O126" t="s">
-        <v>530</v>
-      </c>
-      <c r="Z126" t="s">
-        <v>180</v>
-      </c>
-      <c r="AO126" t="s">
-        <v>215</v>
-      </c>
-      <c r="AP126">
-        <v>1</v>
-      </c>
-      <c r="AU126" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>328</v>
-      </c>
-      <c r="B127" t="s">
-        <v>125</v>
-      </c>
       <c r="D127" t="s">
-        <v>105</v>
-      </c>
-      <c r="X127" t="s">
-        <v>115</v>
+        <v>104</v>
+      </c>
+      <c r="O127" t="s">
+        <v>527</v>
+      </c>
+      <c r="AJ127" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL127" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP127" t="s">
+        <v>307</v>
+      </c>
+      <c r="AR127" t="s">
+        <v>307</v>
       </c>
       <c r="AU127">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="BE127" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="128" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>329</v>
-      </c>
-      <c r="D128" t="s">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="O128" t="s">
-        <v>530</v>
-      </c>
-      <c r="AJ128" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL128" t="s">
-        <v>232</v>
-      </c>
-      <c r="AP128" t="s">
-        <v>308</v>
-      </c>
-      <c r="AR128" t="s">
-        <v>308</v>
+        <v>527</v>
+      </c>
+      <c r="AC128" t="s">
+        <v>228</v>
+      </c>
+      <c r="AE128" t="s">
+        <v>529</v>
       </c>
       <c r="AU128">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="AX128" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="129" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>329</v>
+      </c>
+      <c r="B129" t="s">
+        <v>220</v>
+      </c>
+      <c r="O129" t="s">
+        <v>527</v>
+      </c>
+      <c r="AX129" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="130" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>330</v>
       </c>
-      <c r="D129" t="s">
-        <v>105</v>
-      </c>
-      <c r="O129" t="s">
-        <v>530</v>
-      </c>
-      <c r="AJ129" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL129" t="s">
-        <v>232</v>
-      </c>
-      <c r="AP129" t="s">
-        <v>308</v>
-      </c>
-      <c r="AR129" t="s">
-        <v>308</v>
-      </c>
-      <c r="AU129">
-        <v>1</v>
-      </c>
-      <c r="BE129" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="130" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="B130" t="s">
+        <v>159</v>
+      </c>
+      <c r="O130" t="s">
+        <v>527</v>
+      </c>
+      <c r="AX130" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="131" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>331</v>
       </c>
-      <c r="O130" t="s">
-        <v>530</v>
-      </c>
-      <c r="AC130" t="s">
-        <v>229</v>
-      </c>
-      <c r="AE130" t="s">
-        <v>532</v>
-      </c>
-      <c r="AU130">
-        <v>1</v>
-      </c>
-      <c r="AX130" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="131" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>332</v>
       </c>
-      <c r="B131" t="s">
-        <v>221</v>
+      <c r="D131" t="s">
+        <v>104</v>
       </c>
       <c r="O131" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AX131" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="132" spans="1:57" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="132" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>333</v>
       </c>
       <c r="B132" t="s">
-        <v>160</v>
+        <v>196</v>
+      </c>
+      <c r="D132" t="s">
+        <v>104</v>
       </c>
       <c r="O132" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AX132" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="133" spans="1:57" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="133" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>334</v>
       </c>
       <c r="B133" t="s">
         <v>335</v>
       </c>
-      <c r="D133" t="s">
+      <c r="G133" t="s">
+        <v>123</v>
+      </c>
+      <c r="O133" t="s">
+        <v>527</v>
+      </c>
+      <c r="AY133" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="134" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>338</v>
+      </c>
+      <c r="B134" t="s">
+        <v>337</v>
+      </c>
+      <c r="G134" t="s">
+        <v>123</v>
+      </c>
+      <c r="O134" t="s">
+        <v>527</v>
+      </c>
+      <c r="AY134" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="135" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>339</v>
+      </c>
+      <c r="B135" t="s">
+        <v>281</v>
+      </c>
+      <c r="O135" t="s">
+        <v>527</v>
+      </c>
+      <c r="AX135" t="s">
+        <v>528</v>
+      </c>
+      <c r="AY135" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="136" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>340</v>
+      </c>
+      <c r="E136" t="s">
+        <v>116</v>
+      </c>
+      <c r="M136" t="s">
+        <v>341</v>
+      </c>
+      <c r="O136" t="s">
+        <v>527</v>
+      </c>
+      <c r="S136">
+        <v>1</v>
+      </c>
+      <c r="U136" t="s">
+        <v>342</v>
+      </c>
+      <c r="AX136" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="137" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>343</v>
+      </c>
+      <c r="E137" t="s">
+        <v>267</v>
+      </c>
+      <c r="M137" t="s">
+        <v>266</v>
+      </c>
+      <c r="O137" t="s">
+        <v>527</v>
+      </c>
+      <c r="AP137" t="s">
+        <v>344</v>
+      </c>
+      <c r="AX137" t="s">
+        <v>515</v>
+      </c>
+      <c r="AY137" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="138" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>345</v>
+      </c>
+      <c r="D138" t="s">
+        <v>104</v>
+      </c>
+      <c r="E138" t="s">
+        <v>267</v>
+      </c>
+      <c r="I138" t="s">
+        <v>344</v>
+      </c>
+      <c r="O138" t="s">
+        <v>527</v>
+      </c>
+      <c r="AC138" t="s">
+        <v>228</v>
+      </c>
+      <c r="AX138" t="s">
+        <v>515</v>
+      </c>
+      <c r="AY138" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="139" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>351</v>
+      </c>
+      <c r="D139" t="s">
+        <v>104</v>
+      </c>
+      <c r="L139" t="s">
+        <v>208</v>
+      </c>
+      <c r="M139" t="s">
+        <v>160</v>
+      </c>
+      <c r="O139" t="s">
+        <v>527</v>
+      </c>
+      <c r="AY139" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="140" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>352</v>
+      </c>
+      <c r="B140" t="s">
         <v>105</v>
       </c>
-      <c r="O133" t="s">
-        <v>530</v>
-      </c>
-      <c r="AX133" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="134" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>336</v>
-      </c>
-      <c r="B134" t="s">
-        <v>197</v>
-      </c>
-      <c r="D134" t="s">
-        <v>105</v>
-      </c>
-      <c r="O134" t="s">
-        <v>530</v>
-      </c>
-      <c r="AX134" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="135" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>337</v>
-      </c>
-      <c r="B135" t="s">
-        <v>338</v>
-      </c>
-      <c r="G135" t="s">
-        <v>124</v>
-      </c>
-      <c r="O135" t="s">
-        <v>530</v>
-      </c>
-      <c r="AY135" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="136" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>341</v>
-      </c>
-      <c r="B136" t="s">
-        <v>340</v>
-      </c>
-      <c r="G136" t="s">
-        <v>124</v>
-      </c>
-      <c r="O136" t="s">
-        <v>530</v>
-      </c>
-      <c r="AY136" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="137" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>342</v>
-      </c>
-      <c r="B137" t="s">
-        <v>282</v>
-      </c>
-      <c r="O137" t="s">
-        <v>530</v>
-      </c>
-      <c r="AX137" t="s">
-        <v>531</v>
-      </c>
-      <c r="AY137" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="138" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>343</v>
-      </c>
-      <c r="E138" t="s">
-        <v>117</v>
-      </c>
-      <c r="M138" t="s">
-        <v>344</v>
-      </c>
-      <c r="O138" t="s">
-        <v>530</v>
-      </c>
-      <c r="S138">
+      <c r="C140" t="s">
+        <v>115</v>
+      </c>
+      <c r="M140" t="s">
+        <v>206</v>
+      </c>
+      <c r="T140" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="141" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>353</v>
+      </c>
+      <c r="H141" t="s">
+        <v>297</v>
+      </c>
+      <c r="L141" t="s">
+        <v>307</v>
+      </c>
+      <c r="O141" t="s">
+        <v>527</v>
+      </c>
+      <c r="AC141" t="s">
+        <v>228</v>
+      </c>
+      <c r="AK141" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP141" t="s">
+        <v>307</v>
+      </c>
+      <c r="AR141" t="s">
+        <v>307</v>
+      </c>
+      <c r="AT141" t="s">
+        <v>307</v>
+      </c>
+      <c r="AU141">
         <v>1</v>
       </c>
-      <c r="U138" t="s">
-        <v>345</v>
-      </c>
-      <c r="AX138" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="139" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>346</v>
-      </c>
-      <c r="E139" t="s">
-        <v>268</v>
-      </c>
-      <c r="M139" t="s">
-        <v>267</v>
-      </c>
-      <c r="O139" t="s">
-        <v>530</v>
-      </c>
-      <c r="AP139" t="s">
-        <v>347</v>
-      </c>
-      <c r="AX139" t="s">
-        <v>518</v>
-      </c>
-      <c r="AY139" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="140" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>348</v>
-      </c>
-      <c r="D140" t="s">
-        <v>105</v>
-      </c>
-      <c r="E140" t="s">
-        <v>268</v>
-      </c>
-      <c r="I140" t="s">
-        <v>347</v>
-      </c>
-      <c r="O140" t="s">
-        <v>530</v>
-      </c>
-      <c r="AC140" t="s">
-        <v>229</v>
-      </c>
-      <c r="AX140" t="s">
-        <v>518</v>
-      </c>
-      <c r="AY140" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="141" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+    </row>
+    <row r="142" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>354</v>
       </c>
-      <c r="D141" t="s">
-        <v>105</v>
-      </c>
-      <c r="L141" t="s">
-        <v>209</v>
-      </c>
-      <c r="M141" t="s">
-        <v>161</v>
-      </c>
-      <c r="O141" t="s">
-        <v>530</v>
-      </c>
-      <c r="AY141" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="142" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="K142" t="s">
+        <v>129</v>
+      </c>
+      <c r="O142" t="s">
+        <v>527</v>
+      </c>
+      <c r="T142" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="143" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>355</v>
       </c>
-      <c r="B142" t="s">
-        <v>106</v>
-      </c>
-      <c r="C142" t="s">
-        <v>116</v>
-      </c>
-      <c r="M142" t="s">
-        <v>207</v>
-      </c>
-      <c r="T142" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="143" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>356</v>
-      </c>
-      <c r="H143" t="s">
-        <v>298</v>
-      </c>
-      <c r="L143" t="s">
-        <v>308</v>
+      <c r="K143" t="s">
+        <v>129</v>
       </c>
       <c r="O143" t="s">
-        <v>530</v>
-      </c>
-      <c r="AC143" t="s">
-        <v>229</v>
-      </c>
-      <c r="AK143" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP143" t="s">
-        <v>308</v>
-      </c>
-      <c r="AR143" t="s">
-        <v>308</v>
-      </c>
-      <c r="AT143" t="s">
-        <v>308</v>
-      </c>
-      <c r="AU143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:57" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="T143" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="144" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>357</v>
       </c>
       <c r="K144" t="s">
-        <v>130</v>
+        <v>516</v>
       </c>
       <c r="O144" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="T144" t="s">
-        <v>174</v>
+        <v>356</v>
       </c>
     </row>
     <row r="145" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>359</v>
+      </c>
+      <c r="K145" t="s">
+        <v>516</v>
+      </c>
+      <c r="O145" t="s">
+        <v>527</v>
+      </c>
+      <c r="T145" t="s">
         <v>358</v>
-      </c>
-      <c r="K145" t="s">
-        <v>130</v>
-      </c>
-      <c r="O145" t="s">
-        <v>530</v>
-      </c>
-      <c r="T145" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:51" x14ac:dyDescent="0.25">
@@ -5147,132 +5102,138 @@
         <v>360</v>
       </c>
       <c r="K146" t="s">
-        <v>519</v>
+        <v>244</v>
       </c>
       <c r="O146" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="T146" t="s">
-        <v>359</v>
+        <v>171</v>
+      </c>
+      <c r="W146" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="147" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>362</v>
-      </c>
-      <c r="K147" t="s">
-        <v>519</v>
+        <v>361</v>
       </c>
       <c r="O147" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="T147" t="s">
-        <v>361</v>
+        <v>184</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="148" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>362</v>
+      </c>
+      <c r="N148" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O148" t="s">
+        <v>527</v>
+      </c>
+      <c r="T148" t="s">
         <v>363</v>
       </c>
-      <c r="K148" t="s">
-        <v>245</v>
-      </c>
-      <c r="O148" t="s">
-        <v>530</v>
-      </c>
-      <c r="T148" t="s">
-        <v>172</v>
-      </c>
-      <c r="W148" t="s">
-        <v>372</v>
+      <c r="Y148" t="s">
+        <v>524</v>
+      </c>
+      <c r="AN148" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="149" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>365</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O149" t="s">
+        <v>527</v>
+      </c>
+      <c r="T149" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>524</v>
+      </c>
+      <c r="AN149" t="s">
         <v>364</v>
       </c>
-      <c r="O149" t="s">
-        <v>530</v>
-      </c>
-      <c r="T149" t="s">
-        <v>185</v>
-      </c>
-      <c r="Y149" t="s">
-        <v>126</v>
+      <c r="AY149" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="150" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>365</v>
+        <v>367</v>
+      </c>
+      <c r="B150" t="s">
+        <v>164</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="O150" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="T150" t="s">
-        <v>366</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>527</v>
-      </c>
-      <c r="AN150" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="151" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>368</v>
-      </c>
-      <c r="N151" s="1" t="s">
-        <v>261</v>
+        <v>370</v>
+      </c>
+      <c r="M151" t="s">
+        <v>372</v>
       </c>
       <c r="O151" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="T151" t="s">
-        <v>369</v>
-      </c>
-      <c r="Y151" t="s">
-        <v>527</v>
-      </c>
-      <c r="AN151" t="s">
-        <v>367</v>
-      </c>
-      <c r="AY151" t="s">
-        <v>531</v>
+        <v>371</v>
       </c>
     </row>
     <row r="152" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B152" t="s">
-        <v>165</v>
-      </c>
-      <c r="N152" s="1" t="s">
-        <v>248</v>
+        <v>164</v>
+      </c>
+      <c r="C152" t="s">
+        <v>515</v>
       </c>
       <c r="O152" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="T152" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="153" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>373</v>
-      </c>
-      <c r="M153" t="s">
         <v>375</v>
       </c>
+      <c r="B153" t="s">
+        <v>148</v>
+      </c>
       <c r="O153" t="s">
-        <v>530</v>
-      </c>
-      <c r="T153" t="s">
-        <v>374</v>
+        <v>527</v>
+      </c>
+      <c r="W153">
+        <v>4</v>
+      </c>
+      <c r="AC153" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="154" spans="1:51" x14ac:dyDescent="0.25">
@@ -5280,78 +5241,78 @@
         <v>376</v>
       </c>
       <c r="B154" t="s">
-        <v>165</v>
-      </c>
-      <c r="C154" t="s">
-        <v>518</v>
+        <v>380</v>
       </c>
       <c r="O154" t="s">
-        <v>530</v>
-      </c>
-      <c r="T154" t="s">
-        <v>377</v>
+        <v>527</v>
+      </c>
+      <c r="U154" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="155" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B155" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="O155" t="s">
-        <v>530</v>
-      </c>
-      <c r="W155">
-        <v>4</v>
-      </c>
-      <c r="AC155" t="s">
-        <v>229</v>
+        <v>527</v>
+      </c>
+      <c r="T155" t="s">
+        <v>183</v>
+      </c>
+      <c r="U155" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="156" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>378</v>
+      </c>
+      <c r="B156" t="s">
+        <v>381</v>
+      </c>
+      <c r="O156" t="s">
+        <v>527</v>
+      </c>
+      <c r="U156" t="s">
         <v>379</v>
-      </c>
-      <c r="B156" t="s">
-        <v>383</v>
-      </c>
-      <c r="O156" t="s">
-        <v>530</v>
-      </c>
-      <c r="U156" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="157" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B157" t="s">
-        <v>125</v>
+        <v>138</v>
+      </c>
+      <c r="E157" t="s">
+        <v>267</v>
       </c>
       <c r="O157" t="s">
-        <v>530</v>
-      </c>
-      <c r="T157" t="s">
-        <v>184</v>
+        <v>527</v>
       </c>
       <c r="U157" t="s">
-        <v>382</v>
+        <v>142</v>
       </c>
     </row>
     <row r="158" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B158" t="s">
         <v>384</v>
       </c>
+      <c r="C158" t="s">
+        <v>515</v>
+      </c>
       <c r="O158" t="s">
-        <v>530</v>
-      </c>
-      <c r="U158" t="s">
-        <v>382</v>
+        <v>527</v>
+      </c>
+      <c r="AI158" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="159" spans="1:51" x14ac:dyDescent="0.25">
@@ -5359,70 +5320,64 @@
         <v>385</v>
       </c>
       <c r="B159" t="s">
-        <v>139</v>
-      </c>
-      <c r="E159" t="s">
-        <v>268</v>
+        <v>386</v>
+      </c>
+      <c r="C159" t="s">
+        <v>515</v>
       </c>
       <c r="O159" t="s">
-        <v>530</v>
-      </c>
-      <c r="U159" t="s">
-        <v>143</v>
+        <v>527</v>
+      </c>
+      <c r="AN159" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="160" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B160" t="s">
+        <v>164</v>
+      </c>
+      <c r="C160" t="s">
+        <v>515</v>
+      </c>
+      <c r="O160" t="s">
+        <v>527</v>
+      </c>
+      <c r="T160" t="s">
+        <v>374</v>
+      </c>
+      <c r="AN160" t="s">
         <v>387</v>
-      </c>
-      <c r="C160" t="s">
-        <v>518</v>
-      </c>
-      <c r="O160" t="s">
-        <v>530</v>
-      </c>
-      <c r="AI160" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="161" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B161" t="s">
-        <v>389</v>
-      </c>
-      <c r="C161" t="s">
-        <v>518</v>
-      </c>
-      <c r="O161" t="s">
-        <v>530</v>
+        <v>392</v>
+      </c>
+      <c r="X161" t="s">
+        <v>390</v>
       </c>
       <c r="AN161" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="162" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
-      </c>
-      <c r="C162" t="s">
-        <v>518</v>
+        <v>159</v>
+      </c>
+      <c r="J162" t="s">
+        <v>395</v>
       </c>
       <c r="O162" t="s">
-        <v>530</v>
-      </c>
-      <c r="T162" t="s">
-        <v>377</v>
-      </c>
-      <c r="AN162" t="s">
-        <v>390</v>
+        <v>527</v>
       </c>
     </row>
     <row r="163" spans="1:57" x14ac:dyDescent="0.25">
@@ -5430,13 +5385,19 @@
         <v>396</v>
       </c>
       <c r="B163" t="s">
-        <v>395</v>
-      </c>
-      <c r="X163" t="s">
-        <v>393</v>
-      </c>
-      <c r="AN163" t="s">
-        <v>390</v>
+        <v>109</v>
+      </c>
+      <c r="O163" t="s">
+        <v>527</v>
+      </c>
+      <c r="R163">
+        <v>7</v>
+      </c>
+      <c r="W163">
+        <v>4</v>
+      </c>
+      <c r="AC163" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="164" spans="1:57" x14ac:dyDescent="0.25">
@@ -5444,13 +5405,16 @@
         <v>397</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
-      </c>
-      <c r="J164" t="s">
         <v>398</v>
       </c>
+      <c r="C164" t="s">
+        <v>515</v>
+      </c>
       <c r="O164" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="W164">
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:57" x14ac:dyDescent="0.25">
@@ -5458,36 +5422,30 @@
         <v>399</v>
       </c>
       <c r="B165" t="s">
-        <v>110</v>
-      </c>
-      <c r="O165" t="s">
-        <v>530</v>
-      </c>
-      <c r="R165">
-        <v>7</v>
-      </c>
-      <c r="W165">
-        <v>4</v>
-      </c>
-      <c r="AC165" t="s">
-        <v>134</v>
+        <v>400</v>
+      </c>
+      <c r="C165" t="s">
+        <v>115</v>
+      </c>
+      <c r="X165" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE165" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="166" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B166" t="s">
-        <v>401</v>
-      </c>
-      <c r="C166" t="s">
-        <v>518</v>
+        <v>246</v>
+      </c>
+      <c r="D166">
+        <v>-1</v>
       </c>
       <c r="O166" t="s">
-        <v>530</v>
-      </c>
-      <c r="W166">
-        <v>3</v>
+        <v>527</v>
       </c>
     </row>
     <row r="167" spans="1:57" x14ac:dyDescent="0.25">
@@ -5495,414 +5453,417 @@
         <v>402</v>
       </c>
       <c r="B167" t="s">
-        <v>403</v>
-      </c>
-      <c r="C167" t="s">
-        <v>116</v>
-      </c>
-      <c r="X167" t="s">
-        <v>115</v>
-      </c>
-      <c r="BE167" t="s">
-        <v>518</v>
+        <v>196</v>
+      </c>
+      <c r="D167">
+        <v>-1</v>
+      </c>
+      <c r="O167" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="168" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B168" t="s">
-        <v>247</v>
+        <v>178</v>
       </c>
       <c r="D168">
-        <v>-1</v>
-      </c>
-      <c r="O168" t="s">
-        <v>530</v>
+        <v>-2</v>
+      </c>
+      <c r="X168" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="169" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B169" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="D169">
-        <v>-1</v>
-      </c>
-      <c r="O169" t="s">
-        <v>530</v>
+        <v>5</v>
+      </c>
+      <c r="X169" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="170" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
-      </c>
-      <c r="D170">
-        <v>-2</v>
-      </c>
-      <c r="X170" t="s">
-        <v>198</v>
+        <v>211</v>
+      </c>
+      <c r="H170" t="s">
+        <v>297</v>
+      </c>
+      <c r="O170" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="171" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B171" t="s">
-        <v>125</v>
-      </c>
-      <c r="D171">
-        <v>5</v>
-      </c>
-      <c r="X171" t="s">
-        <v>130</v>
+        <v>188</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+      <c r="O171" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="172" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B172" t="s">
-        <v>212</v>
-      </c>
-      <c r="H172" t="s">
-        <v>298</v>
+        <v>110</v>
+      </c>
+      <c r="C172">
+        <v>5</v>
       </c>
       <c r="O172" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="173" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>408</v>
+      </c>
+      <c r="T173" t="s">
         <v>409</v>
       </c>
-      <c r="B173" t="s">
-        <v>189</v>
-      </c>
-      <c r="C173">
-        <v>2</v>
-      </c>
-      <c r="O173" t="s">
-        <v>530</v>
+      <c r="X173" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI173" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>410</v>
       </c>
-      <c r="B174" t="s">
-        <v>111</v>
-      </c>
-      <c r="C174">
-        <v>5</v>
-      </c>
-      <c r="O174" t="s">
-        <v>530</v>
+      <c r="T174" t="s">
+        <v>411</v>
+      </c>
+      <c r="X174" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI174" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="175" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>411</v>
-      </c>
-      <c r="T175" t="s">
         <v>412</v>
       </c>
-      <c r="X175" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI175" t="s">
-        <v>177</v>
+      <c r="B175" t="s">
+        <v>194</v>
+      </c>
+      <c r="M175" t="s">
+        <v>413</v>
+      </c>
+      <c r="O175" t="s">
+        <v>527</v>
+      </c>
+      <c r="P175" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="176" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>413</v>
-      </c>
-      <c r="T176" t="s">
         <v>414</v>
       </c>
-      <c r="X176" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI176" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="177" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>211</v>
+      </c>
+      <c r="C176" t="s">
+        <v>307</v>
+      </c>
+      <c r="O176" t="s">
+        <v>527</v>
+      </c>
+      <c r="AF176" t="s">
+        <v>415</v>
+      </c>
+      <c r="AY176" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="177" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>416</v>
+      </c>
+      <c r="B177" t="s">
+        <v>384</v>
+      </c>
+      <c r="C177" t="s">
+        <v>307</v>
+      </c>
+      <c r="O177" t="s">
+        <v>527</v>
+      </c>
+      <c r="AF177" t="s">
         <v>415</v>
       </c>
-      <c r="B177" t="s">
-        <v>195</v>
-      </c>
-      <c r="M177" t="s">
-        <v>416</v>
-      </c>
-      <c r="O177" t="s">
-        <v>530</v>
-      </c>
-      <c r="P177" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="178" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AY177" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="178" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>417</v>
       </c>
       <c r="B178" t="s">
-        <v>212</v>
-      </c>
-      <c r="C178" t="s">
-        <v>308</v>
-      </c>
-      <c r="O178" t="s">
+        <v>159</v>
+      </c>
+      <c r="N178" s="1">
+        <v>6</v>
+      </c>
+      <c r="X178" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK178" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="179" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>418</v>
+      </c>
+      <c r="B179" t="s">
+        <v>419</v>
+      </c>
+      <c r="N179" s="1">
+        <v>6</v>
+      </c>
+      <c r="X179" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="180" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>421</v>
+      </c>
+      <c r="D180" t="s">
+        <v>515</v>
+      </c>
+      <c r="E180" t="s">
+        <v>119</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="W180" t="s">
         <v>530</v>
       </c>
-      <c r="AF178" t="s">
-        <v>418</v>
-      </c>
-      <c r="AY178" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="179" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>419</v>
-      </c>
-      <c r="B179" t="s">
-        <v>387</v>
-      </c>
-      <c r="C179" t="s">
-        <v>308</v>
-      </c>
-      <c r="O179" t="s">
-        <v>530</v>
-      </c>
-      <c r="AF179" t="s">
-        <v>418</v>
-      </c>
-      <c r="AY179" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="180" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>420</v>
-      </c>
-      <c r="B180" t="s">
-        <v>160</v>
-      </c>
-      <c r="N180" s="1">
-        <v>6</v>
-      </c>
-      <c r="X180" t="s">
+      <c r="Y180" t="s">
+        <v>526</v>
+      </c>
+      <c r="AZ180" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="181" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>422</v>
+      </c>
+      <c r="B181" t="s">
+        <v>107</v>
+      </c>
+      <c r="D181" t="s">
         <v>115</v>
       </c>
-      <c r="AK180" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="181" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>421</v>
-      </c>
-      <c r="B181" t="s">
-        <v>422</v>
-      </c>
-      <c r="N181" s="1">
-        <v>6</v>
-      </c>
-      <c r="X181" t="s">
+      <c r="Y181" t="s">
+        <v>125</v>
+      </c>
+      <c r="AZ181" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>423</v>
+      </c>
+      <c r="B182" t="s">
+        <v>241</v>
+      </c>
+      <c r="O182" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y182" t="s">
+        <v>526</v>
+      </c>
+      <c r="AZ182" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="183" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>424</v>
+      </c>
+      <c r="B183" t="s">
+        <v>391</v>
+      </c>
+      <c r="E183" t="s">
+        <v>236</v>
+      </c>
+      <c r="O183" t="s">
+        <v>527</v>
+      </c>
+      <c r="AZ183" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="184" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>425</v>
+      </c>
+      <c r="B184" t="s">
+        <v>426</v>
+      </c>
+      <c r="M184" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="185" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>429</v>
+      </c>
+      <c r="B185" t="s">
+        <v>428</v>
+      </c>
+      <c r="M185" t="s">
+        <v>255</v>
+      </c>
+      <c r="V185" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="182" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>424</v>
-      </c>
-      <c r="D182" t="s">
-        <v>518</v>
-      </c>
-      <c r="E182" t="s">
-        <v>120</v>
-      </c>
-      <c r="I182">
+      <c r="X185" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="186" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>446</v>
+      </c>
+      <c r="B186" t="s">
+        <v>156</v>
+      </c>
+      <c r="T186" t="s">
+        <v>437</v>
+      </c>
+      <c r="X186" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC186">
         <v>1</v>
       </c>
-      <c r="W182" t="s">
-        <v>533</v>
-      </c>
-      <c r="Y182" t="s">
-        <v>529</v>
-      </c>
-      <c r="AZ182" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="183" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>425</v>
-      </c>
-      <c r="B183" t="s">
-        <v>108</v>
-      </c>
-      <c r="D183" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y183" t="s">
-        <v>126</v>
-      </c>
-      <c r="AZ183" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="184" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>426</v>
-      </c>
-      <c r="B184" t="s">
-        <v>242</v>
-      </c>
-      <c r="O184" t="s">
-        <v>530</v>
-      </c>
-      <c r="Y184" t="s">
-        <v>529</v>
-      </c>
-      <c r="AZ184" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="185" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>427</v>
-      </c>
-      <c r="B185" t="s">
-        <v>394</v>
-      </c>
-      <c r="E185" t="s">
-        <v>237</v>
-      </c>
-      <c r="O185" t="s">
-        <v>530</v>
-      </c>
-      <c r="AZ185" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="186" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>428</v>
-      </c>
-      <c r="B186" t="s">
-        <v>429</v>
-      </c>
-      <c r="M186" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="187" spans="1:56" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="B187" t="s">
-        <v>431</v>
-      </c>
-      <c r="M187" t="s">
-        <v>256</v>
-      </c>
-      <c r="V187" t="s">
-        <v>116</v>
+        <v>391</v>
+      </c>
+      <c r="T187" t="s">
+        <v>286</v>
       </c>
       <c r="X187" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="188" spans="1:56" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="BC187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>449</v>
       </c>
       <c r="B188" t="s">
-        <v>157</v>
+        <v>451</v>
       </c>
       <c r="T188" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="X188" t="s">
-        <v>115</v>
-      </c>
-      <c r="BC188">
+        <v>114</v>
+      </c>
+      <c r="BD188">
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B189" t="s">
-        <v>394</v>
+        <v>232</v>
       </c>
       <c r="T189" t="s">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="X189" t="s">
-        <v>115</v>
-      </c>
-      <c r="BC189">
+        <v>114</v>
+      </c>
+      <c r="BD189">
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B190" t="s">
-        <v>454</v>
+        <v>322</v>
       </c>
       <c r="T190" t="s">
-        <v>455</v>
-      </c>
-      <c r="X190" t="s">
-        <v>115</v>
+        <v>436</v>
       </c>
       <c r="BD190">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B191" t="s">
-        <v>233</v>
-      </c>
-      <c r="T191" t="s">
-        <v>366</v>
+        <v>113</v>
+      </c>
+      <c r="C191" t="s">
+        <v>115</v>
       </c>
       <c r="X191" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE191" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="192" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>462</v>
+      </c>
+      <c r="B192" t="s">
+        <v>275</v>
+      </c>
+      <c r="C192" t="s">
         <v>115</v>
       </c>
-      <c r="BD191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>460</v>
-      </c>
-      <c r="B192" t="s">
-        <v>323</v>
-      </c>
-      <c r="T192" t="s">
-        <v>439</v>
-      </c>
-      <c r="BD192">
-        <v>1</v>
+      <c r="X192" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE192" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="193" spans="1:57" x14ac:dyDescent="0.25">
@@ -5910,16 +5871,16 @@
         <v>463</v>
       </c>
       <c r="B193" t="s">
+        <v>400</v>
+      </c>
+      <c r="C193" t="s">
+        <v>115</v>
+      </c>
+      <c r="X193" t="s">
         <v>114</v>
       </c>
-      <c r="C193" t="s">
-        <v>116</v>
-      </c>
-      <c r="X193" t="s">
-        <v>115</v>
-      </c>
       <c r="BE193" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="194" spans="1:57" x14ac:dyDescent="0.25">
@@ -5927,16 +5888,16 @@
         <v>465</v>
       </c>
       <c r="B194" t="s">
-        <v>276</v>
+        <v>464</v>
       </c>
       <c r="C194" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X194" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BE194" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="195" spans="1:57" x14ac:dyDescent="0.25">
@@ -5944,203 +5905,206 @@
         <v>466</v>
       </c>
       <c r="B195" t="s">
-        <v>403</v>
-      </c>
-      <c r="C195" t="s">
-        <v>116</v>
+        <v>322</v>
+      </c>
+      <c r="T195" t="s">
+        <v>171</v>
       </c>
       <c r="X195" t="s">
-        <v>115</v>
-      </c>
-      <c r="BE195" t="s">
-        <v>518</v>
+        <v>114</v>
+      </c>
+      <c r="AI195" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="196" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B196" t="s">
-        <v>467</v>
-      </c>
-      <c r="C196" t="s">
-        <v>116</v>
+        <v>210</v>
       </c>
       <c r="X196" t="s">
-        <v>115</v>
-      </c>
-      <c r="BE196" t="s">
-        <v>518</v>
+        <v>114</v>
+      </c>
+      <c r="AI196" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="197" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B197" t="s">
-        <v>323</v>
+        <v>471</v>
       </c>
       <c r="T197" t="s">
-        <v>172</v>
+        <v>472</v>
       </c>
       <c r="X197" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI197" t="s">
-        <v>177</v>
+        <v>114</v>
+      </c>
+      <c r="AK197" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="198" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B198" t="s">
-        <v>211</v>
+        <v>473</v>
+      </c>
+      <c r="T198" t="s">
+        <v>363</v>
       </c>
       <c r="X198" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI198" t="s">
-        <v>177</v>
+        <v>114</v>
+      </c>
+      <c r="AK198" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="199" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B199" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="T199" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="X199" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AK199" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="200" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B200" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="T200" t="s">
-        <v>366</v>
+        <v>480</v>
       </c>
       <c r="X200" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AK200" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="201" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B201" t="s">
-        <v>479</v>
-      </c>
-      <c r="T201" t="s">
-        <v>480</v>
+        <v>210</v>
       </c>
       <c r="X201" t="s">
-        <v>115</v>
+        <v>114</v>
+      </c>
+      <c r="AI201" t="s">
+        <v>519</v>
       </c>
       <c r="AK201" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="202" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B202" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="T202" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="X202" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AK202" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="203" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B203" t="s">
-        <v>211</v>
+        <v>194</v>
+      </c>
+      <c r="M203" t="s">
+        <v>490</v>
+      </c>
+      <c r="V203">
+        <v>1</v>
       </c>
       <c r="X203" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI203" t="s">
-        <v>522</v>
-      </c>
-      <c r="AK203" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
     <row r="204" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B204" t="s">
-        <v>489</v>
+        <v>428</v>
+      </c>
+      <c r="M204" t="s">
+        <v>255</v>
       </c>
       <c r="T204" t="s">
-        <v>490</v>
+        <v>491</v>
+      </c>
+      <c r="V204">
+        <v>1</v>
       </c>
       <c r="X204" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK204" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
     <row r="205" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B205" t="s">
-        <v>195</v>
+        <v>493</v>
       </c>
       <c r="M205" t="s">
-        <v>493</v>
+        <v>167</v>
       </c>
       <c r="V205">
         <v>1</v>
       </c>
       <c r="X205" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="206" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>496</v>
+      </c>
+      <c r="B206" t="s">
         <v>495</v>
       </c>
-      <c r="B206" t="s">
-        <v>431</v>
-      </c>
-      <c r="M206" t="s">
-        <v>256</v>
+      <c r="E206" t="s">
+        <v>212</v>
+      </c>
+      <c r="G206" t="s">
+        <v>123</v>
       </c>
       <c r="T206" t="s">
-        <v>494</v>
-      </c>
-      <c r="V206">
-        <v>1</v>
+        <v>374</v>
       </c>
       <c r="X206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="207" spans="1:57" x14ac:dyDescent="0.25">
@@ -6148,233 +6112,196 @@
         <v>497</v>
       </c>
       <c r="B207" t="s">
-        <v>496</v>
-      </c>
-      <c r="M207" t="s">
-        <v>168</v>
-      </c>
-      <c r="V207">
-        <v>1</v>
+        <v>439</v>
+      </c>
+      <c r="E207" t="s">
+        <v>212</v>
+      </c>
+      <c r="G207" t="s">
+        <v>123</v>
+      </c>
+      <c r="T207" t="s">
+        <v>472</v>
       </c>
       <c r="X207" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="208" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B208" t="s">
-        <v>498</v>
+        <v>110</v>
+      </c>
+      <c r="D208" t="s">
+        <v>104</v>
       </c>
       <c r="E208" t="s">
-        <v>213</v>
-      </c>
-      <c r="G208" t="s">
-        <v>124</v>
-      </c>
-      <c r="T208" t="s">
-        <v>377</v>
+        <v>106</v>
       </c>
       <c r="X208" t="s">
-        <v>115</v>
+        <v>114</v>
+      </c>
+      <c r="AU208">
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B209" t="s">
-        <v>442</v>
+        <v>381</v>
+      </c>
+      <c r="D209" t="s">
+        <v>515</v>
       </c>
       <c r="E209" t="s">
-        <v>213</v>
-      </c>
-      <c r="G209" t="s">
-        <v>124</v>
-      </c>
-      <c r="T209" t="s">
-        <v>475</v>
+        <v>119</v>
       </c>
       <c r="X209" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="210" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="B210" t="s">
-        <v>111</v>
-      </c>
-      <c r="D210" t="s">
-        <v>105</v>
-      </c>
-      <c r="E210" t="s">
-        <v>107</v>
+        <v>455</v>
+      </c>
+      <c r="R210">
+        <v>9</v>
       </c>
       <c r="X210" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU210">
-        <v>1</v>
+        <v>294</v>
+      </c>
+      <c r="BA210" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="211" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="B211" t="s">
-        <v>384</v>
-      </c>
-      <c r="D211" t="s">
-        <v>518</v>
-      </c>
-      <c r="E211" t="s">
-        <v>120</v>
+        <v>196</v>
+      </c>
+      <c r="R211">
+        <v>9</v>
       </c>
       <c r="X211" t="s">
-        <v>115</v>
+        <v>294</v>
       </c>
     </row>
     <row r="212" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B212" t="s">
-        <v>458</v>
+        <v>166</v>
       </c>
       <c r="R212">
         <v>9</v>
       </c>
+      <c r="T212" t="s">
+        <v>411</v>
+      </c>
       <c r="X212" t="s">
-        <v>295</v>
-      </c>
-      <c r="BA212" t="s">
-        <v>308</v>
+        <v>294</v>
+      </c>
+      <c r="BD212" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="213" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B213" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="R213">
         <v>9</v>
       </c>
       <c r="X213" t="s">
-        <v>295</v>
+        <v>294</v>
+      </c>
+      <c r="AI213" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="214" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B214" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="R214">
         <v>9</v>
       </c>
       <c r="T214" t="s">
-        <v>414</v>
+        <v>132</v>
       </c>
       <c r="X214" t="s">
-        <v>295</v>
-      </c>
-      <c r="BD214" t="s">
-        <v>145</v>
+        <v>294</v>
       </c>
     </row>
     <row r="215" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B215" t="s">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="R215">
         <v>9</v>
       </c>
       <c r="X215" t="s">
-        <v>295</v>
-      </c>
-      <c r="AI215" t="s">
-        <v>191</v>
+        <v>294</v>
       </c>
     </row>
     <row r="216" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B216" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="R216">
         <v>9</v>
       </c>
       <c r="T216" t="s">
-        <v>133</v>
+        <v>389</v>
       </c>
       <c r="X216" t="s">
-        <v>295</v>
+        <v>294</v>
+      </c>
+      <c r="AI216" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="217" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="B217" t="s">
-        <v>340</v>
-      </c>
-      <c r="R217">
-        <v>9</v>
-      </c>
-      <c r="X217" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="218" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>545</v>
-      </c>
-      <c r="B218" t="s">
-        <v>176</v>
-      </c>
-      <c r="R218">
-        <v>9</v>
-      </c>
-      <c r="T218" t="s">
-        <v>392</v>
-      </c>
-      <c r="X218" t="s">
-        <v>295</v>
-      </c>
-      <c r="AI218" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="219" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>534</v>
-      </c>
-      <c r="B219" t="s">
-        <v>394</v>
-      </c>
-      <c r="M219" t="s">
-        <v>536</v>
-      </c>
-      <c r="O219" t="s">
-        <v>530</v>
-      </c>
-      <c r="T219" t="s">
-        <v>535</v>
+        <v>391</v>
+      </c>
+      <c r="M217" t="s">
+        <v>533</v>
+      </c>
+      <c r="O217" t="s">
+        <v>527</v>
+      </c>
+      <c r="T217" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BE219" xr:uid="{EA5A6498-8735-4638-A034-733AD69F003F}"/>
+  <autoFilter ref="A1:BE217" xr:uid="{EA5A6498-8735-4638-A034-733AD69F003F}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6388,147 +6315,147 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/Sistemi_sablon_radni.xlsx
+++ b/Sistemi_sablon_radni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andra\PycharmProjects\Horses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019F828A-D975-4279-B96B-5100B45157DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756543D8-E0D7-4C59-920A-45550E134E65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18600" yWindow="0" windowWidth="20880" windowHeight="8430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BE$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BE$210</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="538">
   <si>
     <t>System</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Sys23</t>
   </si>
   <si>
-    <t>Sys24</t>
-  </si>
-  <si>
     <t>Sys25</t>
   </si>
   <si>
@@ -253,18 +250,12 @@
     <t>Sys67</t>
   </si>
   <si>
-    <t>Sys68</t>
-  </si>
-  <si>
     <t>Sys69</t>
   </si>
   <si>
     <t>Sys70</t>
   </si>
   <si>
-    <t>Sys71</t>
-  </si>
-  <si>
     <t>Sys73</t>
   </si>
   <si>
@@ -634,9 +625,6 @@
     <t>Beverley, Hamilton, Carlisle</t>
   </si>
   <si>
-    <t>Redcar, Ayr, Yarmouth, York, Doncaster, Ffos Las, Nottingham, Haydock, Newbury, Wetherby</t>
-  </si>
-  <si>
     <t>Ollie Pears</t>
   </si>
   <si>
@@ -646,9 +634,6 @@
     <t>&lt; -10</t>
   </si>
   <si>
-    <t>between 14 and 29</t>
-  </si>
-  <si>
     <t>Newmarket, Newmarket (July)</t>
   </si>
   <si>
@@ -814,9 +799,6 @@
     <t>between 5 and 6</t>
   </si>
   <si>
-    <t>&lt;-40</t>
-  </si>
-  <si>
     <t>&lt;-1</t>
   </si>
   <si>
@@ -862,9 +844,6 @@
     <t>Sys117</t>
   </si>
   <si>
-    <t>Sys118</t>
-  </si>
-  <si>
     <t>Sys120</t>
   </si>
   <si>
@@ -1006,9 +985,6 @@
     <t>Sys150</t>
   </si>
   <si>
-    <t>Sys151</t>
-  </si>
-  <si>
     <t>Sys152</t>
   </si>
   <si>
@@ -1084,9 +1060,6 @@
     <t>Rank_Track_1</t>
   </si>
   <si>
-    <t>Sys167</t>
-  </si>
-  <si>
     <t>Sys168</t>
   </si>
   <si>
@@ -1250,9 +1223,6 @@
   </si>
   <si>
     <t>Sys208</t>
-  </si>
-  <si>
-    <t>Sys209</t>
   </si>
   <si>
     <t>Sys210</t>
@@ -1704,7 +1674,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1714,6 +1684,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1750,7 +1726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1766,6 +1742,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2080,7 +2060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE217"/>
+  <dimension ref="A1:BE210"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -2143,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -2158,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
@@ -2167,28 +2147,28 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>7</v>
@@ -2197,13 +2177,13 @@
         <v>8</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="W1" s="5" t="s">
         <v>10</v>
@@ -2212,158 +2192,159 @@
         <v>11</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="AH1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="AJ1" s="5" t="s">
         <v>14</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AL1" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="AM1" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR1" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="AS1" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="AT1" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="AU1" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="AV1" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="AX1" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="AY1" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="AZ1" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="BA1" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB1" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="AM1" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="AN1" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="AO1" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="AP1" s="5" t="s">
+      <c r="BC1" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="BD1" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="BE1" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="AQ1" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="AR1" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="AS1" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="AT1" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="AU1" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="AV1" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="AW1" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="AX1" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="AY1" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="AZ1" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="BA1" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="BB1" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="BC1" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="BD1" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="BE1" s="5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="9">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>104</v>
-      </c>
+      <c r="D2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="X3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Z3" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="AX3" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="AY3" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
@@ -2371,25 +2352,25 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="W4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Z4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="AU4" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="AY4" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
@@ -2397,7 +2378,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2406,56 +2387,58 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C6" t="s">
+      <c r="N6" s="10"/>
+      <c r="Q6" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="D7" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>112</v>
-      </c>
-      <c r="R7" t="s">
-        <v>258</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>515</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>528</v>
+      <c r="E7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="N7" s="10"/>
+      <c r="Q7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="AU7" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AY7" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
@@ -2463,25 +2446,25 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="E8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="S8">
         <v>1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AL8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
@@ -2489,22 +2472,22 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O9" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="R9">
         <v>8</v>
       </c>
       <c r="T9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
@@ -2512,22 +2495,22 @@
         <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="M10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O10" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="U10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="V10" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AA10" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
@@ -2535,25 +2518,25 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="W11">
         <v>3</v>
       </c>
       <c r="X11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AU11" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
@@ -2561,22 +2544,22 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="X12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
@@ -2584,28 +2567,28 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="W13">
         <v>3</v>
       </c>
       <c r="X13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Y13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AA13" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
@@ -2613,22 +2596,22 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="X14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Z14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AA14" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
@@ -2636,28 +2619,28 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="T15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="X15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AA15" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
@@ -2665,22 +2648,22 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="O16" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="R16" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="T16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="W16">
         <v>3</v>
@@ -2691,19 +2674,19 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="X17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AE17" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
@@ -2711,16 +2694,16 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="X18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
@@ -2728,13 +2711,13 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O19" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
@@ -2742,19 +2725,19 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N20" s="1">
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="P20" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF20" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
@@ -2762,25 +2745,25 @@
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N21" s="1">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="S21">
         <v>1</v>
       </c>
       <c r="U21" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AF21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2788,242 +2771,243 @@
         <v>35</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="N22" s="3">
         <v>6</v>
       </c>
       <c r="O22" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="P22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY22" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
         <v>143</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AF22" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AY22" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="23" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="N23" s="3"/>
-      <c r="O23" t="s">
-        <v>527</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ23" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>226</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="X23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG23">
+        <v>100</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:51" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="G24" t="s">
-        <v>231</v>
+        <v>145</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O24" t="s">
+        <v>517</v>
       </c>
       <c r="V24">
         <v>1</v>
       </c>
-      <c r="X24" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG24">
-        <v>100</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="25" spans="1:51" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="AH24" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:51" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B25" t="s">
-        <v>148</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O25" t="s">
-        <v>527</v>
-      </c>
-      <c r="V25">
+      <c r="B25" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="N25" s="10"/>
+      <c r="O25" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="V25" s="9">
         <v>1</v>
       </c>
-      <c r="AH25" t="s">
-        <v>254</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="26" spans="1:51" ht="60" x14ac:dyDescent="0.25">
+      <c r="AH25" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM25" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>147</v>
       </c>
       <c r="O26" t="s">
-        <v>527</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>254</v>
-      </c>
-      <c r="AM26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="27" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="O27" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="28" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="O28" t="s">
+        <v>517</v>
+      </c>
+      <c r="AY28" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="29" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="N29" s="10"/>
+      <c r="O29" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="30" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="M30" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="M28" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="O28" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" t="s">
-        <v>135</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O29" t="s">
-        <v>527</v>
-      </c>
-      <c r="AY29" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O30" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="N30" s="10"/>
+      <c r="O30" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="31" spans="1:51" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>44</v>
       </c>
       <c r="B31" t="s">
+        <v>154</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O31" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="32" spans="1:51" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="N32" s="10"/>
+      <c r="O32" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O31" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="32" spans="1:51" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" t="s">
-        <v>157</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O32" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="33" spans="1:35" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
-        <v>158</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O33" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="34" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+      <c r="M33" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="N33" s="10"/>
+      <c r="O33" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="O34" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.25">
@@ -3033,28 +3017,33 @@
       <c r="B35" t="s">
         <v>110</v>
       </c>
+      <c r="C35" t="s">
+        <v>159</v>
+      </c>
       <c r="M35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O35" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="O35" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" t="s">
-        <v>162</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O36" t="s">
-        <v>527</v>
+      <c r="C36" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="U36" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.25">
@@ -3062,17 +3051,20 @@
         <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
-      </c>
-      <c r="C37" t="s">
-        <v>515</v>
+        <v>110</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
       </c>
       <c r="M37" s="1"/>
       <c r="O37" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="U37" t="s">
-        <v>141</v>
+        <v>162</v>
+      </c>
+      <c r="V37" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
@@ -3080,20 +3072,17 @@
         <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="M38" s="1"/>
       <c r="O38" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="U38" t="s">
-        <v>165</v>
-      </c>
-      <c r="V38" t="s">
-        <v>515</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.25">
@@ -3101,17 +3090,20 @@
         <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="M39" s="1"/>
       <c r="O39" t="s">
-        <v>527</v>
+        <v>517</v>
+      </c>
+      <c r="T39" t="s">
+        <v>131</v>
       </c>
       <c r="U39" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.25">
@@ -3119,20 +3111,16 @@
         <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1"/>
+        <v>165</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="O40" t="s">
-        <v>527</v>
-      </c>
-      <c r="T40" t="s">
-        <v>134</v>
+        <v>517</v>
       </c>
       <c r="U40" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.25">
@@ -3140,16 +3128,16 @@
         <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
-      </c>
-      <c r="M41" s="1" t="s">
         <v>167</v>
       </c>
+      <c r="M41" t="s">
+        <v>166</v>
+      </c>
       <c r="O41" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="U41" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.25">
@@ -3157,33 +3145,34 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="M42" t="s">
+        <v>201</v>
+      </c>
+      <c r="T42" t="s">
+        <v>168</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="N43" s="10"/>
+      <c r="O43" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T43" s="9" t="s">
         <v>170</v>
-      </c>
-      <c r="M42" t="s">
-        <v>169</v>
-      </c>
-      <c r="O42" t="s">
-        <v>527</v>
-      </c>
-      <c r="U42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" t="s">
-        <v>105</v>
-      </c>
-      <c r="M43" t="s">
-        <v>206</v>
-      </c>
-      <c r="T43" t="s">
-        <v>171</v>
-      </c>
-      <c r="V43">
-        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.25">
@@ -3193,13 +3182,13 @@
       <c r="B44" t="s">
         <v>172</v>
       </c>
-      <c r="C44" t="s">
-        <v>162</v>
+      <c r="M44" t="s">
+        <v>171</v>
       </c>
       <c r="O44" t="s">
-        <v>527</v>
-      </c>
-      <c r="T44" t="s">
+        <v>517</v>
+      </c>
+      <c r="AI44" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3208,16 +3197,16 @@
         <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="M45" t="s">
         <v>174</v>
       </c>
-      <c r="O45" t="s">
-        <v>527</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>176</v>
+      <c r="T45" t="s">
+        <v>168</v>
+      </c>
+      <c r="V45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.25">
@@ -3225,16 +3214,13 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
-      </c>
-      <c r="M46" t="s">
-        <v>177</v>
-      </c>
-      <c r="T46" t="s">
-        <v>171</v>
-      </c>
-      <c r="V46">
-        <v>1</v>
+        <v>175</v>
+      </c>
+      <c r="O46" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.25">
@@ -3242,13 +3228,13 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O47" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="Z47" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.25">
@@ -3256,13 +3242,16 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>106</v>
       </c>
       <c r="O48" t="s">
-        <v>527</v>
+        <v>517</v>
+      </c>
+      <c r="T48" t="s">
+        <v>131</v>
       </c>
       <c r="Z48" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
@@ -3270,16 +3259,16 @@
         <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
-      </c>
-      <c r="O49" t="s">
-        <v>527</v>
+        <v>169</v>
       </c>
       <c r="T49" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z49" t="s">
+        <v>170</v>
+      </c>
+      <c r="X49" t="s">
         <v>179</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
@@ -3287,16 +3276,13 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>167</v>
+      </c>
+      <c r="O50" t="s">
+        <v>517</v>
       </c>
       <c r="T50" t="s">
-        <v>173</v>
-      </c>
-      <c r="X50" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
@@ -3304,112 +3290,123 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>182</v>
+      </c>
+      <c r="E51" t="s">
+        <v>116</v>
       </c>
       <c r="O51" t="s">
-        <v>527</v>
-      </c>
-      <c r="T51" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="52" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="E52" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="N52" s="10"/>
+      <c r="O52" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="53" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E52" t="s">
-        <v>119</v>
-      </c>
-      <c r="O52" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="F53" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E53" t="s">
+      <c r="N53" s="10"/>
+      <c r="O53" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AI53" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="O53" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    </row>
+    <row r="54" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="N54" s="10"/>
+      <c r="O54" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="U54" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F54" t="s">
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
         <v>189</v>
       </c>
-      <c r="O54" t="s">
-        <v>527</v>
-      </c>
-      <c r="AI54" t="s">
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>517</v>
+      </c>
+      <c r="U55" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" t="s">
-        <v>515</v>
-      </c>
-      <c r="O55" t="s">
-        <v>527</v>
-      </c>
-      <c r="U55" t="s">
+    <row r="56" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" s="9">
+        <v>2</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="N56" s="10"/>
+      <c r="X56" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF56" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C56">
+    </row>
+    <row r="57" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57" s="9">
         <v>1</v>
       </c>
-      <c r="O56" t="s">
-        <v>527</v>
-      </c>
-      <c r="U56" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>70</v>
-      </c>
-      <c r="B57" t="s">
-        <v>194</v>
-      </c>
-      <c r="C57">
-        <v>2</v>
-      </c>
-      <c r="I57" t="s">
-        <v>111</v>
-      </c>
-      <c r="X57" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF57" t="s">
-        <v>195</v>
+      <c r="I57" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="N57" s="10"/>
+      <c r="X57" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF57" s="9" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
@@ -3417,42 +3414,46 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>111</v>
+        <v>108</v>
+      </c>
+      <c r="W58">
+        <v>3</v>
       </c>
       <c r="X58" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="AF58" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B59" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59">
+      <c r="B59" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" s="9">
         <v>1</v>
       </c>
-      <c r="I59" t="s">
-        <v>111</v>
-      </c>
-      <c r="W59">
-        <v>3</v>
-      </c>
-      <c r="X59" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF59" t="s">
-        <v>195</v>
+      <c r="I59" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="N59" s="10"/>
+      <c r="X59" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF59" s="9" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
@@ -3460,42 +3461,37 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>164</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="I60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D60" t="s">
+        <v>101</v>
+      </c>
+      <c r="G60" t="s">
+        <v>186</v>
+      </c>
+      <c r="M60" t="s">
+        <v>152</v>
+      </c>
+      <c r="X60" t="s">
         <v>111</v>
       </c>
-      <c r="M60" t="s">
-        <v>200</v>
-      </c>
-      <c r="X60" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="61" spans="1:35" ht="60" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    </row>
+    <row r="61" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B61" t="s">
-        <v>113</v>
-      </c>
-      <c r="I61" t="s">
-        <v>111</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="X61" t="s">
+      <c r="B61" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="M61" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="AF61" t="s">
-        <v>195</v>
+      <c r="N61" s="10"/>
+      <c r="X61" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
@@ -3503,19 +3499,16 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>202</v>
-      </c>
-      <c r="D62" t="s">
-        <v>104</v>
-      </c>
-      <c r="G62" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="M62" t="s">
-        <v>155</v>
-      </c>
-      <c r="X62" t="s">
-        <v>114</v>
+        <v>201</v>
+      </c>
+      <c r="O62" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
@@ -3523,16 +3516,16 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
-      </c>
-      <c r="G63" t="s">
-        <v>189</v>
-      </c>
-      <c r="M63" t="s">
-        <v>200</v>
-      </c>
-      <c r="X63" t="s">
-        <v>197</v>
+        <v>175</v>
+      </c>
+      <c r="O63" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
@@ -3540,1084 +3533,1132 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
-      </c>
-      <c r="E64" t="s">
+        <v>165</v>
+      </c>
+      <c r="X64" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z64">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:47" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F64" t="s">
-        <v>204</v>
-      </c>
-      <c r="O64" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>78</v>
-      </c>
-      <c r="B65" t="s">
-        <v>170</v>
-      </c>
-      <c r="M65" t="s">
-        <v>206</v>
-      </c>
-      <c r="O65" t="s">
-        <v>527</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="N65" s="10"/>
+      <c r="X65" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z65" s="9">
+        <v>100</v>
+      </c>
+      <c r="AI65" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>178</v>
-      </c>
-      <c r="O66" t="s">
-        <v>527</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB66" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="E66" t="s">
+        <v>207</v>
+      </c>
+      <c r="X66" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB66">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>168</v>
+        <v>208</v>
+      </c>
+      <c r="E67" t="s">
+        <v>207</v>
       </c>
       <c r="X67" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z67">
+        <v>116</v>
+      </c>
+      <c r="AB67">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>81</v>
       </c>
       <c r="B68" t="s">
+        <v>175</v>
+      </c>
+      <c r="C68" t="s">
+        <v>209</v>
+      </c>
+      <c r="N68" s="1">
+        <v>6</v>
+      </c>
+      <c r="O68" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="69" spans="1:47" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="M69" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="X68" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z68">
-        <v>100</v>
-      </c>
-      <c r="AI68" t="s">
+      <c r="N69" s="10"/>
+      <c r="O69" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z69" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>82</v>
-      </c>
-      <c r="B69" t="s">
-        <v>211</v>
-      </c>
-      <c r="E69" t="s">
-        <v>212</v>
-      </c>
-      <c r="X69" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB69">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="70" spans="1:47" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B70" t="s">
-        <v>213</v>
-      </c>
-      <c r="E70" t="s">
-        <v>212</v>
-      </c>
-      <c r="X70" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB70">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B70" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="N70" s="10"/>
+      <c r="X70" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK70" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:47" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B71" t="s">
-        <v>178</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="B71" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D71" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="N71" s="1">
-        <v>6</v>
-      </c>
-      <c r="O71" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="N71" s="10"/>
+      <c r="X71" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK71" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>216</v>
-      </c>
-      <c r="C72" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>218</v>
-      </c>
-      <c r="M72" t="s">
-        <v>215</v>
-      </c>
-      <c r="O72" t="s">
-        <v>527</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="X72" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK72" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" t="s">
-        <v>219</v>
+        <v>135</v>
+      </c>
+      <c r="G73" t="s">
+        <v>120</v>
       </c>
       <c r="X73" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK73" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="74" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D74" t="s">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="X74" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AK74" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>210</v>
-      </c>
-      <c r="D75" t="s">
-        <v>219</v>
+        <v>117</v>
+      </c>
+      <c r="N75" s="1">
+        <v>5</v>
       </c>
       <c r="X75" t="s">
-        <v>197</v>
+        <v>111</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>103</v>
       </c>
       <c r="AK75" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>138</v>
-      </c>
-      <c r="G76" t="s">
-        <v>123</v>
+        <v>205</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="X76" t="s">
-        <v>197</v>
+        <v>111</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>103</v>
       </c>
       <c r="AK76" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="1:47" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B77" t="s">
-        <v>221</v>
-      </c>
-      <c r="D77" t="s">
-        <v>115</v>
-      </c>
-      <c r="X77" t="s">
-        <v>197</v>
-      </c>
-      <c r="AK77" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B77" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="N77" s="10"/>
+      <c r="V77" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="X77" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC77" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="AJ77" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK77" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:47" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="N78" s="10"/>
+      <c r="O78" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK78" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="N78" s="1">
-        <v>5</v>
-      </c>
-      <c r="X78" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>106</v>
-      </c>
-      <c r="AK78" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AU78" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>210</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>260</v>
+        <v>228</v>
+      </c>
+      <c r="V79">
+        <v>1</v>
       </c>
       <c r="X79" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>106</v>
+        <v>111</v>
+      </c>
+      <c r="AD79">
+        <v>100</v>
       </c>
       <c r="AK79" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="80" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
-      </c>
-      <c r="C80" t="s">
-        <v>140</v>
-      </c>
-      <c r="V80" t="s">
-        <v>115</v>
+        <v>145</v>
+      </c>
+      <c r="V80">
+        <v>1</v>
       </c>
       <c r="X80" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC80" t="s">
-        <v>228</v>
-      </c>
-      <c r="AJ80" t="s">
-        <v>208</v>
+        <v>111</v>
+      </c>
+      <c r="AD80">
+        <v>100</v>
       </c>
       <c r="AK80" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B81" t="s">
-        <v>131</v>
-      </c>
-      <c r="O81" t="s">
-        <v>527</v>
-      </c>
-      <c r="AK81" t="s">
-        <v>123</v>
-      </c>
-      <c r="AU81">
+      <c r="B81" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="N81" s="10"/>
+      <c r="V81" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="X81" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD81" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AK81" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B82" t="s">
-        <v>233</v>
-      </c>
-      <c r="V82">
-        <v>1</v>
-      </c>
-      <c r="X82" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD82">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="83" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="B82" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="N82" s="10"/>
+      <c r="X82" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK82" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>96</v>
       </c>
       <c r="B83" t="s">
-        <v>148</v>
-      </c>
-      <c r="V83">
+        <v>172</v>
+      </c>
+      <c r="C83" t="s">
+        <v>505</v>
+      </c>
+      <c r="X83" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>226</v>
+      </c>
+      <c r="AI83" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C84" s="9">
         <v>1</v>
       </c>
-      <c r="X83" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD83">
-        <v>100</v>
-      </c>
-      <c r="AK83" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="84" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>97</v>
-      </c>
-      <c r="B84" t="s">
-        <v>235</v>
-      </c>
-      <c r="V84">
-        <v>1</v>
-      </c>
-      <c r="X84" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD84" t="s">
-        <v>515</v>
-      </c>
-      <c r="AK84" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="N84" s="10"/>
+      <c r="X84" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI84" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="E85" t="s">
-        <v>236</v>
+        <v>196</v>
+      </c>
+      <c r="T85" t="s">
+        <v>234</v>
+      </c>
+      <c r="U85" t="s">
+        <v>138</v>
+      </c>
+      <c r="V85" t="s">
+        <v>235</v>
       </c>
       <c r="X85" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK85" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>99</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
-      </c>
-      <c r="C86" t="s">
-        <v>515</v>
+        <v>121</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>247</v>
+      </c>
+      <c r="W86">
+        <v>3</v>
       </c>
       <c r="X86" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y86" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA86" t="s">
-        <v>231</v>
+        <v>126</v>
+      </c>
+      <c r="AE86" t="s">
+        <v>519</v>
       </c>
       <c r="AI86" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="B87" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" t="s">
+        <v>213</v>
+      </c>
+      <c r="G87" t="s">
+        <v>120</v>
+      </c>
+      <c r="X87" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>218</v>
+      </c>
+      <c r="B88" t="s">
+        <v>236</v>
+      </c>
+      <c r="D88" t="s">
+        <v>213</v>
+      </c>
+      <c r="G88" t="s">
+        <v>120</v>
+      </c>
+      <c r="M88" t="s">
+        <v>157</v>
+      </c>
+      <c r="X88" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="X87" t="s">
-        <v>197</v>
-      </c>
-      <c r="AI87" t="s">
+      <c r="D89" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="N89" s="10"/>
+      <c r="X89" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" s="9" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>101</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="C90" s="9">
+        <v>2</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N90" s="10"/>
+      <c r="X90" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>221</v>
+      </c>
+      <c r="B91" t="s">
+        <v>240</v>
+      </c>
+      <c r="E91" t="s">
+        <v>111</v>
+      </c>
+      <c r="F91" t="s">
+        <v>239</v>
+      </c>
+      <c r="W91" t="s">
+        <v>225</v>
+      </c>
+      <c r="X91" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="N92" s="10"/>
+      <c r="W92" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="X92" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="N93" s="10"/>
+      <c r="X93" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK93" s="9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>258</v>
+      </c>
+      <c r="B94" t="s">
         <v>216</v>
       </c>
-      <c r="E88" t="s">
-        <v>199</v>
-      </c>
-      <c r="T88" t="s">
-        <v>239</v>
-      </c>
-      <c r="U88" t="s">
-        <v>141</v>
-      </c>
-      <c r="V88" t="s">
-        <v>240</v>
-      </c>
-      <c r="X88" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>102</v>
-      </c>
-      <c r="B89" t="s">
-        <v>124</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="H89" t="s">
-        <v>252</v>
-      </c>
-      <c r="W89">
-        <v>3</v>
-      </c>
-      <c r="X89" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE89" t="s">
-        <v>529</v>
-      </c>
-      <c r="AI89" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>222</v>
-      </c>
-      <c r="B90" t="s">
-        <v>122</v>
-      </c>
-      <c r="D90" t="s">
-        <v>218</v>
-      </c>
-      <c r="G90" t="s">
-        <v>123</v>
-      </c>
-      <c r="X90" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>223</v>
-      </c>
-      <c r="B91" t="s">
-        <v>241</v>
-      </c>
-      <c r="D91" t="s">
-        <v>218</v>
-      </c>
-      <c r="G91" t="s">
-        <v>123</v>
-      </c>
-      <c r="M91" t="s">
-        <v>160</v>
-      </c>
-      <c r="X91" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>224</v>
-      </c>
-      <c r="B92" t="s">
-        <v>242</v>
-      </c>
-      <c r="D92" t="s">
-        <v>218</v>
-      </c>
-      <c r="E92" t="s">
-        <v>348</v>
-      </c>
-      <c r="G92" t="s">
-        <v>123</v>
-      </c>
-      <c r="X92" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>225</v>
-      </c>
-      <c r="B93" t="s">
-        <v>243</v>
-      </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="F93" t="s">
-        <v>244</v>
-      </c>
-      <c r="X93" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="94" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>226</v>
-      </c>
-      <c r="B94" t="s">
-        <v>245</v>
-      </c>
-      <c r="E94" t="s">
-        <v>114</v>
-      </c>
-      <c r="F94" t="s">
-        <v>244</v>
-      </c>
-      <c r="W94" t="s">
-        <v>230</v>
-      </c>
       <c r="X94" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="95" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>227</v>
-      </c>
-      <c r="B95" t="s">
-        <v>246</v>
-      </c>
-      <c r="E95" t="s">
-        <v>119</v>
-      </c>
-      <c r="F95" t="s">
-        <v>204</v>
-      </c>
-      <c r="W95" t="s">
-        <v>230</v>
-      </c>
-      <c r="X95" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="AK94" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="M95" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="N95" s="10"/>
+      <c r="O95" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="V95" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="AL95" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>263</v>
       </c>
       <c r="B96" t="s">
-        <v>232</v>
-      </c>
-      <c r="X96" t="s">
-        <v>119</v>
-      </c>
-      <c r="AK96" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="T96" t="s">
+        <v>264</v>
+      </c>
+      <c r="V96">
+        <v>1</v>
+      </c>
+      <c r="AD96">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
-      </c>
-      <c r="X97" t="s">
-        <v>119</v>
-      </c>
-      <c r="AK97" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="M97" t="s">
+        <v>267</v>
+      </c>
+      <c r="V97" t="s">
+        <v>505</v>
+      </c>
+      <c r="W97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>265</v>
-      </c>
-      <c r="C98" t="s">
-        <v>115</v>
-      </c>
-      <c r="E98" t="s">
-        <v>267</v>
-      </c>
-      <c r="M98" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="B98" t="s">
+        <v>240</v>
       </c>
       <c r="O98" t="s">
-        <v>527</v>
-      </c>
-      <c r="V98" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL98" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="W98">
+        <v>5</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="99" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>270</v>
+      </c>
+      <c r="B99" t="s">
         <v>269</v>
       </c>
-      <c r="B99" t="s">
-        <v>148</v>
-      </c>
-      <c r="T99" t="s">
-        <v>270</v>
-      </c>
-      <c r="V99">
-        <v>1</v>
-      </c>
-      <c r="AD99">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="W99">
+        <v>5</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="100" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>271</v>
       </c>
       <c r="B100" t="s">
         <v>272</v>
       </c>
-      <c r="M100" t="s">
+      <c r="K100" t="s">
+        <v>186</v>
+      </c>
+      <c r="O100" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="101" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>273</v>
       </c>
-      <c r="V100" t="s">
-        <v>515</v>
-      </c>
-      <c r="W100">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
         <v>274</v>
       </c>
-      <c r="B101" t="s">
-        <v>245</v>
+      <c r="K101" t="s">
+        <v>186</v>
       </c>
       <c r="O101" t="s">
-        <v>527</v>
-      </c>
-      <c r="W101">
-        <v>5</v>
-      </c>
-      <c r="AC101" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="102" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>276</v>
       </c>
       <c r="B102" t="s">
         <v>275</v>
       </c>
-      <c r="W102">
-        <v>5</v>
-      </c>
-      <c r="AC102" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="E102" t="s">
+        <v>113</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="O102" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="103" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>277</v>
       </c>
       <c r="B103" t="s">
-        <v>203</v>
+        <v>278</v>
+      </c>
+      <c r="E103" t="s">
+        <v>113</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
       </c>
       <c r="O103" t="s">
-        <v>527</v>
-      </c>
-      <c r="W103">
-        <v>5</v>
-      </c>
-      <c r="AC103" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="T103" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="104" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B104" t="s">
-        <v>279</v>
-      </c>
-      <c r="K104" t="s">
-        <v>189</v>
+        <v>280</v>
+      </c>
+      <c r="E104" t="s">
+        <v>113</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
       </c>
       <c r="O104" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>280</v>
-      </c>
-      <c r="B105" t="s">
-        <v>281</v>
-      </c>
-      <c r="K105" t="s">
-        <v>189</v>
-      </c>
-      <c r="O105" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="105" spans="1:37" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I105" s="9">
+        <v>2</v>
+      </c>
+      <c r="N105" s="10"/>
+      <c r="O105" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="106" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B106" t="s">
-        <v>282</v>
-      </c>
-      <c r="E106" t="s">
-        <v>116</v>
-      </c>
-      <c r="I106">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="O106" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="W106">
+        <v>3</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI106" t="s">
+        <v>187</v>
+      </c>
+      <c r="AK106" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B107" t="s">
-        <v>285</v>
-      </c>
-      <c r="E107" t="s">
-        <v>116</v>
-      </c>
-      <c r="I107">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="O107" t="s">
-        <v>527</v>
-      </c>
-      <c r="T107" t="s">
+        <v>517</v>
+      </c>
+      <c r="W107">
+        <v>3</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI107" t="s">
+        <v>187</v>
+      </c>
+      <c r="AK107" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="108" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
+        <v>107</v>
+      </c>
+      <c r="E108" t="s">
+        <v>287</v>
+      </c>
+      <c r="O108" t="s">
+        <v>517</v>
+      </c>
+      <c r="S108" t="s">
+        <v>120</v>
+      </c>
+      <c r="W108" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="109" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>288</v>
       </c>
-      <c r="B108" t="s">
-        <v>287</v>
-      </c>
-      <c r="E108" t="s">
-        <v>116</v>
-      </c>
-      <c r="I108">
-        <v>2</v>
-      </c>
-      <c r="O108" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B109" t="s">
+        <v>205</v>
+      </c>
+      <c r="S109" t="s">
+        <v>226</v>
+      </c>
+      <c r="U109" t="s">
+        <v>138</v>
+      </c>
+      <c r="X109" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI109" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="110" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>289</v>
+      </c>
+      <c r="B110" t="s">
+        <v>272</v>
+      </c>
+      <c r="H110" t="s">
         <v>290</v>
       </c>
-      <c r="B109" t="s">
-        <v>289</v>
-      </c>
-      <c r="E109" t="s">
-        <v>116</v>
-      </c>
-      <c r="I109">
-        <v>2</v>
-      </c>
-      <c r="O109" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="O110" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE110" t="s">
+        <v>519</v>
+      </c>
+      <c r="AI110" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="111" spans="1:37" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B111" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="B110" t="s">
-        <v>113</v>
-      </c>
-      <c r="O110" t="s">
-        <v>527</v>
-      </c>
-      <c r="W110">
-        <v>3</v>
-      </c>
-      <c r="AC110" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI110" t="s">
-        <v>190</v>
-      </c>
-      <c r="AK110" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>292</v>
-      </c>
-      <c r="B111" t="s">
-        <v>156</v>
-      </c>
-      <c r="O111" t="s">
-        <v>527</v>
-      </c>
-      <c r="W111">
-        <v>3</v>
-      </c>
-      <c r="AC111" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI111" t="s">
-        <v>190</v>
-      </c>
-      <c r="AK111" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="H111" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="N111" s="10"/>
+      <c r="O111" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE111" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="AI111" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="112" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>293</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
-      </c>
-      <c r="E112" t="s">
-        <v>294</v>
+        <v>175</v>
       </c>
       <c r="O112" t="s">
-        <v>527</v>
-      </c>
-      <c r="S112" t="s">
-        <v>123</v>
-      </c>
-      <c r="W112" t="s">
-        <v>140</v>
+        <v>517</v>
+      </c>
+      <c r="V112" t="s">
+        <v>235</v>
+      </c>
+      <c r="AJ112">
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B113" t="s">
-        <v>210</v>
-      </c>
-      <c r="S113" t="s">
-        <v>231</v>
-      </c>
-      <c r="U113" t="s">
-        <v>141</v>
-      </c>
-      <c r="X113" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI113" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="114" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+        <v>107</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK113" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="114" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B114" t="s">
-        <v>279</v>
-      </c>
-      <c r="H114" t="s">
+      <c r="B114" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="N114" s="10"/>
+      <c r="X114" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y114" s="9" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="115" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="O114" t="s">
-        <v>527</v>
-      </c>
-      <c r="AE114" t="s">
-        <v>529</v>
-      </c>
-      <c r="AI114" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="115" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B115" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="N115" s="10"/>
+      <c r="V115" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="X115" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B115" t="s">
-        <v>298</v>
-      </c>
-      <c r="H115" t="s">
-        <v>297</v>
-      </c>
-      <c r="O115" t="s">
-        <v>527</v>
-      </c>
-      <c r="AE115" t="s">
-        <v>529</v>
-      </c>
-      <c r="AI115" t="s">
-        <v>520</v>
+      <c r="Y115" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="AH115" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="116" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>300</v>
-      </c>
-      <c r="B116" t="s">
-        <v>178</v>
+        <v>310</v>
+      </c>
+      <c r="C116" t="s">
+        <v>137</v>
+      </c>
+      <c r="I116" t="s">
+        <v>137</v>
       </c>
       <c r="O116" t="s">
-        <v>527</v>
-      </c>
-      <c r="V116" t="s">
-        <v>240</v>
-      </c>
-      <c r="AJ116">
+        <v>517</v>
+      </c>
+      <c r="R116" t="s">
+        <v>311</v>
+      </c>
+      <c r="AU116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>301</v>
-      </c>
-      <c r="B117" t="s">
-        <v>110</v>
-      </c>
-      <c r="I117">
+    <row r="117" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N117" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="O117" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="S117" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="U117" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB117" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AG117" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="AH117" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="AU117" s="9">
         <v>1</v>
-      </c>
-      <c r="O117" t="s">
-        <v>527</v>
-      </c>
-      <c r="AK117" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B118" t="s">
-        <v>285</v>
-      </c>
-      <c r="D118" t="s">
-        <v>115</v>
-      </c>
-      <c r="E118" t="s">
-        <v>187</v>
+        <v>315</v>
+      </c>
+      <c r="N118" s="1">
+        <v>6</v>
       </c>
       <c r="X118" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y118" t="s">
-        <v>525</v>
+        <v>111</v>
+      </c>
+      <c r="AU118">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>304</v>
-      </c>
-      <c r="B119" t="s">
-        <v>305</v>
-      </c>
-      <c r="V119" t="s">
-        <v>115</v>
-      </c>
-      <c r="X119" t="s">
-        <v>306</v>
-      </c>
-      <c r="Y119" t="s">
-        <v>525</v>
-      </c>
-      <c r="AH119" t="s">
-        <v>106</v>
+        <v>316</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>101</v>
+      </c>
+      <c r="G119" t="s">
+        <v>111</v>
+      </c>
+      <c r="O119" t="s">
+        <v>517</v>
+      </c>
+      <c r="R119" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB119" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>223</v>
+      </c>
+      <c r="AU119">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>317</v>
       </c>
-      <c r="C120" t="s">
-        <v>140</v>
+      <c r="D120" t="s">
+        <v>101</v>
       </c>
       <c r="I120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O120" t="s">
-        <v>527</v>
-      </c>
-      <c r="R120" t="s">
-        <v>318</v>
-      </c>
-      <c r="AU120">
+        <v>517</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO120" t="s">
+        <v>209</v>
+      </c>
+      <c r="AP120">
         <v>1</v>
+      </c>
+      <c r="AU120" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="121" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>319</v>
-      </c>
-      <c r="G121" t="s">
-        <v>114</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>144</v>
+        <v>318</v>
+      </c>
+      <c r="D121" t="s">
+        <v>101</v>
       </c>
       <c r="O121" t="s">
-        <v>527</v>
-      </c>
-      <c r="S121" t="s">
-        <v>140</v>
-      </c>
-      <c r="U121" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB121" t="s">
-        <v>515</v>
-      </c>
-      <c r="AG121" t="s">
-        <v>320</v>
-      </c>
-      <c r="AH121" t="s">
-        <v>320</v>
+        <v>517</v>
+      </c>
+      <c r="AJ121" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL121" t="s">
+        <v>226</v>
+      </c>
+      <c r="AP121" t="s">
+        <v>300</v>
+      </c>
+      <c r="AR121" t="s">
+        <v>300</v>
       </c>
       <c r="AU121">
         <v>1</v>
@@ -4625,1683 +4666,1560 @@
     </row>
     <row r="122" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>321</v>
-      </c>
-      <c r="B122" t="s">
-        <v>322</v>
-      </c>
-      <c r="N122" s="1">
-        <v>6</v>
-      </c>
-      <c r="X122" t="s">
-        <v>114</v>
+        <v>319</v>
+      </c>
+      <c r="D122" t="s">
+        <v>101</v>
+      </c>
+      <c r="O122" t="s">
+        <v>517</v>
+      </c>
+      <c r="AJ122" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL122" t="s">
+        <v>226</v>
+      </c>
+      <c r="AP122" t="s">
+        <v>300</v>
+      </c>
+      <c r="AR122" t="s">
+        <v>300</v>
       </c>
       <c r="AU122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>323</v>
-      </c>
-      <c r="C123">
+      <c r="BE122" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="123" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="N123" s="10"/>
+      <c r="O123" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AC123" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="AE123" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="AU123" s="9">
         <v>1</v>
       </c>
-      <c r="D123" t="s">
-        <v>104</v>
-      </c>
-      <c r="G123" t="s">
-        <v>114</v>
-      </c>
-      <c r="O123" t="s">
-        <v>527</v>
-      </c>
-      <c r="R123" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB123" t="s">
-        <v>515</v>
-      </c>
-      <c r="AC123" t="s">
-        <v>228</v>
-      </c>
-      <c r="AU123">
-        <v>1</v>
+      <c r="AX123" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="124" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>321</v>
+      </c>
+      <c r="B124" t="s">
+        <v>215</v>
+      </c>
+      <c r="O124" t="s">
+        <v>517</v>
+      </c>
+      <c r="AX124" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="125" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="N125" s="10"/>
+      <c r="O125" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AX125" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="126" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B126" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="D124" t="s">
-        <v>104</v>
-      </c>
-      <c r="I124" t="s">
-        <v>144</v>
-      </c>
-      <c r="O124" t="s">
-        <v>527</v>
-      </c>
-      <c r="Z124" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO124" t="s">
-        <v>214</v>
-      </c>
-      <c r="AP124">
-        <v>1</v>
-      </c>
-      <c r="AU124" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="125" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="D126" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N126" s="10"/>
+      <c r="O126" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AX126" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="127" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B125" t="s">
-        <v>124</v>
-      </c>
-      <c r="D125" t="s">
-        <v>104</v>
-      </c>
-      <c r="X125" t="s">
-        <v>114</v>
-      </c>
-      <c r="AU125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>326</v>
-      </c>
-      <c r="D126" t="s">
-        <v>104</v>
-      </c>
-      <c r="O126" t="s">
-        <v>527</v>
-      </c>
-      <c r="AJ126" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL126" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP126" t="s">
-        <v>307</v>
-      </c>
-      <c r="AR126" t="s">
-        <v>307</v>
-      </c>
-      <c r="AU126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>327</v>
-      </c>
-      <c r="D127" t="s">
-        <v>104</v>
-      </c>
-      <c r="O127" t="s">
-        <v>527</v>
-      </c>
-      <c r="AJ127" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL127" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP127" t="s">
-        <v>307</v>
-      </c>
-      <c r="AR127" t="s">
-        <v>307</v>
-      </c>
-      <c r="AU127">
-        <v>1</v>
-      </c>
-      <c r="BE127" t="s">
-        <v>515</v>
+      <c r="B127" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N127" s="10"/>
+      <c r="O127" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AX127" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="128" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>328</v>
+        <v>326</v>
+      </c>
+      <c r="B128" t="s">
+        <v>327</v>
+      </c>
+      <c r="G128" t="s">
+        <v>120</v>
       </c>
       <c r="O128" t="s">
-        <v>527</v>
-      </c>
-      <c r="AC128" t="s">
-        <v>228</v>
-      </c>
-      <c r="AE128" t="s">
-        <v>529</v>
-      </c>
-      <c r="AU128">
-        <v>1</v>
-      </c>
-      <c r="AX128" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="129" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+        <v>517</v>
+      </c>
+      <c r="AY128" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="129" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B129" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B129" t="s">
-        <v>220</v>
-      </c>
-      <c r="O129" t="s">
-        <v>527</v>
-      </c>
-      <c r="AX129" t="s">
-        <v>528</v>
+      <c r="G129" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="N129" s="10"/>
+      <c r="O129" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AY129" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="130" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>274</v>
       </c>
       <c r="O130" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="AX130" t="s">
-        <v>528</v>
+        <v>518</v>
+      </c>
+      <c r="AY130" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="131" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>331</v>
-      </c>
-      <c r="B131" t="s">
         <v>332</v>
       </c>
-      <c r="D131" t="s">
-        <v>104</v>
+      <c r="E131" t="s">
+        <v>113</v>
+      </c>
+      <c r="M131" t="s">
+        <v>333</v>
       </c>
       <c r="O131" t="s">
-        <v>527</v>
+        <v>517</v>
+      </c>
+      <c r="S131">
+        <v>1</v>
+      </c>
+      <c r="U131" t="s">
+        <v>334</v>
       </c>
       <c r="AX131" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="132" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>333</v>
-      </c>
-      <c r="B132" t="s">
-        <v>196</v>
-      </c>
-      <c r="D132" t="s">
-        <v>104</v>
-      </c>
-      <c r="O132" t="s">
-        <v>527</v>
-      </c>
-      <c r="AX132" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="133" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>334</v>
-      </c>
-      <c r="B133" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="132" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="G133" t="s">
-        <v>123</v>
-      </c>
-      <c r="O133" t="s">
-        <v>527</v>
-      </c>
-      <c r="AY133" t="s">
-        <v>528</v>
+      <c r="E132" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="M132" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="N132" s="10"/>
+      <c r="O132" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AP132" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="AX132" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AY132" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="133" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="N133" s="10"/>
+      <c r="O133" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AC133" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="AX133" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AY133" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="134" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B134" t="s">
-        <v>337</v>
-      </c>
-      <c r="G134" t="s">
-        <v>123</v>
-      </c>
-      <c r="O134" t="s">
-        <v>527</v>
-      </c>
-      <c r="AY134" t="s">
-        <v>528</v>
+        <v>102</v>
+      </c>
+      <c r="C134" t="s">
+        <v>112</v>
+      </c>
+      <c r="M134" t="s">
+        <v>201</v>
+      </c>
+      <c r="T134" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="135" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>339</v>
-      </c>
-      <c r="B135" t="s">
-        <v>281</v>
+        <v>344</v>
+      </c>
+      <c r="H135" t="s">
+        <v>290</v>
+      </c>
+      <c r="L135" t="s">
+        <v>300</v>
       </c>
       <c r="O135" t="s">
-        <v>527</v>
-      </c>
-      <c r="AX135" t="s">
-        <v>528</v>
-      </c>
-      <c r="AY135" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="136" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>340</v>
-      </c>
-      <c r="E136" t="s">
-        <v>116</v>
-      </c>
-      <c r="M136" t="s">
-        <v>341</v>
-      </c>
-      <c r="O136" t="s">
-        <v>527</v>
-      </c>
-      <c r="S136">
+        <v>517</v>
+      </c>
+      <c r="AC135" t="s">
+        <v>223</v>
+      </c>
+      <c r="AK135" t="s">
+        <v>120</v>
+      </c>
+      <c r="AP135" t="s">
+        <v>300</v>
+      </c>
+      <c r="AR135" t="s">
+        <v>300</v>
+      </c>
+      <c r="AT135" t="s">
+        <v>300</v>
+      </c>
+      <c r="AU135">
         <v>1</v>
       </c>
-      <c r="U136" t="s">
-        <v>342</v>
-      </c>
-      <c r="AX136" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="137" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>343</v>
-      </c>
-      <c r="E137" t="s">
-        <v>267</v>
-      </c>
-      <c r="M137" t="s">
-        <v>266</v>
-      </c>
-      <c r="O137" t="s">
-        <v>527</v>
-      </c>
-      <c r="AP137" t="s">
-        <v>344</v>
-      </c>
-      <c r="AX137" t="s">
-        <v>515</v>
-      </c>
-      <c r="AY137" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="138" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+    </row>
+    <row r="136" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="D138" t="s">
-        <v>104</v>
-      </c>
-      <c r="E138" t="s">
-        <v>267</v>
-      </c>
-      <c r="I138" t="s">
-        <v>344</v>
-      </c>
-      <c r="O138" t="s">
-        <v>527</v>
-      </c>
-      <c r="AC138" t="s">
-        <v>228</v>
-      </c>
-      <c r="AX138" t="s">
-        <v>515</v>
-      </c>
-      <c r="AY138" t="s">
-        <v>528</v>
+      <c r="K136" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="N136" s="10"/>
+      <c r="O136" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T136" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="137" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="K137" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="N137" s="10"/>
+      <c r="O137" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T137" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="138" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="K138" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="N138" s="10"/>
+      <c r="O138" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T138" s="9" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="139" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>350</v>
+      </c>
+      <c r="K139" t="s">
+        <v>506</v>
+      </c>
+      <c r="O139" t="s">
+        <v>517</v>
+      </c>
+      <c r="T139" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="140" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="D139" t="s">
-        <v>104</v>
-      </c>
-      <c r="L139" t="s">
-        <v>208</v>
-      </c>
-      <c r="M139" t="s">
-        <v>160</v>
-      </c>
-      <c r="O139" t="s">
-        <v>527</v>
-      </c>
-      <c r="AY139" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="140" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>352</v>
-      </c>
-      <c r="B140" t="s">
-        <v>105</v>
-      </c>
-      <c r="C140" t="s">
-        <v>115</v>
-      </c>
-      <c r="M140" t="s">
-        <v>206</v>
-      </c>
-      <c r="T140" t="s">
-        <v>171</v>
+      <c r="K140" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="N140" s="10"/>
+      <c r="O140" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T140" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="W140" s="9" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="141" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>353</v>
-      </c>
-      <c r="H141" t="s">
-        <v>297</v>
-      </c>
-      <c r="L141" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="O141" t="s">
-        <v>527</v>
-      </c>
-      <c r="AC141" t="s">
-        <v>228</v>
-      </c>
-      <c r="AK141" t="s">
-        <v>123</v>
-      </c>
-      <c r="AP141" t="s">
-        <v>307</v>
-      </c>
-      <c r="AR141" t="s">
-        <v>307</v>
-      </c>
-      <c r="AT141" t="s">
-        <v>307</v>
-      </c>
-      <c r="AU141">
-        <v>1</v>
+        <v>517</v>
+      </c>
+      <c r="T141" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="142" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>353</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O142" t="s">
+        <v>517</v>
+      </c>
+      <c r="T142" t="s">
         <v>354</v>
       </c>
-      <c r="K142" t="s">
-        <v>129</v>
-      </c>
-      <c r="O142" t="s">
-        <v>527</v>
-      </c>
-      <c r="T142" t="s">
+      <c r="Y142" t="s">
+        <v>514</v>
+      </c>
+      <c r="AN142" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="143" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="N143" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="O143" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T143" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y143" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="AN143" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="AY143" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="144" spans="1:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="N144" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="O144" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T144" s="9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="145" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="M145" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="N145" s="10"/>
+      <c r="O145" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T145" s="9" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>364</v>
+      </c>
+      <c r="B146" t="s">
+        <v>161</v>
+      </c>
+      <c r="C146" t="s">
+        <v>505</v>
+      </c>
+      <c r="O146" t="s">
+        <v>517</v>
+      </c>
+      <c r="T146" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>366</v>
+      </c>
+      <c r="B147" t="s">
+        <v>145</v>
+      </c>
+      <c r="O147" t="s">
+        <v>517</v>
+      </c>
+      <c r="W147">
+        <v>4</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>367</v>
+      </c>
+      <c r="B148" t="s">
+        <v>371</v>
+      </c>
+      <c r="O148" t="s">
+        <v>517</v>
+      </c>
+      <c r="U148" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>368</v>
+      </c>
+      <c r="B149" t="s">
+        <v>121</v>
+      </c>
+      <c r="O149" t="s">
+        <v>517</v>
+      </c>
+      <c r="T149" t="s">
+        <v>180</v>
+      </c>
+      <c r="U149" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="150" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="N150" s="10"/>
+      <c r="O150" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="U150" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>373</v>
+      </c>
+      <c r="B151" t="s">
+        <v>135</v>
+      </c>
+      <c r="E151" t="s">
+        <v>261</v>
+      </c>
+      <c r="O151" t="s">
+        <v>517</v>
+      </c>
+      <c r="U151" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>374</v>
+      </c>
+      <c r="B152" t="s">
+        <v>375</v>
+      </c>
+      <c r="C152" t="s">
+        <v>505</v>
+      </c>
+      <c r="O152" t="s">
+        <v>517</v>
+      </c>
+      <c r="AI152" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="143" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>355</v>
-      </c>
-      <c r="K143" t="s">
-        <v>129</v>
-      </c>
-      <c r="O143" t="s">
-        <v>527</v>
-      </c>
-      <c r="T143" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="144" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>357</v>
-      </c>
-      <c r="K144" t="s">
-        <v>516</v>
-      </c>
-      <c r="O144" t="s">
-        <v>527</v>
-      </c>
-      <c r="T144" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="145" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>359</v>
-      </c>
-      <c r="K145" t="s">
-        <v>516</v>
-      </c>
-      <c r="O145" t="s">
-        <v>527</v>
-      </c>
-      <c r="T145" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="146" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>360</v>
-      </c>
-      <c r="K146" t="s">
-        <v>244</v>
-      </c>
-      <c r="O146" t="s">
-        <v>527</v>
-      </c>
-      <c r="T146" t="s">
-        <v>171</v>
-      </c>
-      <c r="W146" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="147" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>361</v>
-      </c>
-      <c r="O147" t="s">
-        <v>527</v>
-      </c>
-      <c r="T147" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y147" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="148" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>362</v>
-      </c>
-      <c r="N148" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O148" t="s">
-        <v>527</v>
-      </c>
-      <c r="T148" t="s">
-        <v>363</v>
-      </c>
-      <c r="Y148" t="s">
-        <v>524</v>
-      </c>
-      <c r="AN148" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="149" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+    <row r="153" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="N153" s="10"/>
+      <c r="O153" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AN153" s="9" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>379</v>
+      </c>
+      <c r="B154" t="s">
+        <v>161</v>
+      </c>
+      <c r="C154" t="s">
+        <v>505</v>
+      </c>
+      <c r="O154" t="s">
+        <v>517</v>
+      </c>
+      <c r="T154" t="s">
         <v>365</v>
       </c>
-      <c r="N149" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O149" t="s">
-        <v>527</v>
-      </c>
-      <c r="T149" t="s">
-        <v>366</v>
-      </c>
-      <c r="Y149" t="s">
-        <v>524</v>
-      </c>
-      <c r="AN149" t="s">
-        <v>364</v>
-      </c>
-      <c r="AY149" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="150" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>367</v>
-      </c>
-      <c r="B150" t="s">
-        <v>164</v>
-      </c>
-      <c r="N150" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="O150" t="s">
-        <v>527</v>
-      </c>
-      <c r="T150" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="151" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>370</v>
-      </c>
-      <c r="M151" t="s">
-        <v>372</v>
-      </c>
-      <c r="O151" t="s">
-        <v>527</v>
-      </c>
-      <c r="T151" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="152" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>373</v>
-      </c>
-      <c r="B152" t="s">
-        <v>164</v>
-      </c>
-      <c r="C152" t="s">
-        <v>515</v>
-      </c>
-      <c r="O152" t="s">
-        <v>527</v>
-      </c>
-      <c r="T152" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="153" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>375</v>
-      </c>
-      <c r="B153" t="s">
-        <v>148</v>
-      </c>
-      <c r="O153" t="s">
-        <v>527</v>
-      </c>
-      <c r="W153">
+      <c r="AN154" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>384</v>
+      </c>
+      <c r="B155" t="s">
+        <v>383</v>
+      </c>
+      <c r="X155" t="s">
+        <v>381</v>
+      </c>
+      <c r="AN155" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>385</v>
+      </c>
+      <c r="B156" t="s">
+        <v>156</v>
+      </c>
+      <c r="J156" t="s">
+        <v>386</v>
+      </c>
+      <c r="O156" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>387</v>
+      </c>
+      <c r="B157" t="s">
+        <v>106</v>
+      </c>
+      <c r="O157" t="s">
+        <v>517</v>
+      </c>
+      <c r="R157">
+        <v>7</v>
+      </c>
+      <c r="W157">
         <v>4</v>
       </c>
-      <c r="AC153" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="154" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>376</v>
-      </c>
-      <c r="B154" t="s">
-        <v>380</v>
-      </c>
-      <c r="O154" t="s">
-        <v>527</v>
-      </c>
-      <c r="U154" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="155" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>377</v>
-      </c>
-      <c r="B155" t="s">
-        <v>124</v>
-      </c>
-      <c r="O155" t="s">
-        <v>527</v>
-      </c>
-      <c r="T155" t="s">
-        <v>183</v>
-      </c>
-      <c r="U155" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="156" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>378</v>
-      </c>
-      <c r="B156" t="s">
-        <v>381</v>
-      </c>
-      <c r="O156" t="s">
-        <v>527</v>
-      </c>
-      <c r="U156" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="157" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>382</v>
-      </c>
-      <c r="B157" t="s">
-        <v>138</v>
-      </c>
-      <c r="E157" t="s">
-        <v>267</v>
-      </c>
-      <c r="O157" t="s">
-        <v>527</v>
-      </c>
-      <c r="U157" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="158" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC157" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B158" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C158" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="O158" t="s">
-        <v>527</v>
-      </c>
-      <c r="AI158" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="159" spans="1:51" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="W158">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B159" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C159" t="s">
-        <v>515</v>
-      </c>
-      <c r="O159" t="s">
-        <v>527</v>
-      </c>
-      <c r="AN159" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="160" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>388</v>
-      </c>
-      <c r="B160" t="s">
-        <v>164</v>
-      </c>
-      <c r="C160" t="s">
-        <v>515</v>
-      </c>
-      <c r="O160" t="s">
-        <v>527</v>
-      </c>
-      <c r="T160" t="s">
-        <v>374</v>
-      </c>
-      <c r="AN160" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="161" spans="1:57" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="X159" t="s">
+        <v>111</v>
+      </c>
+      <c r="BE159" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="160" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D160" s="9">
+        <v>-1</v>
+      </c>
+      <c r="N160" s="10"/>
+      <c r="O160" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="161" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>393</v>
       </c>
       <c r="B161" t="s">
-        <v>392</v>
-      </c>
-      <c r="X161" t="s">
-        <v>390</v>
-      </c>
-      <c r="AN161" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="162" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+        <v>193</v>
+      </c>
+      <c r="D161">
+        <v>-1</v>
+      </c>
+      <c r="O161" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="162" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B162" t="s">
-        <v>159</v>
-      </c>
-      <c r="J162" t="s">
+      <c r="B162" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D162" s="9">
+        <v>-2</v>
+      </c>
+      <c r="N162" s="10"/>
+      <c r="X162" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="163" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="O162" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="163" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="B163" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D163" s="9">
+        <v>5</v>
+      </c>
+      <c r="N163" s="10"/>
+      <c r="X163" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="164" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="B163" t="s">
-        <v>109</v>
-      </c>
-      <c r="O163" t="s">
-        <v>527</v>
-      </c>
-      <c r="R163">
-        <v>7</v>
-      </c>
-      <c r="W163">
-        <v>4</v>
-      </c>
-      <c r="AC163" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="164" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="B164" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="N164" s="10"/>
+      <c r="O164" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="165" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>397</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B165" t="s">
+        <v>185</v>
+      </c>
+      <c r="C165">
+        <v>2</v>
+      </c>
+      <c r="O165" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="166" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="C164" t="s">
+      <c r="N166" s="10"/>
+      <c r="T166" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="X166" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI166" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>400</v>
+      </c>
+      <c r="T167" t="s">
+        <v>401</v>
+      </c>
+      <c r="X167" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI167" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="168" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>402</v>
+      </c>
+      <c r="B168" t="s">
+        <v>191</v>
+      </c>
+      <c r="M168" t="s">
+        <v>403</v>
+      </c>
+      <c r="O168" t="s">
+        <v>517</v>
+      </c>
+      <c r="P168" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="169" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="N169" s="10"/>
+      <c r="O169" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AF169" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="AY169" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="170" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="C170" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="N170" s="10"/>
+      <c r="O170" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AF170" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="AY170" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="171" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="N171" s="10">
+        <v>6</v>
+      </c>
+      <c r="X171" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK171" s="9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="172" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>408</v>
+      </c>
+      <c r="B172" t="s">
+        <v>409</v>
+      </c>
+      <c r="N172" s="1">
+        <v>6</v>
+      </c>
+      <c r="X172" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="173" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I173" s="9">
+        <v>1</v>
+      </c>
+      <c r="N173" s="10"/>
+      <c r="W173" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="Y173" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="AZ173" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="O164" t="s">
-        <v>527</v>
-      </c>
-      <c r="W164">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>399</v>
-      </c>
-      <c r="B165" t="s">
-        <v>400</v>
-      </c>
-      <c r="C165" t="s">
-        <v>115</v>
-      </c>
-      <c r="X165" t="s">
-        <v>114</v>
-      </c>
-      <c r="BE165" t="s">
+    </row>
+    <row r="174" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>412</v>
+      </c>
+      <c r="B174" t="s">
+        <v>104</v>
+      </c>
+      <c r="D174" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y174" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ174" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="175" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>413</v>
+      </c>
+      <c r="B175" t="s">
+        <v>236</v>
+      </c>
+      <c r="O175" t="s">
+        <v>517</v>
+      </c>
+      <c r="Y175" t="s">
+        <v>516</v>
+      </c>
+      <c r="AZ175" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="166" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>401</v>
-      </c>
-      <c r="B166" t="s">
-        <v>246</v>
-      </c>
-      <c r="D166">
-        <v>-1</v>
-      </c>
-      <c r="O166" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="167" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>402</v>
-      </c>
-      <c r="B167" t="s">
-        <v>196</v>
-      </c>
-      <c r="D167">
-        <v>-1</v>
-      </c>
-      <c r="O167" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="168" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>403</v>
-      </c>
-      <c r="B168" t="s">
-        <v>178</v>
-      </c>
-      <c r="D168">
-        <v>-2</v>
-      </c>
-      <c r="X168" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="169" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>404</v>
-      </c>
-      <c r="B169" t="s">
-        <v>124</v>
-      </c>
-      <c r="D169">
-        <v>5</v>
-      </c>
-      <c r="X169" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="170" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>405</v>
-      </c>
-      <c r="B170" t="s">
-        <v>211</v>
-      </c>
-      <c r="H170" t="s">
-        <v>297</v>
-      </c>
-      <c r="O170" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="171" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>406</v>
-      </c>
-      <c r="B171" t="s">
-        <v>188</v>
-      </c>
-      <c r="C171">
-        <v>2</v>
-      </c>
-      <c r="O171" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="172" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>407</v>
-      </c>
-      <c r="B172" t="s">
-        <v>110</v>
-      </c>
-      <c r="C172">
-        <v>5</v>
-      </c>
-      <c r="O172" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="173" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>408</v>
-      </c>
-      <c r="T173" t="s">
-        <v>409</v>
-      </c>
-      <c r="X173" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI173" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="174" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>410</v>
-      </c>
-      <c r="T174" t="s">
-        <v>411</v>
-      </c>
-      <c r="X174" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI174" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="175" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>412</v>
-      </c>
-      <c r="B175" t="s">
-        <v>194</v>
-      </c>
-      <c r="M175" t="s">
-        <v>413</v>
-      </c>
-      <c r="O175" t="s">
-        <v>527</v>
-      </c>
-      <c r="P175" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="176" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>414</v>
       </c>
       <c r="B176" t="s">
-        <v>211</v>
-      </c>
-      <c r="C176" t="s">
-        <v>307</v>
+        <v>382</v>
+      </c>
+      <c r="E176" t="s">
+        <v>231</v>
       </c>
       <c r="O176" t="s">
-        <v>527</v>
-      </c>
-      <c r="AF176" t="s">
-        <v>415</v>
-      </c>
-      <c r="AY176" t="s">
-        <v>528</v>
+        <v>517</v>
+      </c>
+      <c r="AZ176" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="177" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>415</v>
+      </c>
+      <c r="B177" t="s">
         <v>416</v>
       </c>
-      <c r="B177" t="s">
-        <v>384</v>
-      </c>
-      <c r="C177" t="s">
-        <v>307</v>
-      </c>
-      <c r="O177" t="s">
-        <v>527</v>
-      </c>
-      <c r="AF177" t="s">
-        <v>415</v>
-      </c>
-      <c r="AY177" t="s">
-        <v>528</v>
+      <c r="M177" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B178" t="s">
-        <v>159</v>
-      </c>
-      <c r="N178" s="1">
-        <v>6</v>
+        <v>418</v>
+      </c>
+      <c r="M178" t="s">
+        <v>250</v>
+      </c>
+      <c r="V178" t="s">
+        <v>112</v>
       </c>
       <c r="X178" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK178" t="s">
-        <v>521</v>
+        <v>111</v>
       </c>
     </row>
     <row r="179" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B179" t="s">
-        <v>419</v>
-      </c>
-      <c r="N179" s="1">
-        <v>6</v>
+        <v>153</v>
+      </c>
+      <c r="T179" t="s">
+        <v>427</v>
       </c>
       <c r="X179" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="180" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>421</v>
-      </c>
-      <c r="D180" t="s">
-        <v>515</v>
-      </c>
-      <c r="E180" t="s">
-        <v>119</v>
-      </c>
-      <c r="I180">
+        <v>111</v>
+      </c>
+      <c r="BC179">
         <v>1</v>
       </c>
-      <c r="W180" t="s">
-        <v>530</v>
-      </c>
-      <c r="Y180" t="s">
-        <v>526</v>
-      </c>
-      <c r="AZ180" t="s">
-        <v>525</v>
+    </row>
+    <row r="180" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="N180" s="10"/>
+      <c r="T180" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="X180" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="BC180" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="B181" t="s">
-        <v>107</v>
-      </c>
-      <c r="D181" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y181" t="s">
-        <v>125</v>
-      </c>
-      <c r="AZ181" t="s">
-        <v>125</v>
+        <v>441</v>
+      </c>
+      <c r="T181" t="s">
+        <v>442</v>
+      </c>
+      <c r="X181" t="s">
+        <v>111</v>
+      </c>
+      <c r="BD181">
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="B182" t="s">
-        <v>241</v>
-      </c>
-      <c r="O182" t="s">
-        <v>527</v>
-      </c>
-      <c r="Y182" t="s">
-        <v>526</v>
-      </c>
-      <c r="AZ182" t="s">
-        <v>525</v>
+        <v>227</v>
+      </c>
+      <c r="T182" t="s">
+        <v>354</v>
+      </c>
+      <c r="X182" t="s">
+        <v>111</v>
+      </c>
+      <c r="BD182">
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="B183" t="s">
-        <v>391</v>
-      </c>
-      <c r="E183" t="s">
-        <v>236</v>
-      </c>
-      <c r="O183" t="s">
-        <v>527</v>
-      </c>
-      <c r="AZ183" t="s">
-        <v>125</v>
+        <v>315</v>
+      </c>
+      <c r="T183" t="s">
+        <v>426</v>
+      </c>
+      <c r="BD183">
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="B184" t="s">
-        <v>426</v>
-      </c>
-      <c r="M184" t="s">
-        <v>427</v>
+        <v>110</v>
+      </c>
+      <c r="C184" t="s">
+        <v>112</v>
+      </c>
+      <c r="X184" t="s">
+        <v>111</v>
+      </c>
+      <c r="BE184" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="185" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="B185" t="s">
-        <v>428</v>
-      </c>
-      <c r="M185" t="s">
-        <v>255</v>
-      </c>
-      <c r="V185" t="s">
-        <v>115</v>
+        <v>269</v>
+      </c>
+      <c r="C185" t="s">
+        <v>112</v>
       </c>
       <c r="X185" t="s">
-        <v>114</v>
+        <v>111</v>
+      </c>
+      <c r="BE185" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="186" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B186" t="s">
-        <v>156</v>
-      </c>
-      <c r="T186" t="s">
-        <v>437</v>
+        <v>391</v>
+      </c>
+      <c r="C186" t="s">
+        <v>112</v>
       </c>
       <c r="X186" t="s">
-        <v>114</v>
-      </c>
-      <c r="BC186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>448</v>
-      </c>
-      <c r="B187" t="s">
-        <v>391</v>
-      </c>
-      <c r="T187" t="s">
-        <v>286</v>
-      </c>
-      <c r="X187" t="s">
-        <v>114</v>
-      </c>
-      <c r="BC187">
-        <v>1</v>
+        <v>111</v>
+      </c>
+      <c r="BE186" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="187" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="N187" s="10"/>
+      <c r="X187" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="BE187" s="9" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="188" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B188" t="s">
-        <v>451</v>
+        <v>315</v>
       </c>
       <c r="T188" t="s">
-        <v>452</v>
+        <v>168</v>
       </c>
       <c r="X188" t="s">
-        <v>114</v>
-      </c>
-      <c r="BD188">
-        <v>1</v>
+        <v>111</v>
+      </c>
+      <c r="AI188" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="189" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B189" t="s">
-        <v>232</v>
-      </c>
-      <c r="T189" t="s">
-        <v>363</v>
+        <v>205</v>
       </c>
       <c r="X189" t="s">
-        <v>114</v>
-      </c>
-      <c r="BD189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>457</v>
-      </c>
-      <c r="B190" t="s">
-        <v>322</v>
-      </c>
-      <c r="T190" t="s">
-        <v>436</v>
-      </c>
-      <c r="BD190">
-        <v>1</v>
+        <v>111</v>
+      </c>
+      <c r="AI189" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="190" spans="1:57" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N190" s="10"/>
+      <c r="T190" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="X190" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK190" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="191" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
-      </c>
-      <c r="C191" t="s">
-        <v>115</v>
+        <v>463</v>
+      </c>
+      <c r="T191" t="s">
+        <v>354</v>
       </c>
       <c r="X191" t="s">
-        <v>114</v>
-      </c>
-      <c r="BE191" t="s">
-        <v>515</v>
+        <v>111</v>
+      </c>
+      <c r="AK191" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="192" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>468</v>
+      </c>
+      <c r="B192" t="s">
+        <v>466</v>
+      </c>
+      <c r="T192" t="s">
+        <v>467</v>
+      </c>
+      <c r="X192" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK192" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="193" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>471</v>
+      </c>
+      <c r="B193" t="s">
+        <v>469</v>
+      </c>
+      <c r="T193" t="s">
+        <v>470</v>
+      </c>
+      <c r="X193" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK193" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="194" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>474</v>
+      </c>
+      <c r="B194" t="s">
+        <v>205</v>
+      </c>
+      <c r="X194" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI194" t="s">
+        <v>509</v>
+      </c>
+      <c r="AK194" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="195" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>475</v>
+      </c>
+      <c r="B195" t="s">
+        <v>476</v>
+      </c>
+      <c r="T195" t="s">
+        <v>477</v>
+      </c>
+      <c r="X195" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK195" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="196" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>479</v>
+      </c>
+      <c r="B196" t="s">
+        <v>191</v>
+      </c>
+      <c r="M196" t="s">
+        <v>480</v>
+      </c>
+      <c r="V196">
+        <v>1</v>
+      </c>
+      <c r="X196" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="197" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>482</v>
+      </c>
+      <c r="B197" t="s">
+        <v>418</v>
+      </c>
+      <c r="M197" t="s">
+        <v>250</v>
+      </c>
+      <c r="T197" t="s">
+        <v>481</v>
+      </c>
+      <c r="V197">
+        <v>1</v>
+      </c>
+      <c r="X197" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="198" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>484</v>
+      </c>
+      <c r="B198" t="s">
+        <v>483</v>
+      </c>
+      <c r="M198" t="s">
+        <v>164</v>
+      </c>
+      <c r="V198">
+        <v>1</v>
+      </c>
+      <c r="X198" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="199" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>486</v>
+      </c>
+      <c r="B199" t="s">
+        <v>485</v>
+      </c>
+      <c r="E199" t="s">
+        <v>207</v>
+      </c>
+      <c r="G199" t="s">
+        <v>120</v>
+      </c>
+      <c r="T199" t="s">
+        <v>365</v>
+      </c>
+      <c r="X199" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="200" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>487</v>
+      </c>
+      <c r="B200" t="s">
+        <v>429</v>
+      </c>
+      <c r="E200" t="s">
+        <v>207</v>
+      </c>
+      <c r="G200" t="s">
+        <v>120</v>
+      </c>
+      <c r="T200" t="s">
         <v>462</v>
       </c>
-      <c r="B192" t="s">
-        <v>275</v>
-      </c>
-      <c r="C192" t="s">
-        <v>115</v>
-      </c>
-      <c r="X192" t="s">
-        <v>114</v>
-      </c>
-      <c r="BE192" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="193" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>463</v>
-      </c>
-      <c r="B193" t="s">
-        <v>400</v>
-      </c>
-      <c r="C193" t="s">
-        <v>115</v>
-      </c>
-      <c r="X193" t="s">
-        <v>114</v>
-      </c>
-      <c r="BE193" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="194" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>465</v>
-      </c>
-      <c r="B194" t="s">
-        <v>464</v>
-      </c>
-      <c r="C194" t="s">
-        <v>115</v>
-      </c>
-      <c r="X194" t="s">
-        <v>114</v>
-      </c>
-      <c r="BE194" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="195" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>466</v>
-      </c>
-      <c r="B195" t="s">
-        <v>322</v>
-      </c>
-      <c r="T195" t="s">
-        <v>171</v>
-      </c>
-      <c r="X195" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI195" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="196" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>469</v>
-      </c>
-      <c r="B196" t="s">
-        <v>210</v>
-      </c>
-      <c r="X196" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI196" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="197" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>470</v>
-      </c>
-      <c r="B197" t="s">
-        <v>471</v>
-      </c>
-      <c r="T197" t="s">
-        <v>472</v>
-      </c>
-      <c r="X197" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK197" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="198" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>474</v>
-      </c>
-      <c r="B198" t="s">
-        <v>473</v>
-      </c>
-      <c r="T198" t="s">
-        <v>363</v>
-      </c>
-      <c r="X198" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK198" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="199" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>478</v>
-      </c>
-      <c r="B199" t="s">
-        <v>476</v>
-      </c>
-      <c r="T199" t="s">
-        <v>477</v>
-      </c>
-      <c r="X199" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK199" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="200" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>481</v>
-      </c>
-      <c r="B200" t="s">
-        <v>479</v>
-      </c>
-      <c r="T200" t="s">
-        <v>480</v>
-      </c>
       <c r="X200" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK200" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="201" spans="1:57" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="201" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B201" t="s">
-        <v>210</v>
+        <v>107</v>
+      </c>
+      <c r="D201" t="s">
+        <v>101</v>
+      </c>
+      <c r="E201" t="s">
+        <v>103</v>
       </c>
       <c r="X201" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI201" t="s">
-        <v>519</v>
-      </c>
-      <c r="AK201" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="202" spans="1:57" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="AU201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B202" t="s">
-        <v>486</v>
-      </c>
-      <c r="T202" t="s">
-        <v>487</v>
+        <v>372</v>
+      </c>
+      <c r="D202" t="s">
+        <v>505</v>
+      </c>
+      <c r="E202" t="s">
+        <v>116</v>
       </c>
       <c r="X202" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK202" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="203" spans="1:57" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="203" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="B203" t="s">
-        <v>194</v>
-      </c>
-      <c r="M203" t="s">
-        <v>490</v>
-      </c>
-      <c r="V203">
-        <v>1</v>
+        <v>445</v>
+      </c>
+      <c r="R203">
+        <v>9</v>
       </c>
       <c r="X203" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="204" spans="1:57" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="BA203" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="204" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="B204" t="s">
-        <v>428</v>
-      </c>
-      <c r="M204" t="s">
-        <v>255</v>
-      </c>
-      <c r="T204" t="s">
-        <v>491</v>
-      </c>
-      <c r="V204">
-        <v>1</v>
+        <v>193</v>
+      </c>
+      <c r="R204">
+        <v>9</v>
       </c>
       <c r="X204" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="205" spans="1:57" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="205" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="B205" t="s">
-        <v>493</v>
-      </c>
-      <c r="M205" t="s">
-        <v>167</v>
-      </c>
-      <c r="V205">
-        <v>1</v>
+        <v>163</v>
+      </c>
+      <c r="R205">
+        <v>9</v>
+      </c>
+      <c r="T205" t="s">
+        <v>401</v>
       </c>
       <c r="X205" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="206" spans="1:57" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="BD205" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="206" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>496</v>
+        <v>529</v>
       </c>
       <c r="B206" t="s">
-        <v>495</v>
-      </c>
-      <c r="E206" t="s">
-        <v>212</v>
-      </c>
-      <c r="G206" t="s">
-        <v>123</v>
-      </c>
-      <c r="T206" t="s">
-        <v>374</v>
+        <v>199</v>
+      </c>
+      <c r="R206">
+        <v>9</v>
       </c>
       <c r="X206" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="207" spans="1:57" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="AI206" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="207" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="B207" t="s">
-        <v>439</v>
-      </c>
-      <c r="E207" t="s">
-        <v>212</v>
-      </c>
-      <c r="G207" t="s">
-        <v>123</v>
+        <v>107</v>
+      </c>
+      <c r="R207">
+        <v>9</v>
       </c>
       <c r="T207" t="s">
-        <v>472</v>
+        <v>129</v>
       </c>
       <c r="X207" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="208" spans="1:57" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="208" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="B208" t="s">
-        <v>110</v>
-      </c>
-      <c r="D208" t="s">
-        <v>104</v>
-      </c>
-      <c r="E208" t="s">
-        <v>106</v>
+        <v>329</v>
+      </c>
+      <c r="R208">
+        <v>9</v>
       </c>
       <c r="X208" t="s">
-        <v>114</v>
-      </c>
-      <c r="AU208">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:56" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="B209" t="s">
-        <v>381</v>
-      </c>
-      <c r="D209" t="s">
-        <v>515</v>
-      </c>
-      <c r="E209" t="s">
-        <v>119</v>
+        <v>172</v>
+      </c>
+      <c r="R209">
+        <v>9</v>
+      </c>
+      <c r="T209" t="s">
+        <v>380</v>
       </c>
       <c r="X209" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="210" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>536</v>
-      </c>
-      <c r="B210" t="s">
-        <v>455</v>
-      </c>
-      <c r="R210">
-        <v>9</v>
-      </c>
-      <c r="X210" t="s">
-        <v>294</v>
-      </c>
-      <c r="BA210" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="211" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>537</v>
-      </c>
-      <c r="B211" t="s">
-        <v>196</v>
-      </c>
-      <c r="R211">
-        <v>9</v>
-      </c>
-      <c r="X211" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="212" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>538</v>
-      </c>
-      <c r="B212" t="s">
-        <v>166</v>
-      </c>
-      <c r="R212">
-        <v>9</v>
-      </c>
-      <c r="T212" t="s">
-        <v>411</v>
-      </c>
-      <c r="X212" t="s">
-        <v>294</v>
-      </c>
-      <c r="BD212" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="213" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>539</v>
-      </c>
-      <c r="B213" t="s">
-        <v>203</v>
-      </c>
-      <c r="R213">
-        <v>9</v>
-      </c>
-      <c r="X213" t="s">
-        <v>294</v>
-      </c>
-      <c r="AI213" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="214" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>540</v>
-      </c>
-      <c r="B214" t="s">
-        <v>110</v>
-      </c>
-      <c r="R214">
-        <v>9</v>
-      </c>
-      <c r="T214" t="s">
-        <v>132</v>
-      </c>
-      <c r="X214" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="215" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>541</v>
-      </c>
-      <c r="B215" t="s">
-        <v>337</v>
-      </c>
-      <c r="R215">
-        <v>9</v>
-      </c>
-      <c r="X215" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="216" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>542</v>
-      </c>
-      <c r="B216" t="s">
-        <v>175</v>
-      </c>
-      <c r="R216">
-        <v>9</v>
-      </c>
-      <c r="T216" t="s">
-        <v>389</v>
-      </c>
-      <c r="X216" t="s">
-        <v>294</v>
-      </c>
-      <c r="AI216" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="217" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>531</v>
-      </c>
-      <c r="B217" t="s">
-        <v>391</v>
-      </c>
-      <c r="M217" t="s">
-        <v>533</v>
-      </c>
-      <c r="O217" t="s">
-        <v>527</v>
-      </c>
-      <c r="T217" t="s">
-        <v>532</v>
+        <v>287</v>
+      </c>
+      <c r="AI209" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="210" spans="1:35" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="M210" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="N210" s="10"/>
+      <c r="O210" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T210" s="9" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BE217" xr:uid="{EA5A6498-8735-4638-A034-733AD69F003F}"/>
+  <autoFilter ref="A1:BE210" xr:uid="{EA5A6498-8735-4638-A034-733AD69F003F}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6315,147 +6233,147 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
